--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5229,7 +5229,7 @@
         <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>127169172</v>
       </c>
       <c r="B40" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209391</v>
+        <v>127209408</v>
       </c>
       <c r="B41" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5645,16 +5645,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733292</v>
+        <v>733340</v>
       </c>
       <c r="R41" t="n">
-        <v>7102236</v>
+        <v>7102327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5705,6 +5705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5731,10 +5736,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5742,16 +5747,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5766,10 +5771,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R42" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5802,11 +5807,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5833,48 +5833,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R43" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,19 +5901,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,60 +5918,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R44" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,9 +5998,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,60 +6025,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127170226</v>
+        <v>127209432</v>
       </c>
       <c r="B45" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733338</v>
+        <v>733313</v>
       </c>
       <c r="R45" t="n">
-        <v>7102256</v>
+        <v>7102466</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,19 +6105,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6132,60 +6122,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209432</v>
+        <v>127170226</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733313</v>
+        <v>733338</v>
       </c>
       <c r="R46" t="n">
-        <v>7102466</v>
+        <v>7102256</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6212,9 +6202,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6229,61 +6229,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127212703</v>
+        <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>57654</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733290</v>
+        <v>733357</v>
       </c>
       <c r="R47" t="n">
-        <v>7102188</v>
+        <v>7102361</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6345,7 +6341,7 @@
         <v>127209434</v>
       </c>
       <c r="B48" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6439,45 +6435,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127209411</v>
+        <v>127212703</v>
       </c>
       <c r="B49" t="n">
-        <v>80119</v>
+        <v>57654</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733357</v>
+        <v>733290</v>
       </c>
       <c r="R49" t="n">
-        <v>7102361</v>
+        <v>7102188</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6539,7 +6539,7 @@
         <v>127209431</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6633,52 +6633,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>92609</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R51" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6705,19 +6701,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6732,60 +6718,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>92535</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R52" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6812,9 +6802,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,22 +6829,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R53" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,19 +6909,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6936,22 +6931,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6959,37 +6954,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R54" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7016,14 +7011,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7053,7 +7053,7 @@
         <v>127171825</v>
       </c>
       <c r="B55" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209393</v>
+        <v>127209397</v>
       </c>
       <c r="B56" t="n">
         <v>57654</v>
@@ -7192,10 +7192,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733129</v>
+        <v>733264</v>
       </c>
       <c r="R56" t="n">
-        <v>7102002</v>
+        <v>7102152</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7257,7 +7257,7 @@
         <v>127209427</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127209397</v>
+        <v>127209393</v>
       </c>
       <c r="B58" t="n">
         <v>57654</v>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733264</v>
+        <v>733129</v>
       </c>
       <c r="R58" t="n">
-        <v>7102152</v>
+        <v>7102002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7457,7 +7457,7 @@
         <v>127170235</v>
       </c>
       <c r="B59" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7658,32 +7658,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B61" t="n">
-        <v>91210</v>
+        <v>91337</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R61" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127169259</v>
+        <v>127168961</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>91284</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733273</v>
+        <v>733165</v>
       </c>
       <c r="R62" t="n">
-        <v>7102237</v>
+        <v>7102177</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7872,10 +7872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172533</v>
+        <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7883,21 +7883,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733058</v>
+        <v>733273</v>
       </c>
       <c r="R63" t="n">
-        <v>7102382</v>
+        <v>7102237</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7979,51 +7979,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127213086</v>
+        <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733292</v>
+        <v>733365</v>
       </c>
       <c r="R64" t="n">
-        <v>7102236</v>
+        <v>7102422</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8050,40 +8051,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127209409</v>
+        <v>127213086</v>
       </c>
       <c r="B65" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8091,34 +8101,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733357</v>
+        <v>733292</v>
       </c>
       <c r="R65" t="n">
-        <v>7102357</v>
+        <v>7102236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8159,6 +8172,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8177,52 +8191,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172025</v>
+        <v>127209409</v>
       </c>
       <c r="B66" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733365</v>
+        <v>733357</v>
       </c>
       <c r="R66" t="n">
-        <v>7102422</v>
+        <v>7102357</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8249,19 +8259,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,22 +8276,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127168323</v>
+        <v>127209442</v>
       </c>
       <c r="B67" t="n">
-        <v>91210</v>
+        <v>80149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8299,37 +8299,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R67" t="n">
-        <v>7102111</v>
+        <v>7102353</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8356,87 +8359,75 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209442</v>
+        <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>80118</v>
+        <v>57654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R68" t="n">
-        <v>7102353</v>
+        <v>7102084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8477,7 +8468,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8499,7 +8489,7 @@
         <v>127209388</v>
       </c>
       <c r="B69" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8593,48 +8583,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127209399</v>
+        <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>57654</v>
+        <v>91284</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
         <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7102084</v>
+        <v>7102111</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8661,9 +8651,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8787,45 +8787,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127173185</v>
+        <v>127209444</v>
       </c>
       <c r="B72" t="n">
-        <v>91263</v>
+        <v>56849</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733067</v>
+        <v>733140</v>
       </c>
       <c r="R72" t="n">
-        <v>7102302</v>
+        <v>7102617</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8860,6 +8868,11 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>4 stycken tjädrar flög upp</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8872,65 +8885,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127209444</v>
+        <v>127209403</v>
       </c>
       <c r="B73" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733140</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7102617</v>
+        <v>7102321</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8967,7 +8972,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>4 stycken tjädrar flög upp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9095,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127209403</v>
+        <v>127168623</v>
       </c>
       <c r="B75" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9106,37 +9111,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733380</v>
+        <v>733163</v>
       </c>
       <c r="R75" t="n">
-        <v>7102321</v>
+        <v>7102182</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9163,14 +9168,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9185,39 +9195,39 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127168623</v>
+        <v>127209440</v>
       </c>
       <c r="B76" t="n">
-        <v>78980</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9226,19 +9236,22 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733163</v>
+        <v>733324</v>
       </c>
       <c r="R76" t="n">
-        <v>7102182</v>
+        <v>7102432</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9265,93 +9278,75 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127168984</v>
+        <v>127209429</v>
       </c>
       <c r="B77" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733206</v>
+        <v>733361</v>
       </c>
       <c r="R77" t="n">
-        <v>7102172</v>
+        <v>7102666</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9398,22 +9393,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jonas Eilertsen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127209405</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9421,34 +9416,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733153</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9481,6 +9480,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9507,52 +9511,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127209405</v>
+        <v>127172437</v>
       </c>
       <c r="B79" t="n">
-        <v>57657</v>
+        <v>98436</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733153</v>
+        <v>733268</v>
       </c>
       <c r="R79" t="n">
-        <v>7102629</v>
+        <v>7102284</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9579,14 +9579,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9601,22 +9606,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127209440</v>
+        <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>80118</v>
+        <v>92609</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9624,37 +9629,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733324</v>
+        <v>733350</v>
       </c>
       <c r="R80" t="n">
-        <v>7102432</v>
+        <v>7102804</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9695,7 +9697,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9714,48 +9715,51 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127172437</v>
+        <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>98361</v>
+        <v>91315</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733268</v>
+        <v>733067</v>
       </c>
       <c r="R81" t="n">
-        <v>7102284</v>
+        <v>7102302</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9782,84 +9786,84 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127209438</v>
+        <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>92535</v>
+        <v>98436</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733350</v>
+        <v>733206</v>
       </c>
       <c r="R82" t="n">
-        <v>7102804</v>
+        <v>7102172</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9906,15 +9910,838 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127265350</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>733212</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7102051</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127265357</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>733162</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7102144</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127265352</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>733152</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7101994</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska hål</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127265356</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>733288</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7102194</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127265351</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>733164</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7102008</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska hål i gran</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127265358</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>733189</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7102064</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127265349</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>733241</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7102094</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Stora hål gran</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127265353</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>733095</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7102030</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 10 hål på tallåga</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B37" t="n">
-        <v>79629</v>
+        <v>92615</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R37" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,9 +5294,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5311,60 +5321,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B38" t="n">
-        <v>92609</v>
+        <v>79632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R38" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5391,19 +5401,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5530,7 +5530,7 @@
         <v>127169172</v>
       </c>
       <c r="B40" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6037,48 +6037,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127209432</v>
+        <v>127170226</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733313</v>
+        <v>733338</v>
       </c>
       <c r="R45" t="n">
-        <v>7102466</v>
+        <v>7102256</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,9 +6105,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6122,60 +6132,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127170226</v>
+        <v>127209432</v>
       </c>
       <c r="B46" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733338</v>
+        <v>733313</v>
       </c>
       <c r="R46" t="n">
-        <v>7102256</v>
+        <v>7102466</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6202,19 +6212,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6229,12 +6229,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6244,7 +6244,7 @@
         <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>127209434</v>
       </c>
       <c r="B48" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>127209431</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6633,48 +6633,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B51" t="n">
-        <v>92609</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R51" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6701,9 +6705,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6718,64 +6732,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>92615</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R52" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6802,19 +6812,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,22 +6829,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R53" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6931,22 +6936,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B54" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,37 +6959,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R54" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7053,7 +7053,7 @@
         <v>127171825</v>
       </c>
       <c r="B55" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>127209427</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>127170235</v>
       </c>
       <c r="B59" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7658,32 +7658,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172533</v>
+        <v>127168961</v>
       </c>
       <c r="B61" t="n">
-        <v>91337</v>
+        <v>91290</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733058</v>
+        <v>733165</v>
       </c>
       <c r="R61" t="n">
-        <v>7102382</v>
+        <v>7102177</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B62" t="n">
-        <v>91284</v>
+        <v>91343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R62" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7875,7 +7875,7 @@
         <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7979,52 +7979,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172025</v>
+        <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733365</v>
+        <v>733292</v>
       </c>
       <c r="R64" t="n">
-        <v>7102422</v>
+        <v>7102236</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8051,49 +8050,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127213086</v>
+        <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,37 +8091,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733292</v>
+        <v>733357</v>
       </c>
       <c r="R65" t="n">
-        <v>7102236</v>
+        <v>7102357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8172,7 +8159,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8191,48 +8177,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127209409</v>
+        <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733357</v>
+        <v>733365</v>
       </c>
       <c r="R66" t="n">
-        <v>7102357</v>
+        <v>7102422</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8259,9 +8249,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,22 +8276,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127209442</v>
+        <v>127168323</v>
       </c>
       <c r="B67" t="n">
-        <v>80149</v>
+        <v>91290</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8299,40 +8299,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R67" t="n">
-        <v>7102353</v>
+        <v>7102111</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8359,75 +8356,87 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209399</v>
+        <v>127209442</v>
       </c>
       <c r="B68" t="n">
-        <v>57654</v>
+        <v>80152</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R68" t="n">
-        <v>7102084</v>
+        <v>7102353</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8468,6 +8477,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8486,10 +8496,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209388</v>
+        <v>127209399</v>
       </c>
       <c r="B69" t="n">
-        <v>79629</v>
+        <v>57654</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8497,21 +8507,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8521,10 +8531,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R69" t="n">
-        <v>7102463</v>
+        <v>7102084</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8583,48 +8593,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127168323</v>
+        <v>127209388</v>
       </c>
       <c r="B70" t="n">
-        <v>91284</v>
+        <v>79632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733192</v>
+        <v>733440</v>
       </c>
       <c r="R70" t="n">
-        <v>7102111</v>
+        <v>7102463</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8651,19 +8661,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127209403</v>
+        <v>127168623</v>
       </c>
       <c r="B73" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733380</v>
+        <v>733163</v>
       </c>
       <c r="R73" t="n">
-        <v>7102321</v>
+        <v>7102182</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,14 +8965,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8987,22 +8992,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209401</v>
+        <v>127209403</v>
       </c>
       <c r="B74" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,16 +9015,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9028,20 +9033,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733172</v>
+        <v>733380</v>
       </c>
       <c r="R74" t="n">
-        <v>7102001</v>
+        <v>7102321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9074,6 +9075,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9100,10 +9106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127168623</v>
+        <v>127209401</v>
       </c>
       <c r="B75" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9111,37 +9117,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733163</v>
+        <v>733172</v>
       </c>
       <c r="R75" t="n">
-        <v>7102182</v>
+        <v>7102001</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9168,19 +9178,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,63 +9195,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209440</v>
+        <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>98442</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733324</v>
+        <v>733268</v>
       </c>
       <c r="R76" t="n">
-        <v>7102432</v>
+        <v>7102284</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9278,57 +9275,66 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209429</v>
+        <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>79011</v>
+        <v>80152</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9337,16 +9343,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733361</v>
+        <v>733324</v>
       </c>
       <c r="R77" t="n">
-        <v>7102666</v>
+        <v>7102432</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9387,6 +9396,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9405,10 +9415,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209405</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9416,38 +9426,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733153</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102629</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9480,11 +9486,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9511,48 +9512,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127172437</v>
+        <v>127209405</v>
       </c>
       <c r="B79" t="n">
-        <v>98436</v>
+        <v>57657</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733268</v>
+        <v>733153</v>
       </c>
       <c r="R79" t="n">
-        <v>7102284</v>
+        <v>7102629</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9579,19 +9584,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>127265357</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>127265358</v>
       </c>
       <c r="B88" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R37" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,19 +5294,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5321,60 +5311,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R38" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5401,9 +5391,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127169172</v>
+        <v>127209408</v>
       </c>
       <c r="B40" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733225</v>
+        <v>733340</v>
       </c>
       <c r="R40" t="n">
-        <v>7102172</v>
+        <v>7102327</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,19 +5595,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:41</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5622,22 +5617,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5645,16 +5640,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R41" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5705,11 +5700,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5736,48 +5726,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127209391</v>
+        <v>127169172</v>
       </c>
       <c r="B42" t="n">
-        <v>57654</v>
+        <v>97320</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733292</v>
+        <v>733225</v>
       </c>
       <c r="R42" t="n">
-        <v>7102236</v>
+        <v>7102172</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5804,9 +5794,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,60 +5821,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R43" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,9 +5901,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,60 +5928,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R44" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5998,19 +6008,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,60 +6025,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127170226</v>
+        <v>127209432</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733338</v>
+        <v>733313</v>
       </c>
       <c r="R45" t="n">
-        <v>7102256</v>
+        <v>7102466</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,19 +6105,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6132,44 +6122,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209432</v>
+        <v>127209434</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6179,10 +6169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733313</v>
+        <v>733218</v>
       </c>
       <c r="R46" t="n">
-        <v>7102466</v>
+        <v>7102512</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6241,32 +6231,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209411</v>
+        <v>127209431</v>
       </c>
       <c r="B47" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6276,10 +6266,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733357</v>
+        <v>733392</v>
       </c>
       <c r="R47" t="n">
-        <v>7102361</v>
+        <v>7102590</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6338,10 +6328,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127209434</v>
+        <v>127209411</v>
       </c>
       <c r="B48" t="n">
-        <v>92615</v>
+        <v>80153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6349,21 +6339,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6373,10 +6363,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733218</v>
+        <v>733357</v>
       </c>
       <c r="R48" t="n">
-        <v>7102512</v>
+        <v>7102361</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6536,48 +6526,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127209431</v>
+        <v>127170226</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733392</v>
+        <v>733338</v>
       </c>
       <c r="R50" t="n">
-        <v>7102590</v>
+        <v>7102256</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6604,9 +6594,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,64 +6621,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>92615</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R51" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6705,19 +6701,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6732,60 +6718,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>92615</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R52" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6812,9 +6802,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,22 +6829,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R53" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,19 +6909,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6936,22 +6931,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6959,37 +6954,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R54" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7016,14 +7011,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,60 +7038,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127171825</v>
+        <v>127209427</v>
       </c>
       <c r="B55" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733389</v>
+        <v>733364</v>
       </c>
       <c r="R55" t="n">
-        <v>7102445</v>
+        <v>7102666</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7118,19 +7118,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:19</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7139,18 +7134,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7254,10 +7250,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127209427</v>
+        <v>127209393</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7265,21 +7261,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7289,10 +7285,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733364</v>
+        <v>733129</v>
       </c>
       <c r="R57" t="n">
-        <v>7102666</v>
+        <v>7102002</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7327,18 +7323,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7357,48 +7347,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127209393</v>
+        <v>127171825</v>
       </c>
       <c r="B58" t="n">
-        <v>57654</v>
+        <v>91290</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733129</v>
+        <v>733389</v>
       </c>
       <c r="R58" t="n">
-        <v>7102002</v>
+        <v>7102445</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7425,9 +7415,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7442,60 +7442,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127170235</v>
+        <v>127209420</v>
       </c>
       <c r="B59" t="n">
-        <v>80117</v>
+        <v>58027</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733349</v>
+        <v>733290</v>
       </c>
       <c r="R59" t="n">
-        <v>7102356</v>
+        <v>7102188</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7522,19 +7522,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7549,60 +7539,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127209420</v>
+        <v>127170235</v>
       </c>
       <c r="B60" t="n">
-        <v>58027</v>
+        <v>80117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733290</v>
+        <v>733349</v>
       </c>
       <c r="R60" t="n">
-        <v>7102188</v>
+        <v>7102356</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7629,9 +7619,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7646,44 +7646,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B61" t="n">
-        <v>91290</v>
+        <v>91343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R61" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172533</v>
+        <v>127168961</v>
       </c>
       <c r="B62" t="n">
-        <v>91343</v>
+        <v>91290</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733058</v>
+        <v>733165</v>
       </c>
       <c r="R62" t="n">
-        <v>7102382</v>
+        <v>7102177</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7979,51 +7979,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127213086</v>
+        <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733292</v>
+        <v>733365</v>
       </c>
       <c r="R64" t="n">
-        <v>7102236</v>
+        <v>7102422</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8050,40 +8051,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127209409</v>
+        <v>127213086</v>
       </c>
       <c r="B65" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8091,34 +8101,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733357</v>
+        <v>733292</v>
       </c>
       <c r="R65" t="n">
-        <v>7102357</v>
+        <v>7102236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8159,6 +8172,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8177,52 +8191,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172025</v>
+        <v>127209409</v>
       </c>
       <c r="B66" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733365</v>
+        <v>733357</v>
       </c>
       <c r="R66" t="n">
-        <v>7102422</v>
+        <v>7102357</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8249,19 +8259,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,60 +8276,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127168323</v>
+        <v>127209388</v>
       </c>
       <c r="B67" t="n">
-        <v>91290</v>
+        <v>79632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733192</v>
+        <v>733440</v>
       </c>
       <c r="R67" t="n">
-        <v>7102111</v>
+        <v>7102463</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8356,19 +8356,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8383,60 +8373,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209442</v>
+        <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>80152</v>
+        <v>57654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R68" t="n">
-        <v>7102353</v>
+        <v>7102084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8477,7 +8464,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8496,45 +8482,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209399</v>
+        <v>127209442</v>
       </c>
       <c r="B69" t="n">
-        <v>57654</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R69" t="n">
-        <v>7102084</v>
+        <v>7102353</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8575,6 +8564,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8593,48 +8583,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127209388</v>
+        <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>91290</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7102463</v>
+        <v>7102111</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8661,9 +8651,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127168623</v>
+        <v>127209403</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733163</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7102182</v>
+        <v>7102321</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,19 +8965,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:18</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8992,22 +8987,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209403</v>
+        <v>127209401</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9015,16 +9010,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9033,16 +9028,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733380</v>
+        <v>733172</v>
       </c>
       <c r="R74" t="n">
-        <v>7102321</v>
+        <v>7102001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9075,11 +9074,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9106,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127209401</v>
+        <v>127168623</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9117,41 +9111,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733172</v>
+        <v>733163</v>
       </c>
       <c r="R75" t="n">
-        <v>7102001</v>
+        <v>7102182</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9178,9 +9168,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,60 +9195,63 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127172437</v>
+        <v>127209440</v>
       </c>
       <c r="B76" t="n">
-        <v>98442</v>
+        <v>80152</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733268</v>
+        <v>733324</v>
       </c>
       <c r="R76" t="n">
-        <v>7102284</v>
+        <v>7102432</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,66 +9278,57 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209440</v>
+        <v>127209429</v>
       </c>
       <c r="B77" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9343,19 +9337,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733324</v>
+        <v>733361</v>
       </c>
       <c r="R77" t="n">
-        <v>7102432</v>
+        <v>7102666</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9396,7 +9387,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9415,48 +9405,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127172437</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733268</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102284</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9483,9 +9473,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9500,12 +9500,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -10116,45 +10116,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B85" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R85" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10191,7 +10199,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10200,6 +10208,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10218,53 +10227,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B86" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R86" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10301,7 +10302,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10310,7 +10311,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10743,6 +10743,2999 @@
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127352850</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>732865</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7102255</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127352849</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>732858</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7102299</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127352856</v>
+      </c>
+      <c r="B93" t="n">
+        <v>82855</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>732867</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7102250</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127352845</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91321</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>733015</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7102294</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127352822</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91683</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>733131</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7102015</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127352829</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>732945</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7102361</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127352841</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>732992</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7102126</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127352851</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>733008</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7102279</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127352828</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>732881</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7102356</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127352846</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>733141</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7102155</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127352853</v>
+      </c>
+      <c r="B101" t="n">
+        <v>82855</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>733168</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7102021</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127352833</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>733067</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7102180</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127352824</v>
+      </c>
+      <c r="B103" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>732841</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7102300</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>127352831</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91275</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>112</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>733269</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7102176</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127352857</v>
+      </c>
+      <c r="B105" t="n">
+        <v>75130</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>308</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>733195</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7102084</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127352830</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>732870</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7102344</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>127352837</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>732901</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7102156</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127352848</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>732920</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7102396</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>127352825</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>733193</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7102147</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127352852</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>732946</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7102368</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127352832</v>
+      </c>
+      <c r="B111" t="n">
+        <v>91275</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>112</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>732878</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7102347</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127352844</v>
+      </c>
+      <c r="B112" t="n">
+        <v>58027</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>732900</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7102348</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127352855</v>
+      </c>
+      <c r="B113" t="n">
+        <v>82855</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>732882</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7102273</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127352827</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>732905</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7102362</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127352834</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>732868</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7102325</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127352835</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>733013</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7102291</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127352836</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>732906</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7102369</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>127352847</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>733006</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7102273</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>127352823</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91683</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>732915</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7102363</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127352854</v>
+      </c>
+      <c r="B120" t="n">
+        <v>82855</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>732861</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7102297</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B37" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R37" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,9 +5294,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5311,60 +5321,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B38" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R38" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5391,19 +5401,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5833,48 +5833,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R43" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,19 +5901,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,60 +5918,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R44" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,9 +5998,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -7979,52 +7979,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172025</v>
+        <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733365</v>
+        <v>733292</v>
       </c>
       <c r="R64" t="n">
-        <v>7102422</v>
+        <v>7102236</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8051,49 +8050,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127213086</v>
+        <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,37 +8091,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733292</v>
+        <v>733357</v>
       </c>
       <c r="R65" t="n">
-        <v>7102236</v>
+        <v>7102357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8172,7 +8159,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8191,48 +8177,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127209409</v>
+        <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733357</v>
+        <v>733365</v>
       </c>
       <c r="R66" t="n">
-        <v>7102357</v>
+        <v>7102422</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8259,9 +8249,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,12 +8276,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -10116,53 +10116,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B85" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R85" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10199,7 +10191,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10208,7 +10200,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10227,45 +10218,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R86" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10302,7 +10301,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10311,6 +10310,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R37" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,19 +5294,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5321,60 +5311,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R38" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5401,9 +5391,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127209408</v>
+        <v>127169172</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>97321</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733340</v>
+        <v>733225</v>
       </c>
       <c r="R40" t="n">
-        <v>7102327</v>
+        <v>7102172</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,14 +5595,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5617,22 +5622,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209391</v>
+        <v>127209408</v>
       </c>
       <c r="B41" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5640,16 +5645,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733292</v>
+        <v>733340</v>
       </c>
       <c r="R41" t="n">
-        <v>7102236</v>
+        <v>7102327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5700,6 +5705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5726,48 +5736,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127169172</v>
+        <v>127209391</v>
       </c>
       <c r="B42" t="n">
-        <v>97320</v>
+        <v>57654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733225</v>
+        <v>733292</v>
       </c>
       <c r="R42" t="n">
-        <v>7102172</v>
+        <v>7102236</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5794,19 +5804,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,60 +5821,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R43" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,9 +5901,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,60 +5928,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R44" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5998,19 +6008,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,60 +6025,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127209432</v>
+        <v>127170226</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733313</v>
+        <v>733338</v>
       </c>
       <c r="R45" t="n">
-        <v>7102466</v>
+        <v>7102256</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,9 +6105,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6122,44 +6132,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209434</v>
+        <v>127209432</v>
       </c>
       <c r="B46" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6169,10 +6179,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733218</v>
+        <v>733313</v>
       </c>
       <c r="R46" t="n">
-        <v>7102512</v>
+        <v>7102466</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6231,32 +6241,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209431</v>
+        <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6266,10 +6276,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733392</v>
+        <v>733357</v>
       </c>
       <c r="R47" t="n">
-        <v>7102590</v>
+        <v>7102361</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6328,10 +6338,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127209411</v>
+        <v>127209434</v>
       </c>
       <c r="B48" t="n">
-        <v>80153</v>
+        <v>92616</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6339,21 +6349,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6363,10 +6373,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733357</v>
+        <v>733218</v>
       </c>
       <c r="R48" t="n">
-        <v>7102361</v>
+        <v>7102512</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6526,48 +6536,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127170226</v>
+        <v>127209431</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733338</v>
+        <v>733392</v>
       </c>
       <c r="R50" t="n">
-        <v>7102256</v>
+        <v>7102590</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6594,19 +6604,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,60 +6621,64 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B51" t="n">
-        <v>92615</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R51" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6701,9 +6705,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6718,64 +6732,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>92616</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R52" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6802,19 +6812,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,22 +6829,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R53" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6931,22 +6936,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B54" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,37 +6959,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R54" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209427</v>
+        <v>127209397</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733364</v>
+        <v>733264</v>
       </c>
       <c r="R55" t="n">
-        <v>7102666</v>
+        <v>7102152</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7123,18 +7123,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7153,10 +7147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209397</v>
+        <v>127209427</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7164,21 +7158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7188,10 +7182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733264</v>
+        <v>733364</v>
       </c>
       <c r="R56" t="n">
-        <v>7102152</v>
+        <v>7102666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7226,12 +7220,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>127171825</v>
       </c>
       <c r="B58" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7454,48 +7454,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127209420</v>
+        <v>127170235</v>
       </c>
       <c r="B59" t="n">
-        <v>58027</v>
+        <v>80117</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733290</v>
+        <v>733349</v>
       </c>
       <c r="R59" t="n">
-        <v>7102188</v>
+        <v>7102356</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7522,9 +7522,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7539,60 +7549,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127170235</v>
+        <v>127209420</v>
       </c>
       <c r="B60" t="n">
-        <v>80117</v>
+        <v>58027</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733349</v>
+        <v>733290</v>
       </c>
       <c r="R60" t="n">
-        <v>7102356</v>
+        <v>7102188</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7619,19 +7629,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7646,22 +7646,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172533</v>
+        <v>127169259</v>
       </c>
       <c r="B61" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7669,21 +7669,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733058</v>
+        <v>733273</v>
       </c>
       <c r="R61" t="n">
-        <v>7102382</v>
+        <v>7102237</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7768,7 +7768,7 @@
         <v>127168961</v>
       </c>
       <c r="B62" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127169259</v>
+        <v>127172533</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7883,21 +7883,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733273</v>
+        <v>733058</v>
       </c>
       <c r="R63" t="n">
-        <v>7102237</v>
+        <v>7102382</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7979,51 +7979,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127213086</v>
+        <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733292</v>
+        <v>733365</v>
       </c>
       <c r="R64" t="n">
-        <v>7102236</v>
+        <v>7102422</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8050,40 +8051,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127209409</v>
+        <v>127213086</v>
       </c>
       <c r="B65" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8091,34 +8101,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733357</v>
+        <v>733292</v>
       </c>
       <c r="R65" t="n">
-        <v>7102357</v>
+        <v>7102236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8159,6 +8172,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8177,52 +8191,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172025</v>
+        <v>127209409</v>
       </c>
       <c r="B66" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733365</v>
+        <v>733357</v>
       </c>
       <c r="R66" t="n">
-        <v>7102422</v>
+        <v>7102357</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8249,19 +8259,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,60 +8276,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127209388</v>
+        <v>127168323</v>
       </c>
       <c r="B67" t="n">
-        <v>79632</v>
+        <v>91291</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R67" t="n">
-        <v>7102463</v>
+        <v>7102111</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8356,9 +8356,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8373,57 +8383,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209399</v>
+        <v>127209442</v>
       </c>
       <c r="B68" t="n">
-        <v>57654</v>
+        <v>80152</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R68" t="n">
-        <v>7102084</v>
+        <v>7102353</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8464,6 +8477,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8482,48 +8496,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209442</v>
+        <v>127209399</v>
       </c>
       <c r="B69" t="n">
-        <v>80152</v>
+        <v>57654</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R69" t="n">
-        <v>7102353</v>
+        <v>7102084</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8564,7 +8575,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8583,48 +8593,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127168323</v>
+        <v>127209388</v>
       </c>
       <c r="B70" t="n">
-        <v>91290</v>
+        <v>79632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733192</v>
+        <v>733440</v>
       </c>
       <c r="R70" t="n">
-        <v>7102111</v>
+        <v>7102463</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8651,19 +8661,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127209403</v>
+        <v>127168623</v>
       </c>
       <c r="B73" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733380</v>
+        <v>733163</v>
       </c>
       <c r="R73" t="n">
-        <v>7102321</v>
+        <v>7102182</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,14 +8965,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8987,22 +8992,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209401</v>
+        <v>127209403</v>
       </c>
       <c r="B74" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,16 +9015,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9028,20 +9033,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733172</v>
+        <v>733380</v>
       </c>
       <c r="R74" t="n">
-        <v>7102001</v>
+        <v>7102321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9074,6 +9075,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9100,10 +9106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127168623</v>
+        <v>127209401</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9111,37 +9117,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733163</v>
+        <v>733172</v>
       </c>
       <c r="R75" t="n">
-        <v>7102182</v>
+        <v>7102001</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9168,19 +9178,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,63 +9195,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209440</v>
+        <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>80152</v>
+        <v>98443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733324</v>
+        <v>733268</v>
       </c>
       <c r="R76" t="n">
-        <v>7102432</v>
+        <v>7102284</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9278,57 +9275,66 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209429</v>
+        <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9337,16 +9343,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733361</v>
+        <v>733324</v>
       </c>
       <c r="R77" t="n">
-        <v>7102666</v>
+        <v>7102432</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9387,6 +9396,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9405,48 +9415,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127172437</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733268</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102284</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9473,19 +9483,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9500,12 +9500,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10116,45 +10116,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B85" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R85" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10191,7 +10199,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10200,6 +10208,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10218,53 +10227,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B86" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R86" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10301,7 +10302,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10310,7 +10311,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10842,10 +10842,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127352849</v>
+        <v>127352856</v>
       </c>
       <c r="B92" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10853,34 +10853,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>732858</v>
+        <v>732867</v>
       </c>
       <c r="R92" t="n">
-        <v>7102299</v>
+        <v>7102250</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10915,12 +10918,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10939,10 +10948,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127352856</v>
+        <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>82855</v>
+        <v>91322</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10950,37 +10959,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>732867</v>
+        <v>733015</v>
       </c>
       <c r="R93" t="n">
-        <v>7102250</v>
+        <v>7102294</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11015,18 +11021,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11045,10 +11045,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127352845</v>
+        <v>127352849</v>
       </c>
       <c r="B94" t="n">
-        <v>91321</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11056,21 +11056,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11080,10 +11080,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733015</v>
+        <v>732858</v>
       </c>
       <c r="R94" t="n">
-        <v>7102294</v>
+        <v>7102299</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11142,45 +11142,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127352822</v>
+        <v>127352829</v>
       </c>
       <c r="B95" t="n">
-        <v>91683</v>
+        <v>57657</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733131</v>
+        <v>732945</v>
       </c>
       <c r="R95" t="n">
-        <v>7102015</v>
+        <v>7102361</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11217,7 +11229,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11226,7 +11238,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11245,57 +11256,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127352829</v>
+        <v>127352822</v>
       </c>
       <c r="B96" t="n">
-        <v>57657</v>
+        <v>91684</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>732945</v>
+        <v>733131</v>
       </c>
       <c r="R96" t="n">
-        <v>7102361</v>
+        <v>7102015</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11332,7 +11331,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
+          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11341,6 +11340,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R98" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R99" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352846</v>
+        <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,21 +11661,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11685,10 +11685,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733141</v>
+        <v>733168</v>
       </c>
       <c r="R100" t="n">
-        <v>7102155</v>
+        <v>7102021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11747,10 +11747,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127352853</v>
+        <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11758,21 +11758,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733168</v>
+        <v>733141</v>
       </c>
       <c r="R101" t="n">
-        <v>7102021</v>
+        <v>7102155</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352831</v>
+        <v>127352830</v>
       </c>
       <c r="B104" t="n">
-        <v>91275</v>
+        <v>57817</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>733269</v>
+        <v>732870</v>
       </c>
       <c r="R104" t="n">
-        <v>7102176</v>
+        <v>7102344</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352857</v>
+        <v>127352831</v>
       </c>
       <c r="B105" t="n">
-        <v>75130</v>
+        <v>91276</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733195</v>
+        <v>733269</v>
       </c>
       <c r="R105" t="n">
-        <v>7102084</v>
+        <v>7102176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352830</v>
+        <v>127352857</v>
       </c>
       <c r="B106" t="n">
-        <v>57817</v>
+        <v>75130</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732870</v>
+        <v>733195</v>
       </c>
       <c r="R106" t="n">
-        <v>7102344</v>
+        <v>7102084</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12547,7 +12547,7 @@
         <v>127352825</v>
       </c>
       <c r="B109" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>91275</v>
+        <v>91276</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13441,32 +13441,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352847</v>
+        <v>127352823</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>91684</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13476,10 +13476,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733006</v>
+        <v>732915</v>
       </c>
       <c r="R118" t="n">
-        <v>7102273</v>
+        <v>7102363</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13514,12 +13514,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13538,32 +13544,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352823</v>
+        <v>127352854</v>
       </c>
       <c r="B119" t="n">
-        <v>91683</v>
+        <v>82855</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13573,10 +13579,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732915</v>
+        <v>732861</v>
       </c>
       <c r="R119" t="n">
-        <v>7102363</v>
+        <v>7102297</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13611,18 +13617,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13641,10 +13641,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352854</v>
+        <v>127352847</v>
       </c>
       <c r="B120" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13652,21 +13652,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13676,10 +13676,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>732861</v>
+        <v>733006</v>
       </c>
       <c r="R120" t="n">
-        <v>7102297</v>
+        <v>7102273</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B37" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R37" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,9 +5294,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5311,60 +5321,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B38" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R38" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5391,19 +5401,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127169172</v>
+        <v>127209408</v>
       </c>
       <c r="B40" t="n">
-        <v>97321</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733225</v>
+        <v>733340</v>
       </c>
       <c r="R40" t="n">
-        <v>7102172</v>
+        <v>7102327</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,19 +5595,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:41</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5622,22 +5617,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5645,16 +5640,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R41" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5705,11 +5700,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5736,48 +5726,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127209391</v>
+        <v>127169172</v>
       </c>
       <c r="B42" t="n">
-        <v>57654</v>
+        <v>97321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733292</v>
+        <v>733225</v>
       </c>
       <c r="R42" t="n">
-        <v>7102236</v>
+        <v>7102172</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5804,9 +5794,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,12 +5821,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6037,48 +6037,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127170226</v>
+        <v>127209432</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733338</v>
+        <v>733313</v>
       </c>
       <c r="R45" t="n">
-        <v>7102256</v>
+        <v>7102466</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,19 +6105,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6132,44 +6122,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209432</v>
+        <v>127209411</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6179,10 +6169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733313</v>
+        <v>733357</v>
       </c>
       <c r="R46" t="n">
-        <v>7102466</v>
+        <v>7102361</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6241,10 +6231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209411</v>
+        <v>127209434</v>
       </c>
       <c r="B47" t="n">
-        <v>80153</v>
+        <v>92616</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6252,21 +6242,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6276,10 +6266,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733357</v>
+        <v>733218</v>
       </c>
       <c r="R47" t="n">
-        <v>7102361</v>
+        <v>7102512</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6338,45 +6328,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127209434</v>
+        <v>127212703</v>
       </c>
       <c r="B48" t="n">
-        <v>92616</v>
+        <v>57654</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733218</v>
+        <v>733290</v>
       </c>
       <c r="R48" t="n">
-        <v>7102512</v>
+        <v>7102188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6435,10 +6429,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127212703</v>
+        <v>127209431</v>
       </c>
       <c r="B49" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6446,38 +6440,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733290</v>
+        <v>733392</v>
       </c>
       <c r="R49" t="n">
-        <v>7102188</v>
+        <v>7102590</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6536,48 +6526,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127209431</v>
+        <v>127170226</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733392</v>
+        <v>733338</v>
       </c>
       <c r="R50" t="n">
-        <v>7102590</v>
+        <v>7102256</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6604,9 +6594,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,12 +6621,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -9207,48 +9207,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127172437</v>
+        <v>127209440</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>80152</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733268</v>
+        <v>733324</v>
       </c>
       <c r="R76" t="n">
-        <v>7102284</v>
+        <v>7102432</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,66 +9278,57 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209440</v>
+        <v>127209429</v>
       </c>
       <c r="B77" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9343,19 +9337,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733324</v>
+        <v>733361</v>
       </c>
       <c r="R77" t="n">
-        <v>7102432</v>
+        <v>7102666</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9396,7 +9387,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9415,10 +9405,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127209405</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9426,34 +9416,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733153</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9486,6 +9480,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9512,52 +9511,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127209405</v>
+        <v>127172437</v>
       </c>
       <c r="B79" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733153</v>
+        <v>733268</v>
       </c>
       <c r="R79" t="n">
-        <v>7102629</v>
+        <v>7102284</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9584,14 +9579,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B98" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R98" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R99" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B100" t="n">
-        <v>82855</v>
+        <v>57654</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,34 +11661,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R100" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11844,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B102" t="n">
-        <v>57654</v>
+        <v>82855</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11855,42 +11863,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R102" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R37" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,19 +5294,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5321,60 +5311,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R38" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5401,9 +5391,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5833,48 +5833,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R43" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,19 +5901,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,60 +5918,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R44" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,9 +5998,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,60 +6025,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127209432</v>
+        <v>127170226</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733313</v>
+        <v>733338</v>
       </c>
       <c r="R45" t="n">
-        <v>7102466</v>
+        <v>7102256</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,9 +6105,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6122,44 +6132,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209411</v>
+        <v>127209432</v>
       </c>
       <c r="B46" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6169,10 +6179,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733357</v>
+        <v>733313</v>
       </c>
       <c r="R46" t="n">
-        <v>7102361</v>
+        <v>7102466</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6231,10 +6241,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209434</v>
+        <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>92616</v>
+        <v>80153</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6242,21 +6252,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6266,10 +6276,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733218</v>
+        <v>733357</v>
       </c>
       <c r="R47" t="n">
-        <v>7102512</v>
+        <v>7102361</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6328,49 +6338,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127212703</v>
+        <v>127209434</v>
       </c>
       <c r="B48" t="n">
-        <v>57654</v>
+        <v>92616</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733290</v>
+        <v>733218</v>
       </c>
       <c r="R48" t="n">
-        <v>7102188</v>
+        <v>7102512</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6526,48 +6532,52 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127170226</v>
+        <v>127212703</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>57654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733338</v>
+        <v>733290</v>
       </c>
       <c r="R50" t="n">
-        <v>7102256</v>
+        <v>7102188</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6594,19 +6604,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,64 +6621,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R51" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6705,19 +6701,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6732,60 +6718,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R52" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6812,9 +6802,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,22 +6829,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R53" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,19 +6909,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6936,22 +6931,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6959,37 +6954,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R54" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7016,14 +7011,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209427</v>
+        <v>127209393</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7158,21 +7158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733364</v>
+        <v>733129</v>
       </c>
       <c r="R56" t="n">
-        <v>7102666</v>
+        <v>7102002</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7220,18 +7220,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7250,10 +7244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127209393</v>
+        <v>127209427</v>
       </c>
       <c r="B57" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7261,21 +7255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7285,10 +7279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733129</v>
+        <v>733364</v>
       </c>
       <c r="R57" t="n">
-        <v>7102002</v>
+        <v>7102666</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7323,12 +7317,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7454,48 +7454,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127170235</v>
+        <v>127209420</v>
       </c>
       <c r="B59" t="n">
-        <v>80117</v>
+        <v>58027</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733349</v>
+        <v>733290</v>
       </c>
       <c r="R59" t="n">
-        <v>7102356</v>
+        <v>7102188</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7522,19 +7522,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7549,60 +7539,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127209420</v>
+        <v>127170235</v>
       </c>
       <c r="B60" t="n">
-        <v>58027</v>
+        <v>80117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733290</v>
+        <v>733349</v>
       </c>
       <c r="R60" t="n">
-        <v>7102188</v>
+        <v>7102356</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7629,9 +7619,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7646,22 +7646,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127169259</v>
+        <v>127172533</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7669,21 +7669,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733273</v>
+        <v>733058</v>
       </c>
       <c r="R61" t="n">
-        <v>7102237</v>
+        <v>7102382</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7872,10 +7872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172533</v>
+        <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7883,21 +7883,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733058</v>
+        <v>733273</v>
       </c>
       <c r="R63" t="n">
-        <v>7102382</v>
+        <v>7102237</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7979,52 +7979,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172025</v>
+        <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733365</v>
+        <v>733292</v>
       </c>
       <c r="R64" t="n">
-        <v>7102422</v>
+        <v>7102236</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8051,49 +8050,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127213086</v>
+        <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,37 +8091,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733292</v>
+        <v>733357</v>
       </c>
       <c r="R65" t="n">
-        <v>7102236</v>
+        <v>7102357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8172,7 +8159,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8191,48 +8177,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127209409</v>
+        <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733357</v>
+        <v>733365</v>
       </c>
       <c r="R66" t="n">
-        <v>7102357</v>
+        <v>7102422</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8259,9 +8249,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,60 +8276,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127168323</v>
+        <v>127209399</v>
       </c>
       <c r="B67" t="n">
-        <v>91291</v>
+        <v>57654</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>733192</v>
       </c>
       <c r="R67" t="n">
-        <v>7102111</v>
+        <v>7102084</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8356,19 +8356,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8383,12 +8373,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8496,10 +8486,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209399</v>
+        <v>127209388</v>
       </c>
       <c r="B69" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8507,21 +8497,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8531,10 +8521,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733192</v>
+        <v>733440</v>
       </c>
       <c r="R69" t="n">
-        <v>7102084</v>
+        <v>7102463</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8593,48 +8583,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127209388</v>
+        <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>91291</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7102463</v>
+        <v>7102111</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8661,9 +8651,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127168623</v>
+        <v>127209403</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733163</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7102182</v>
+        <v>7102321</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,19 +8965,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:18</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8992,22 +8987,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209403</v>
+        <v>127209401</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9015,16 +9010,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9033,16 +9028,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733380</v>
+        <v>733172</v>
       </c>
       <c r="R74" t="n">
-        <v>7102321</v>
+        <v>7102001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9075,11 +9074,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9106,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127209401</v>
+        <v>127168623</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9117,41 +9111,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733172</v>
+        <v>733163</v>
       </c>
       <c r="R75" t="n">
-        <v>7102001</v>
+        <v>7102182</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9178,9 +9168,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,49 +9195,50 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209440</v>
+        <v>127209405</v>
       </c>
       <c r="B76" t="n">
-        <v>80152</v>
+        <v>57657</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9245,10 +9246,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733324</v>
+        <v>733153</v>
       </c>
       <c r="R76" t="n">
-        <v>7102432</v>
+        <v>7102629</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9283,13 +9284,17 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9308,27 +9313,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209429</v>
+        <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9337,16 +9342,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733361</v>
+        <v>733324</v>
       </c>
       <c r="R77" t="n">
-        <v>7102666</v>
+        <v>7102432</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9387,6 +9395,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9405,10 +9414,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209405</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9416,38 +9425,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733153</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102629</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9480,11 +9485,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10116,53 +10116,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B85" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R85" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10199,7 +10191,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10208,7 +10200,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10227,45 +10218,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R86" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10302,7 +10301,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10311,6 +10310,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352830</v>
+        <v>127352857</v>
       </c>
       <c r="B104" t="n">
-        <v>57817</v>
+        <v>75130</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>732870</v>
+        <v>733195</v>
       </c>
       <c r="R104" t="n">
-        <v>7102344</v>
+        <v>7102084</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352857</v>
+        <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>75130</v>
+        <v>57817</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>733195</v>
+        <v>732870</v>
       </c>
       <c r="R106" t="n">
-        <v>7102084</v>
+        <v>7102344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12447,10 +12447,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127352848</v>
+        <v>127352825</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12458,21 +12458,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732920</v>
+        <v>733193</v>
       </c>
       <c r="R108" t="n">
-        <v>7102396</v>
+        <v>7102147</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12544,10 +12544,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127352825</v>
+        <v>127352848</v>
       </c>
       <c r="B109" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12555,21 +12555,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>733193</v>
+        <v>732920</v>
       </c>
       <c r="R109" t="n">
-        <v>7102147</v>
+        <v>7102396</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13029,10 +13029,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127352827</v>
+        <v>127352834</v>
       </c>
       <c r="B114" t="n">
-        <v>91326</v>
+        <v>57654</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13040,34 +13040,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732905</v>
+        <v>732868</v>
       </c>
       <c r="R114" t="n">
-        <v>7102362</v>
+        <v>7102325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13126,10 +13134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127352834</v>
+        <v>127352827</v>
       </c>
       <c r="B115" t="n">
-        <v>57654</v>
+        <v>91326</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13137,42 +13145,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732868</v>
+        <v>732905</v>
       </c>
       <c r="R115" t="n">
-        <v>7102325</v>
+        <v>7102362</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127209408</v>
+        <v>127169172</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>97321</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733340</v>
+        <v>733225</v>
       </c>
       <c r="R40" t="n">
-        <v>7102327</v>
+        <v>7102172</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,14 +5595,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5617,22 +5622,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209391</v>
+        <v>127209408</v>
       </c>
       <c r="B41" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5640,16 +5645,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733292</v>
+        <v>733340</v>
       </c>
       <c r="R41" t="n">
-        <v>7102236</v>
+        <v>7102327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5700,6 +5705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5726,48 +5736,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127169172</v>
+        <v>127209391</v>
       </c>
       <c r="B42" t="n">
-        <v>97321</v>
+        <v>57654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733225</v>
+        <v>733292</v>
       </c>
       <c r="R42" t="n">
-        <v>7102172</v>
+        <v>7102236</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5794,19 +5804,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,12 +5821,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6037,48 +6037,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127170226</v>
+        <v>127212703</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>57654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733338</v>
+        <v>733290</v>
       </c>
       <c r="R45" t="n">
-        <v>7102256</v>
+        <v>7102188</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,19 +6109,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6132,12 +6126,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6532,52 +6526,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127212703</v>
+        <v>127170226</v>
       </c>
       <c r="B50" t="n">
-        <v>57654</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733290</v>
+        <v>733338</v>
       </c>
       <c r="R50" t="n">
-        <v>7102188</v>
+        <v>7102256</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6604,9 +6594,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,60 +6621,64 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B51" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R51" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6701,9 +6705,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6718,64 +6732,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R52" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6802,19 +6812,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,12 +6829,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7979,51 +7979,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127213086</v>
+        <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733292</v>
+        <v>733365</v>
       </c>
       <c r="R64" t="n">
-        <v>7102236</v>
+        <v>7102422</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8050,40 +8051,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127209409</v>
+        <v>127213086</v>
       </c>
       <c r="B65" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8091,34 +8101,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733357</v>
+        <v>733292</v>
       </c>
       <c r="R65" t="n">
-        <v>7102357</v>
+        <v>7102236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8159,6 +8172,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8177,52 +8191,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172025</v>
+        <v>127209409</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733365</v>
+        <v>733357</v>
       </c>
       <c r="R66" t="n">
-        <v>7102422</v>
+        <v>7102357</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8249,19 +8259,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,57 +8276,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127209399</v>
+        <v>127209442</v>
       </c>
       <c r="B67" t="n">
-        <v>57654</v>
+        <v>80152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R67" t="n">
-        <v>7102084</v>
+        <v>7102353</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8367,6 +8370,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8385,48 +8389,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209442</v>
+        <v>127209388</v>
       </c>
       <c r="B68" t="n">
-        <v>80152</v>
+        <v>79632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733349</v>
+        <v>733440</v>
       </c>
       <c r="R68" t="n">
-        <v>7102353</v>
+        <v>7102463</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8467,7 +8468,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8486,48 +8486,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209388</v>
+        <v>127168323</v>
       </c>
       <c r="B69" t="n">
-        <v>79632</v>
+        <v>91291</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R69" t="n">
-        <v>7102463</v>
+        <v>7102111</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8554,9 +8554,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8571,60 +8581,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127168323</v>
+        <v>127209399</v>
       </c>
       <c r="B70" t="n">
-        <v>91291</v>
+        <v>57654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
         <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7102111</v>
+        <v>7102084</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8651,19 +8661,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127209403</v>
+        <v>127168623</v>
       </c>
       <c r="B73" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733380</v>
+        <v>733163</v>
       </c>
       <c r="R73" t="n">
-        <v>7102321</v>
+        <v>7102182</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,14 +8965,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8987,22 +8992,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209401</v>
+        <v>127209403</v>
       </c>
       <c r="B74" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,16 +9015,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9028,20 +9033,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733172</v>
+        <v>733380</v>
       </c>
       <c r="R74" t="n">
-        <v>7102001</v>
+        <v>7102321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9074,6 +9075,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9100,10 +9106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127168623</v>
+        <v>127209401</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9111,37 +9117,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733163</v>
+        <v>733172</v>
       </c>
       <c r="R75" t="n">
-        <v>7102182</v>
+        <v>7102001</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9168,19 +9178,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,12 +9195,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>57654</v>
+        <v>82855</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,42 +11661,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R100" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11755,10 +11747,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127352846</v>
+        <v>127352833</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11766,34 +11758,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733141</v>
+        <v>733067</v>
       </c>
       <c r="R101" t="n">
-        <v>7102155</v>
+        <v>7102180</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11852,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352853</v>
+        <v>127352846</v>
       </c>
       <c r="B102" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,21 +11863,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733168</v>
+        <v>733141</v>
       </c>
       <c r="R102" t="n">
-        <v>7102021</v>
+        <v>7102155</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352835</v>
+        <v>127352854</v>
       </c>
       <c r="B116" t="n">
-        <v>57654</v>
+        <v>82855</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13242,42 +13242,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>733013</v>
+        <v>732861</v>
       </c>
       <c r="R116" t="n">
-        <v>7102291</v>
+        <v>7102297</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13336,53 +13328,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352836</v>
+        <v>127352823</v>
       </c>
       <c r="B117" t="n">
-        <v>57654</v>
+        <v>91684</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732906</v>
+        <v>732915</v>
       </c>
       <c r="R117" t="n">
-        <v>7102369</v>
+        <v>7102363</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13417,12 +13401,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13441,45 +13431,53 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352823</v>
+        <v>127352835</v>
       </c>
       <c r="B118" t="n">
-        <v>91684</v>
+        <v>57654</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732915</v>
+        <v>733013</v>
       </c>
       <c r="R118" t="n">
-        <v>7102363</v>
+        <v>7102291</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13514,18 +13512,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13544,10 +13536,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352854</v>
+        <v>127352836</v>
       </c>
       <c r="B119" t="n">
-        <v>82855</v>
+        <v>57654</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13555,34 +13547,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732861</v>
+        <v>732906</v>
       </c>
       <c r="R119" t="n">
-        <v>7102297</v>
+        <v>7102369</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -6841,10 +6841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R53" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6931,22 +6936,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B54" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,37 +6959,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R54" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7979,52 +7979,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172025</v>
+        <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733365</v>
+        <v>733292</v>
       </c>
       <c r="R64" t="n">
-        <v>7102422</v>
+        <v>7102236</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8051,49 +8050,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127213086</v>
+        <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,37 +8091,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733292</v>
+        <v>733357</v>
       </c>
       <c r="R65" t="n">
-        <v>7102236</v>
+        <v>7102357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8172,7 +8159,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8191,48 +8177,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127209409</v>
+        <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733357</v>
+        <v>733365</v>
       </c>
       <c r="R66" t="n">
-        <v>7102357</v>
+        <v>7102422</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8259,9 +8249,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,12 +8276,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -10116,45 +10116,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B85" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R85" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10191,7 +10199,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10200,6 +10208,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10218,53 +10227,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B86" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R86" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10301,7 +10302,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10310,7 +10311,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R98" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R99" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B100" t="n">
-        <v>82855</v>
+        <v>57654</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,34 +11661,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R100" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11747,10 +11755,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127352833</v>
+        <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11758,42 +11766,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733067</v>
+        <v>733141</v>
       </c>
       <c r="R101" t="n">
-        <v>7102180</v>
+        <v>7102155</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11852,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352846</v>
+        <v>127352853</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,21 +11863,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733141</v>
+        <v>733168</v>
       </c>
       <c r="R102" t="n">
-        <v>7102155</v>
+        <v>7102021</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352854</v>
+        <v>127352835</v>
       </c>
       <c r="B116" t="n">
-        <v>82855</v>
+        <v>57654</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13242,34 +13242,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732861</v>
+        <v>733013</v>
       </c>
       <c r="R116" t="n">
-        <v>7102297</v>
+        <v>7102291</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13328,45 +13336,53 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352823</v>
+        <v>127352836</v>
       </c>
       <c r="B117" t="n">
-        <v>91684</v>
+        <v>57654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732915</v>
+        <v>732906</v>
       </c>
       <c r="R117" t="n">
-        <v>7102363</v>
+        <v>7102369</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13401,18 +13417,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13431,53 +13441,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352835</v>
+        <v>127352823</v>
       </c>
       <c r="B118" t="n">
-        <v>57654</v>
+        <v>91684</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733013</v>
+        <v>732915</v>
       </c>
       <c r="R118" t="n">
-        <v>7102291</v>
+        <v>7102363</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13512,12 +13514,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13536,10 +13544,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352836</v>
+        <v>127352854</v>
       </c>
       <c r="B119" t="n">
-        <v>57654</v>
+        <v>82855</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13547,42 +13555,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732906</v>
+        <v>732861</v>
       </c>
       <c r="R119" t="n">
-        <v>7102369</v>
+        <v>7102297</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5229,7 +5229,7 @@
         <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>127209396</v>
       </c>
       <c r="B39" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127169172</v>
+        <v>127209408</v>
       </c>
       <c r="B40" t="n">
-        <v>97321</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733225</v>
+        <v>733340</v>
       </c>
       <c r="R40" t="n">
-        <v>7102172</v>
+        <v>7102327</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,19 +5595,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:41</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5622,22 +5617,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57658</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5645,16 +5640,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R41" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5705,11 +5700,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5736,48 +5726,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127209391</v>
+        <v>127169172</v>
       </c>
       <c r="B42" t="n">
-        <v>57654</v>
+        <v>97325</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733292</v>
+        <v>733225</v>
       </c>
       <c r="R42" t="n">
-        <v>7102236</v>
+        <v>7102172</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5804,9 +5794,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,60 +5821,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R43" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,9 +5901,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,60 +5928,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R44" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5998,19 +6008,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,22 +6025,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127212703</v>
+        <v>127209432</v>
       </c>
       <c r="B45" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6048,38 +6048,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733290</v>
+        <v>733313</v>
       </c>
       <c r="R45" t="n">
-        <v>7102188</v>
+        <v>7102466</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6138,10 +6134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209432</v>
+        <v>127209431</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6173,10 +6169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733313</v>
+        <v>733392</v>
       </c>
       <c r="R46" t="n">
-        <v>7102466</v>
+        <v>7102590</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6238,7 +6234,7 @@
         <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6332,45 +6328,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127209434</v>
+        <v>127212703</v>
       </c>
       <c r="B48" t="n">
-        <v>92616</v>
+        <v>57658</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733218</v>
+        <v>733290</v>
       </c>
       <c r="R48" t="n">
-        <v>7102512</v>
+        <v>7102188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6429,32 +6429,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127209431</v>
+        <v>127209434</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733392</v>
+        <v>733218</v>
       </c>
       <c r="R49" t="n">
-        <v>7102590</v>
+        <v>7102512</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6529,7 +6529,7 @@
         <v>127170226</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>127171706</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>127209436</v>
       </c>
       <c r="B52" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57817</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R53" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,19 +6909,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6936,22 +6931,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>57821</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6959,37 +6954,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R54" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7016,14 +7011,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209397</v>
+        <v>127209393</v>
       </c>
       <c r="B55" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733264</v>
+        <v>733129</v>
       </c>
       <c r="R55" t="n">
-        <v>7102152</v>
+        <v>7102002</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209393</v>
+        <v>127209397</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733129</v>
+        <v>733264</v>
       </c>
       <c r="R56" t="n">
-        <v>7102002</v>
+        <v>7102152</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7247,7 +7247,7 @@
         <v>127209427</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>127171825</v>
       </c>
       <c r="B58" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>127209420</v>
       </c>
       <c r="B59" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>127170235</v>
       </c>
       <c r="B60" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>127172533</v>
       </c>
       <c r="B61" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>127168961</v>
       </c>
       <c r="B62" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8288,10 +8288,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127209442</v>
+        <v>127168323</v>
       </c>
       <c r="B67" t="n">
-        <v>80152</v>
+        <v>91295</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8299,40 +8299,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R67" t="n">
-        <v>7102353</v>
+        <v>7102111</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8359,40 +8356,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209388</v>
+        <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>79632</v>
+        <v>57658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8400,21 +8406,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8424,10 +8430,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R68" t="n">
-        <v>7102463</v>
+        <v>7102084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8486,10 +8492,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127168323</v>
+        <v>127209442</v>
       </c>
       <c r="B69" t="n">
-        <v>91291</v>
+        <v>80156</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8497,37 +8503,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R69" t="n">
-        <v>7102111</v>
+        <v>7102353</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8554,49 +8563,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127209399</v>
+        <v>127209388</v>
       </c>
       <c r="B70" t="n">
-        <v>57654</v>
+        <v>79636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8604,21 +8604,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733192</v>
+        <v>733440</v>
       </c>
       <c r="R70" t="n">
-        <v>7102084</v>
+        <v>7102463</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>127209444</v>
       </c>
       <c r="B72" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127168623</v>
+        <v>127209403</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733163</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7102182</v>
+        <v>7102321</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,19 +8965,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:18</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8992,22 +8987,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209403</v>
+        <v>127209401</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>57658</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9015,16 +9010,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9033,16 +9028,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733380</v>
+        <v>733172</v>
       </c>
       <c r="R74" t="n">
-        <v>7102321</v>
+        <v>7102001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9075,11 +9074,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9106,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127209401</v>
+        <v>127168623</v>
       </c>
       <c r="B75" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9117,41 +9111,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733172</v>
+        <v>733163</v>
       </c>
       <c r="R75" t="n">
-        <v>7102001</v>
+        <v>7102182</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9178,9 +9168,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,64 +9195,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209405</v>
+        <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733153</v>
+        <v>733268</v>
       </c>
       <c r="R76" t="n">
-        <v>7102629</v>
+        <v>7102284</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9279,14 +9275,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9301,12 +9302,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9316,7 +9317,7 @@
         <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9417,7 +9418,7 @@
         <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9511,48 +9512,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127172437</v>
+        <v>127209405</v>
       </c>
       <c r="B79" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733268</v>
+        <v>733153</v>
       </c>
       <c r="R79" t="n">
-        <v>7102284</v>
+        <v>7102629</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9579,19 +9584,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>127265350</v>
       </c>
       <c r="B83" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>127265357</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,53 +10116,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B85" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R85" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10199,7 +10191,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10208,7 +10200,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10227,45 +10218,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R86" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10302,7 +10301,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10311,6 +10310,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>127265351</v>
       </c>
       <c r="B87" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>127265358</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>127265349</v>
       </c>
       <c r="B89" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>127265353</v>
       </c>
       <c r="B90" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>127352850</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>127352856</v>
       </c>
       <c r="B92" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>127352849</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>127352829</v>
       </c>
       <c r="B95" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>127352822</v>
       </c>
       <c r="B96" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>127352841</v>
       </c>
       <c r="B97" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>57654</v>
+        <v>82859</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,42 +11661,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R100" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11758,7 +11750,7 @@
         <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11852,10 +11844,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B102" t="n">
-        <v>82855</v>
+        <v>57658</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,34 +11855,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R102" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352857</v>
+        <v>127352831</v>
       </c>
       <c r="B104" t="n">
-        <v>75130</v>
+        <v>91280</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>733195</v>
+        <v>733269</v>
       </c>
       <c r="R104" t="n">
-        <v>7102084</v>
+        <v>7102176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352831</v>
+        <v>127352857</v>
       </c>
       <c r="B105" t="n">
-        <v>91276</v>
+        <v>75134</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733269</v>
+        <v>733195</v>
       </c>
       <c r="R105" t="n">
-        <v>7102176</v>
+        <v>7102084</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
         <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>127352837</v>
       </c>
       <c r="B107" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>127352825</v>
       </c>
       <c r="B108" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>127352848</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>127352852</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>91276</v>
+        <v>91280</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>127352844</v>
       </c>
       <c r="B112" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>127352855</v>
       </c>
       <c r="B113" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13029,10 +13029,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127352834</v>
+        <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>57654</v>
+        <v>91330</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13040,42 +13040,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732868</v>
+        <v>732905</v>
       </c>
       <c r="R114" t="n">
-        <v>7102325</v>
+        <v>7102362</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13134,10 +13126,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127352827</v>
+        <v>127352834</v>
       </c>
       <c r="B115" t="n">
-        <v>91326</v>
+        <v>57658</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13145,34 +13137,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732905</v>
+        <v>732868</v>
       </c>
       <c r="R115" t="n">
-        <v>7102362</v>
+        <v>7102325</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13234,7 +13234,7 @@
         <v>127352835</v>
       </c>
       <c r="B116" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>127352836</v>
       </c>
       <c r="B117" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13441,32 +13441,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352823</v>
+        <v>127352854</v>
       </c>
       <c r="B118" t="n">
-        <v>91684</v>
+        <v>82859</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13476,10 +13476,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732915</v>
+        <v>732861</v>
       </c>
       <c r="R118" t="n">
-        <v>7102363</v>
+        <v>7102297</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13514,18 +13514,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13544,32 +13538,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352854</v>
+        <v>127352823</v>
       </c>
       <c r="B119" t="n">
-        <v>82855</v>
+        <v>91688</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13579,10 +13573,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732861</v>
+        <v>732915</v>
       </c>
       <c r="R119" t="n">
-        <v>7102297</v>
+        <v>7102363</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13617,12 +13611,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>127352847</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5527,10 +5527,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R40" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5598,11 +5598,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5629,10 +5624,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209391</v>
+        <v>127209408</v>
       </c>
       <c r="B41" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5640,16 +5635,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5664,10 +5659,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733292</v>
+        <v>733340</v>
       </c>
       <c r="R41" t="n">
-        <v>7102236</v>
+        <v>7102327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5700,6 +5695,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5833,48 +5833,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R43" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,19 +5901,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,60 +5918,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R44" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,9 +5998,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,19 +6025,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127209432</v>
+        <v>127209431</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733313</v>
+        <v>733392</v>
       </c>
       <c r="R45" t="n">
-        <v>7102466</v>
+        <v>7102590</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6134,48 +6134,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209431</v>
+        <v>127170226</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733392</v>
+        <v>733338</v>
       </c>
       <c r="R46" t="n">
-        <v>7102590</v>
+        <v>7102256</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6202,9 +6202,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6219,44 +6229,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209411</v>
+        <v>127209432</v>
       </c>
       <c r="B47" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6266,10 +6276,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733357</v>
+        <v>733313</v>
       </c>
       <c r="R47" t="n">
-        <v>7102361</v>
+        <v>7102466</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6328,49 +6338,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127212703</v>
+        <v>127209411</v>
       </c>
       <c r="B48" t="n">
-        <v>57658</v>
+        <v>80157</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733290</v>
+        <v>733357</v>
       </c>
       <c r="R48" t="n">
-        <v>7102188</v>
+        <v>7102361</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6526,48 +6532,52 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127170226</v>
+        <v>127212703</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>57658</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733338</v>
+        <v>733290</v>
       </c>
       <c r="R50" t="n">
-        <v>7102256</v>
+        <v>7102188</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6594,19 +6604,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,64 +6621,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R51" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6705,19 +6701,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6732,60 +6718,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R52" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6812,9 +6802,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,12 +6829,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7050,7 +7050,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209393</v>
+        <v>127209397</v>
       </c>
       <c r="B55" t="n">
         <v>57658</v>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733129</v>
+        <v>733264</v>
       </c>
       <c r="R55" t="n">
-        <v>7102002</v>
+        <v>7102152</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209397</v>
+        <v>127209427</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7158,21 +7158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733264</v>
+        <v>733364</v>
       </c>
       <c r="R56" t="n">
-        <v>7102152</v>
+        <v>7102666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7220,12 +7220,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7244,10 +7250,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127209427</v>
+        <v>127209393</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7255,21 +7261,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7279,10 +7285,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733364</v>
+        <v>733129</v>
       </c>
       <c r="R57" t="n">
-        <v>7102666</v>
+        <v>7102002</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7317,18 +7323,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7979,51 +7979,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127213086</v>
+        <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733292</v>
+        <v>733365</v>
       </c>
       <c r="R64" t="n">
-        <v>7102236</v>
+        <v>7102422</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8050,40 +8051,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127209409</v>
+        <v>127213086</v>
       </c>
       <c r="B65" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8091,34 +8101,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733357</v>
+        <v>733292</v>
       </c>
       <c r="R65" t="n">
-        <v>7102357</v>
+        <v>7102236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8159,6 +8172,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8177,52 +8191,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172025</v>
+        <v>127209409</v>
       </c>
       <c r="B66" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733365</v>
+        <v>733357</v>
       </c>
       <c r="R66" t="n">
-        <v>7102422</v>
+        <v>7102357</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8249,19 +8259,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,12 +8276,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8395,45 +8395,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209399</v>
+        <v>127209442</v>
       </c>
       <c r="B68" t="n">
-        <v>57658</v>
+        <v>80156</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R68" t="n">
-        <v>7102084</v>
+        <v>7102353</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8474,6 +8477,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8492,48 +8496,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209442</v>
+        <v>127209399</v>
       </c>
       <c r="B69" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R69" t="n">
-        <v>7102353</v>
+        <v>7102084</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8574,7 +8575,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127209403</v>
+        <v>127168623</v>
       </c>
       <c r="B73" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733380</v>
+        <v>733163</v>
       </c>
       <c r="R73" t="n">
-        <v>7102321</v>
+        <v>7102182</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,14 +8965,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8987,22 +8992,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209401</v>
+        <v>127209403</v>
       </c>
       <c r="B74" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,16 +9015,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9028,20 +9033,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733172</v>
+        <v>733380</v>
       </c>
       <c r="R74" t="n">
-        <v>7102001</v>
+        <v>7102321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9074,6 +9075,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9100,10 +9106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127168623</v>
+        <v>127209401</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9111,37 +9117,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733163</v>
+        <v>733172</v>
       </c>
       <c r="R75" t="n">
-        <v>7102182</v>
+        <v>7102001</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9168,19 +9178,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,60 +9195,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127172437</v>
+        <v>127209405</v>
       </c>
       <c r="B76" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733268</v>
+        <v>733153</v>
       </c>
       <c r="R76" t="n">
-        <v>7102284</v>
+        <v>7102629</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,19 +9279,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9302,12 +9301,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9512,52 +9511,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127209405</v>
+        <v>127172437</v>
       </c>
       <c r="B79" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733153</v>
+        <v>733268</v>
       </c>
       <c r="R79" t="n">
-        <v>7102629</v>
+        <v>7102284</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9584,14 +9579,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10842,10 +10842,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127352856</v>
+        <v>127352845</v>
       </c>
       <c r="B92" t="n">
-        <v>82859</v>
+        <v>91326</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10853,37 +10853,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>732867</v>
+        <v>733015</v>
       </c>
       <c r="R92" t="n">
-        <v>7102250</v>
+        <v>7102294</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10918,18 +10915,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10948,10 +10939,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127352845</v>
+        <v>127352849</v>
       </c>
       <c r="B93" t="n">
-        <v>91326</v>
+        <v>79018</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10959,21 +10950,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10983,10 +10974,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733015</v>
+        <v>732858</v>
       </c>
       <c r="R93" t="n">
-        <v>7102294</v>
+        <v>7102299</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11045,10 +11036,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127352849</v>
+        <v>127352856</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11056,34 +11047,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>732858</v>
+        <v>732867</v>
       </c>
       <c r="R94" t="n">
-        <v>7102299</v>
+        <v>7102250</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11118,12 +11112,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B100" t="n">
-        <v>82859</v>
+        <v>57658</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,34 +11661,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R100" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11844,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B102" t="n">
-        <v>57658</v>
+        <v>82859</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11855,42 +11863,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R102" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352831</v>
+        <v>127352830</v>
       </c>
       <c r="B104" t="n">
-        <v>91280</v>
+        <v>57821</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>733269</v>
+        <v>732870</v>
       </c>
       <c r="R104" t="n">
-        <v>7102176</v>
+        <v>7102344</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352857</v>
+        <v>127352831</v>
       </c>
       <c r="B105" t="n">
-        <v>75134</v>
+        <v>91280</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733195</v>
+        <v>733269</v>
       </c>
       <c r="R105" t="n">
-        <v>7102084</v>
+        <v>7102176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352830</v>
+        <v>127352857</v>
       </c>
       <c r="B106" t="n">
-        <v>57821</v>
+        <v>75134</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732870</v>
+        <v>733195</v>
       </c>
       <c r="R106" t="n">
-        <v>7102344</v>
+        <v>7102084</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13029,10 +13029,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127352827</v>
+        <v>127352834</v>
       </c>
       <c r="B114" t="n">
-        <v>91330</v>
+        <v>57658</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13040,34 +13040,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732905</v>
+        <v>732868</v>
       </c>
       <c r="R114" t="n">
-        <v>7102362</v>
+        <v>7102325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13126,10 +13134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127352834</v>
+        <v>127352827</v>
       </c>
       <c r="B115" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13137,42 +13145,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732868</v>
+        <v>732905</v>
       </c>
       <c r="R115" t="n">
-        <v>7102325</v>
+        <v>7102362</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13231,53 +13231,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352835</v>
+        <v>127352823</v>
       </c>
       <c r="B116" t="n">
-        <v>57658</v>
+        <v>91688</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>733013</v>
+        <v>732915</v>
       </c>
       <c r="R116" t="n">
-        <v>7102291</v>
+        <v>7102363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13312,12 +13304,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13336,10 +13334,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352836</v>
+        <v>127352854</v>
       </c>
       <c r="B117" t="n">
-        <v>57658</v>
+        <v>82859</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13347,42 +13345,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732906</v>
+        <v>732861</v>
       </c>
       <c r="R117" t="n">
-        <v>7102369</v>
+        <v>7102297</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13441,10 +13431,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352854</v>
+        <v>127352847</v>
       </c>
       <c r="B118" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13452,21 +13442,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13476,10 +13466,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732861</v>
+        <v>733006</v>
       </c>
       <c r="R118" t="n">
-        <v>7102297</v>
+        <v>7102273</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13538,45 +13528,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352823</v>
+        <v>127352836</v>
       </c>
       <c r="B119" t="n">
-        <v>91688</v>
+        <v>57658</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732915</v>
+        <v>732906</v>
       </c>
       <c r="R119" t="n">
-        <v>7102363</v>
+        <v>7102369</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13611,18 +13609,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13641,10 +13633,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352847</v>
+        <v>127352835</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13652,34 +13644,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>733006</v>
+        <v>733013</v>
       </c>
       <c r="R120" t="n">
-        <v>7102273</v>
+        <v>7102291</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -8288,10 +8288,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127168323</v>
+        <v>127209442</v>
       </c>
       <c r="B67" t="n">
-        <v>91295</v>
+        <v>80156</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8299,37 +8299,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R67" t="n">
-        <v>7102111</v>
+        <v>7102353</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8356,87 +8359,75 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209442</v>
+        <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R68" t="n">
-        <v>7102353</v>
+        <v>7102084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8477,7 +8468,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8496,10 +8486,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209399</v>
+        <v>127209388</v>
       </c>
       <c r="B69" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8507,21 +8497,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8531,10 +8521,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733192</v>
+        <v>733440</v>
       </c>
       <c r="R69" t="n">
-        <v>7102084</v>
+        <v>7102463</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8593,48 +8583,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127209388</v>
+        <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>79636</v>
+        <v>91295</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7102463</v>
+        <v>7102111</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8661,9 +8651,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9207,38 +9207,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209405</v>
+        <v>127209440</v>
       </c>
       <c r="B76" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9246,10 +9245,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733153</v>
+        <v>733324</v>
       </c>
       <c r="R76" t="n">
-        <v>7102629</v>
+        <v>7102432</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9284,17 +9283,13 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9313,27 +9308,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209440</v>
+        <v>127209429</v>
       </c>
       <c r="B77" t="n">
-        <v>80156</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9342,19 +9337,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733324</v>
+        <v>733361</v>
       </c>
       <c r="R77" t="n">
-        <v>7102432</v>
+        <v>7102666</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9395,7 +9387,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9414,10 +9405,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127209405</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,34 +9416,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733153</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9485,6 +9480,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B98" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R98" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R99" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>57658</v>
+        <v>82859</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,42 +11661,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R100" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11852,10 +11844,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B102" t="n">
-        <v>82859</v>
+        <v>57658</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,34 +11855,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R102" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352823</v>
+        <v>127352847</v>
       </c>
       <c r="B116" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732915</v>
+        <v>733006</v>
       </c>
       <c r="R116" t="n">
-        <v>7102363</v>
+        <v>7102273</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,18 +13304,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13334,32 +13328,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352854</v>
+        <v>127352823</v>
       </c>
       <c r="B117" t="n">
-        <v>82859</v>
+        <v>91688</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13369,10 +13363,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732861</v>
+        <v>732915</v>
       </c>
       <c r="R117" t="n">
-        <v>7102297</v>
+        <v>7102363</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13407,12 +13401,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13431,10 +13431,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352847</v>
+        <v>127352854</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13442,21 +13442,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13466,10 +13466,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733006</v>
+        <v>732861</v>
       </c>
       <c r="R118" t="n">
-        <v>7102273</v>
+        <v>7102297</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5833,48 +5833,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R43" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,9 +5901,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,60 +5928,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R44" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5998,19 +6008,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6633,48 +6633,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B51" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R51" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6701,9 +6705,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6718,64 +6732,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R52" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6802,19 +6812,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,12 +6829,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -9207,37 +9207,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209440</v>
+        <v>127209405</v>
       </c>
       <c r="B76" t="n">
-        <v>80156</v>
+        <v>57661</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9245,10 +9246,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733324</v>
+        <v>733153</v>
       </c>
       <c r="R76" t="n">
-        <v>7102432</v>
+        <v>7102629</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9283,13 +9284,17 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9308,27 +9313,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209429</v>
+        <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9337,16 +9342,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733361</v>
+        <v>733324</v>
       </c>
       <c r="R77" t="n">
-        <v>7102666</v>
+        <v>7102432</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9387,6 +9395,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9405,10 +9414,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209405</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9416,38 +9425,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733153</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102629</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9480,11 +9485,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11142,57 +11142,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127352829</v>
+        <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>57661</v>
+        <v>91688</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>732945</v>
+        <v>733131</v>
       </c>
       <c r="R95" t="n">
-        <v>7102361</v>
+        <v>7102015</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11229,7 +11217,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
+          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11238,6 +11226,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11256,45 +11245,57 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127352822</v>
+        <v>127352829</v>
       </c>
       <c r="B96" t="n">
-        <v>91688</v>
+        <v>57661</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733131</v>
+        <v>732945</v>
       </c>
       <c r="R96" t="n">
-        <v>7102015</v>
+        <v>7102361</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11331,7 +11332,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11340,7 +11341,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R98" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R99" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B100" t="n">
-        <v>82859</v>
+        <v>57658</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,34 +11661,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R100" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11844,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B102" t="n">
-        <v>57658</v>
+        <v>82859</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11855,42 +11863,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R102" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13029,10 +13029,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127352834</v>
+        <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>57658</v>
+        <v>91330</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13040,42 +13040,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732868</v>
+        <v>732905</v>
       </c>
       <c r="R114" t="n">
-        <v>7102325</v>
+        <v>7102362</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13134,10 +13126,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127352827</v>
+        <v>127352834</v>
       </c>
       <c r="B115" t="n">
-        <v>91330</v>
+        <v>57658</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13145,34 +13137,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732905</v>
+        <v>732868</v>
       </c>
       <c r="R115" t="n">
-        <v>7102362</v>
+        <v>7102325</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352847</v>
+        <v>127352823</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>91688</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>733006</v>
+        <v>732915</v>
       </c>
       <c r="R116" t="n">
-        <v>7102273</v>
+        <v>7102363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,12 +13304,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13328,32 +13334,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352823</v>
+        <v>127352854</v>
       </c>
       <c r="B117" t="n">
-        <v>91688</v>
+        <v>82859</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13363,10 +13369,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732915</v>
+        <v>732861</v>
       </c>
       <c r="R117" t="n">
-        <v>7102363</v>
+        <v>7102297</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13401,18 +13407,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13431,10 +13431,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352854</v>
+        <v>127352847</v>
       </c>
       <c r="B118" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13442,21 +13442,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13466,10 +13466,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732861</v>
+        <v>733006</v>
       </c>
       <c r="R118" t="n">
-        <v>7102297</v>
+        <v>7102273</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R37" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,9 +5294,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5311,60 +5321,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B38" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R38" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5391,19 +5401,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127209391</v>
+        <v>127209408</v>
       </c>
       <c r="B40" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733292</v>
+        <v>733340</v>
       </c>
       <c r="R40" t="n">
-        <v>7102236</v>
+        <v>7102327</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5598,6 +5598,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5624,10 +5629,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5635,16 +5640,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5659,10 +5664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R41" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5695,11 +5700,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5833,48 +5833,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R43" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,19 +5901,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,60 +5918,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R44" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,9 +5998,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,19 +6025,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127209431</v>
+        <v>127209432</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733392</v>
+        <v>733313</v>
       </c>
       <c r="R45" t="n">
-        <v>7102590</v>
+        <v>7102466</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6134,48 +6134,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127170226</v>
+        <v>127209431</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733338</v>
+        <v>733392</v>
       </c>
       <c r="R46" t="n">
-        <v>7102256</v>
+        <v>7102590</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6202,19 +6202,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6229,44 +6219,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209432</v>
+        <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6276,10 +6266,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733313</v>
+        <v>733357</v>
       </c>
       <c r="R47" t="n">
-        <v>7102466</v>
+        <v>7102361</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6338,45 +6328,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127209411</v>
+        <v>127212703</v>
       </c>
       <c r="B48" t="n">
-        <v>80157</v>
+        <v>57658</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733357</v>
+        <v>733290</v>
       </c>
       <c r="R48" t="n">
-        <v>7102361</v>
+        <v>7102188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6532,52 +6526,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127212703</v>
+        <v>127170226</v>
       </c>
       <c r="B50" t="n">
-        <v>57658</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733290</v>
+        <v>733338</v>
       </c>
       <c r="R50" t="n">
-        <v>7102188</v>
+        <v>7102256</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6604,9 +6594,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,64 +6621,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R51" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6705,19 +6701,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6732,60 +6718,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R52" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6812,9 +6802,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,12 +6829,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7050,7 +7050,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209397</v>
+        <v>127209393</v>
       </c>
       <c r="B55" t="n">
         <v>57658</v>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733264</v>
+        <v>733129</v>
       </c>
       <c r="R55" t="n">
-        <v>7102152</v>
+        <v>7102002</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209427</v>
+        <v>127209397</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7158,21 +7158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733364</v>
+        <v>733264</v>
       </c>
       <c r="R56" t="n">
-        <v>7102666</v>
+        <v>7102152</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7220,18 +7220,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7250,48 +7244,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127209393</v>
+        <v>127171825</v>
       </c>
       <c r="B57" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733129</v>
+        <v>733389</v>
       </c>
       <c r="R57" t="n">
-        <v>7102002</v>
+        <v>7102445</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7318,9 +7312,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7335,60 +7339,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127171825</v>
+        <v>127209427</v>
       </c>
       <c r="B58" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733389</v>
+        <v>733364</v>
       </c>
       <c r="R58" t="n">
-        <v>7102445</v>
+        <v>7102666</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7415,19 +7419,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:19</t>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7436,18 +7435,19 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7982,7 +7982,7 @@
         <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8288,48 +8288,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127209442</v>
+        <v>127209399</v>
       </c>
       <c r="B67" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R67" t="n">
-        <v>7102353</v>
+        <v>7102084</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8370,7 +8367,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8389,45 +8385,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209399</v>
+        <v>127209442</v>
       </c>
       <c r="B68" t="n">
-        <v>57658</v>
+        <v>80156</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R68" t="n">
-        <v>7102084</v>
+        <v>7102353</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8468,6 +8467,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127168623</v>
+        <v>127209403</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733163</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7102182</v>
+        <v>7102321</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,19 +8965,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:18</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8992,22 +8987,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209403</v>
+        <v>127209401</v>
       </c>
       <c r="B74" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9015,16 +9010,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9033,16 +9028,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733380</v>
+        <v>733172</v>
       </c>
       <c r="R74" t="n">
-        <v>7102321</v>
+        <v>7102001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9075,11 +9074,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9106,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127209401</v>
+        <v>127168623</v>
       </c>
       <c r="B75" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9117,41 +9111,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733172</v>
+        <v>733163</v>
       </c>
       <c r="R75" t="n">
-        <v>7102001</v>
+        <v>7102182</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9178,9 +9168,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,50 +9195,49 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209405</v>
+        <v>127209440</v>
       </c>
       <c r="B76" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9246,10 +9245,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733153</v>
+        <v>733324</v>
       </c>
       <c r="R76" t="n">
-        <v>7102629</v>
+        <v>7102432</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9284,17 +9283,13 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9313,27 +9308,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209440</v>
+        <v>127209429</v>
       </c>
       <c r="B77" t="n">
-        <v>80156</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9342,19 +9337,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733324</v>
+        <v>733361</v>
       </c>
       <c r="R77" t="n">
-        <v>7102432</v>
+        <v>7102666</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9395,7 +9387,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9414,10 +9405,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127209405</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9425,34 +9416,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733153</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9485,6 +9480,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9514,7 +9514,7 @@
         <v>127172437</v>
       </c>
       <c r="B79" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127352845</v>
+        <v>127352856</v>
       </c>
       <c r="B92" t="n">
-        <v>91326</v>
+        <v>82859</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10853,34 +10853,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733015</v>
+        <v>732867</v>
       </c>
       <c r="R92" t="n">
-        <v>7102294</v>
+        <v>7102250</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10915,12 +10918,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10939,10 +10948,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127352849</v>
+        <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>91326</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10950,21 +10959,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10974,10 +10983,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>732858</v>
+        <v>733015</v>
       </c>
       <c r="R93" t="n">
-        <v>7102299</v>
+        <v>7102294</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11036,10 +11045,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127352856</v>
+        <v>127352849</v>
       </c>
       <c r="B94" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11047,37 +11056,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>732867</v>
+        <v>732858</v>
       </c>
       <c r="R94" t="n">
-        <v>7102250</v>
+        <v>7102299</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11112,18 +11118,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>57658</v>
+        <v>82859</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,42 +11661,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R100" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11852,10 +11844,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B102" t="n">
-        <v>82859</v>
+        <v>57658</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,34 +11855,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R102" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352830</v>
+        <v>127352831</v>
       </c>
       <c r="B104" t="n">
-        <v>57821</v>
+        <v>91280</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>732870</v>
+        <v>733269</v>
       </c>
       <c r="R104" t="n">
-        <v>7102344</v>
+        <v>7102176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352831</v>
+        <v>127352857</v>
       </c>
       <c r="B105" t="n">
-        <v>91280</v>
+        <v>75134</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733269</v>
+        <v>733195</v>
       </c>
       <c r="R105" t="n">
-        <v>7102176</v>
+        <v>7102084</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352857</v>
+        <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>75134</v>
+        <v>57821</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>733195</v>
+        <v>732870</v>
       </c>
       <c r="R106" t="n">
-        <v>7102084</v>
+        <v>7102344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352823</v>
+        <v>127352847</v>
       </c>
       <c r="B116" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732915</v>
+        <v>733006</v>
       </c>
       <c r="R116" t="n">
-        <v>7102363</v>
+        <v>7102273</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,18 +13304,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13334,10 +13328,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352854</v>
+        <v>127352835</v>
       </c>
       <c r="B117" t="n">
-        <v>82859</v>
+        <v>57658</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13345,34 +13339,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732861</v>
+        <v>733013</v>
       </c>
       <c r="R117" t="n">
-        <v>7102297</v>
+        <v>7102291</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13431,10 +13433,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352847</v>
+        <v>127352836</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13442,34 +13444,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733006</v>
+        <v>732906</v>
       </c>
       <c r="R118" t="n">
-        <v>7102273</v>
+        <v>7102369</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13528,53 +13538,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352836</v>
+        <v>127352823</v>
       </c>
       <c r="B119" t="n">
-        <v>57658</v>
+        <v>91688</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732906</v>
+        <v>732915</v>
       </c>
       <c r="R119" t="n">
-        <v>7102369</v>
+        <v>7102363</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13609,12 +13611,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13633,10 +13641,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352835</v>
+        <v>127352854</v>
       </c>
       <c r="B120" t="n">
-        <v>57658</v>
+        <v>82859</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13644,42 +13652,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>733013</v>
+        <v>732861</v>
       </c>
       <c r="R120" t="n">
-        <v>7102291</v>
+        <v>7102297</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -8288,48 +8288,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127209399</v>
+        <v>127168323</v>
       </c>
       <c r="B67" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>733192</v>
       </c>
       <c r="R67" t="n">
-        <v>7102084</v>
+        <v>7102111</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8356,9 +8356,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8373,60 +8383,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127209442</v>
+        <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>80156</v>
+        <v>57658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>733349</v>
+        <v>733192</v>
       </c>
       <c r="R68" t="n">
-        <v>7102353</v>
+        <v>7102084</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8467,7 +8474,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8486,45 +8492,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209388</v>
+        <v>127209442</v>
       </c>
       <c r="B69" t="n">
-        <v>79636</v>
+        <v>80156</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733440</v>
+        <v>733349</v>
       </c>
       <c r="R69" t="n">
-        <v>7102463</v>
+        <v>7102353</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8565,6 +8574,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8583,48 +8593,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127168323</v>
+        <v>127209388</v>
       </c>
       <c r="B70" t="n">
-        <v>91295</v>
+        <v>79636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733192</v>
+        <v>733440</v>
       </c>
       <c r="R70" t="n">
-        <v>7102111</v>
+        <v>7102463</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8651,19 +8661,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9207,51 +9207,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209440</v>
+        <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>80156</v>
+        <v>98448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733324</v>
+        <v>733268</v>
       </c>
       <c r="R76" t="n">
-        <v>7102432</v>
+        <v>7102284</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9278,57 +9275,66 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209429</v>
+        <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9337,16 +9343,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733361</v>
+        <v>733324</v>
       </c>
       <c r="R77" t="n">
-        <v>7102666</v>
+        <v>7102432</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9387,6 +9396,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9405,10 +9415,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209405</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9416,38 +9426,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733153</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102629</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9480,11 +9486,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9511,48 +9512,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127172437</v>
+        <v>127209405</v>
       </c>
       <c r="B79" t="n">
-        <v>98448</v>
+        <v>57661</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733268</v>
+        <v>733153</v>
       </c>
       <c r="R79" t="n">
-        <v>7102284</v>
+        <v>7102629</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9579,19 +9584,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10116,45 +10116,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B85" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R85" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10191,7 +10199,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10200,6 +10208,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10218,53 +10227,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B86" t="n">
-        <v>98448</v>
+        <v>57658</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R86" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10301,7 +10302,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10310,7 +10311,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11142,45 +11142,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127352822</v>
+        <v>127352829</v>
       </c>
       <c r="B95" t="n">
-        <v>91688</v>
+        <v>57661</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733131</v>
+        <v>732945</v>
       </c>
       <c r="R95" t="n">
-        <v>7102015</v>
+        <v>7102361</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11217,7 +11229,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11226,7 +11238,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11245,57 +11256,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127352829</v>
+        <v>127352822</v>
       </c>
       <c r="B96" t="n">
-        <v>57661</v>
+        <v>91688</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>732945</v>
+        <v>733131</v>
       </c>
       <c r="R96" t="n">
-        <v>7102361</v>
+        <v>7102015</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11332,7 +11331,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
+          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11341,6 +11340,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R37" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,19 +5294,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5321,60 +5311,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R38" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5401,9 +5391,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5433,7 +5433,7 @@
         <v>127209396</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127209408</v>
+        <v>127169172</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>97327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733340</v>
+        <v>733225</v>
       </c>
       <c r="R40" t="n">
-        <v>7102327</v>
+        <v>7102172</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,14 +5595,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5617,22 +5622,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209391</v>
+        <v>127209408</v>
       </c>
       <c r="B41" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5640,16 +5645,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733292</v>
+        <v>733340</v>
       </c>
       <c r="R41" t="n">
-        <v>7102236</v>
+        <v>7102327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5700,6 +5705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5726,48 +5736,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127169172</v>
+        <v>127209391</v>
       </c>
       <c r="B42" t="n">
-        <v>97325</v>
+        <v>57660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733225</v>
+        <v>733292</v>
       </c>
       <c r="R42" t="n">
-        <v>7102172</v>
+        <v>7102236</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5794,19 +5804,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,60 +5821,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R43" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,9 +5901,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,60 +5928,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R44" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5998,19 +6008,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
         <v>127209432</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>127209431</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6328,49 +6328,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127212703</v>
+        <v>127209434</v>
       </c>
       <c r="B48" t="n">
-        <v>57658</v>
+        <v>92622</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733290</v>
+        <v>733218</v>
       </c>
       <c r="R48" t="n">
-        <v>7102188</v>
+        <v>7102512</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6429,10 +6425,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127209434</v>
+        <v>127170226</v>
       </c>
       <c r="B49" t="n">
-        <v>92620</v>
+        <v>80152</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6440,37 +6436,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733218</v>
+        <v>733338</v>
       </c>
       <c r="R49" t="n">
-        <v>7102512</v>
+        <v>7102256</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6497,9 +6493,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6514,60 +6520,64 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127170226</v>
+        <v>127212703</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>57660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733338</v>
+        <v>733290</v>
       </c>
       <c r="R50" t="n">
-        <v>7102256</v>
+        <v>7102188</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6594,19 +6604,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,12 +6621,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6636,7 +6636,7 @@
         <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7050,48 +7050,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209393</v>
+        <v>127171825</v>
       </c>
       <c r="B55" t="n">
-        <v>57658</v>
+        <v>91297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733129</v>
+        <v>733389</v>
       </c>
       <c r="R55" t="n">
-        <v>7102002</v>
+        <v>7102445</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7118,9 +7118,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7135,22 +7145,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209397</v>
+        <v>127209427</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7158,21 +7168,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7182,10 +7192,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733264</v>
+        <v>733364</v>
       </c>
       <c r="R56" t="n">
-        <v>7102152</v>
+        <v>7102666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7220,12 +7230,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7244,48 +7260,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127171825</v>
+        <v>127209397</v>
       </c>
       <c r="B57" t="n">
-        <v>91295</v>
+        <v>57660</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733389</v>
+        <v>733264</v>
       </c>
       <c r="R57" t="n">
-        <v>7102445</v>
+        <v>7102152</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7312,19 +7328,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7339,22 +7345,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127209427</v>
+        <v>127209393</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7362,21 +7368,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7386,10 +7392,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733364</v>
+        <v>733129</v>
       </c>
       <c r="R58" t="n">
-        <v>7102666</v>
+        <v>7102002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7424,18 +7430,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7454,48 +7454,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127209420</v>
+        <v>127170235</v>
       </c>
       <c r="B59" t="n">
-        <v>58031</v>
+        <v>80123</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733290</v>
+        <v>733349</v>
       </c>
       <c r="R59" t="n">
-        <v>7102188</v>
+        <v>7102356</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7522,9 +7522,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7539,60 +7549,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127170235</v>
+        <v>127209420</v>
       </c>
       <c r="B60" t="n">
-        <v>80121</v>
+        <v>58033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733349</v>
+        <v>733290</v>
       </c>
       <c r="R60" t="n">
-        <v>7102356</v>
+        <v>7102188</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7619,19 +7629,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7646,44 +7646,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172533</v>
+        <v>127168961</v>
       </c>
       <c r="B61" t="n">
-        <v>91348</v>
+        <v>91297</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733058</v>
+        <v>733165</v>
       </c>
       <c r="R61" t="n">
-        <v>7102382</v>
+        <v>7102177</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127168961</v>
+        <v>127169259</v>
       </c>
       <c r="B62" t="n">
-        <v>91295</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733165</v>
+        <v>733273</v>
       </c>
       <c r="R62" t="n">
-        <v>7102177</v>
+        <v>7102237</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7872,10 +7872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127169259</v>
+        <v>127172533</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7883,21 +7883,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733273</v>
+        <v>733058</v>
       </c>
       <c r="R63" t="n">
-        <v>7102237</v>
+        <v>7102382</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7982,7 +7982,7 @@
         <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>127213086</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>127209409</v>
       </c>
       <c r="B66" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>127168323</v>
       </c>
       <c r="B67" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>127209442</v>
       </c>
       <c r="B69" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>127209388</v>
       </c>
       <c r="B70" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>127209444</v>
       </c>
       <c r="B72" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127209403</v>
+        <v>127168623</v>
       </c>
       <c r="B73" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733380</v>
+        <v>733163</v>
       </c>
       <c r="R73" t="n">
-        <v>7102321</v>
+        <v>7102182</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,14 +8965,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8987,22 +8992,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209401</v>
+        <v>127209403</v>
       </c>
       <c r="B74" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,16 +9015,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9028,20 +9033,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733172</v>
+        <v>733380</v>
       </c>
       <c r="R74" t="n">
-        <v>7102001</v>
+        <v>7102321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9074,6 +9075,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9100,10 +9106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127168623</v>
+        <v>127209401</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9111,37 +9117,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733163</v>
+        <v>733172</v>
       </c>
       <c r="R75" t="n">
-        <v>7102182</v>
+        <v>7102001</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9168,19 +9178,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,60 +9195,64 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127172437</v>
+        <v>127209405</v>
       </c>
       <c r="B76" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733268</v>
+        <v>733153</v>
       </c>
       <c r="R76" t="n">
-        <v>7102284</v>
+        <v>7102629</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,19 +9279,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9302,63 +9301,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209440</v>
+        <v>127172437</v>
       </c>
       <c r="B77" t="n">
-        <v>80156</v>
+        <v>98450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733324</v>
+        <v>733268</v>
       </c>
       <c r="R77" t="n">
-        <v>7102432</v>
+        <v>7102284</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9385,57 +9381,66 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127209440</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>80158</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9444,16 +9449,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733324</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102432</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9494,6 +9502,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9512,10 +9521,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127209405</v>
+        <v>127209429</v>
       </c>
       <c r="B79" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9523,38 +9532,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733153</v>
+        <v>733361</v>
       </c>
       <c r="R79" t="n">
-        <v>7102629</v>
+        <v>7102666</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9587,11 +9592,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>127265350</v>
       </c>
       <c r="B83" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>127265357</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,53 +10116,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B85" t="n">
-        <v>98448</v>
+        <v>57660</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R85" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10199,7 +10191,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10208,7 +10200,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10227,45 +10218,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>57658</v>
+        <v>98450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R86" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10302,7 +10301,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10311,6 +10310,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>127265351</v>
       </c>
       <c r="B87" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>127265358</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>127265349</v>
       </c>
       <c r="B89" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>127265353</v>
       </c>
       <c r="B90" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>127352850</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>127352856</v>
       </c>
       <c r="B92" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>127352849</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11142,57 +11142,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127352829</v>
+        <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>57661</v>
+        <v>91690</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>732945</v>
+        <v>733131</v>
       </c>
       <c r="R95" t="n">
-        <v>7102361</v>
+        <v>7102015</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11229,7 +11217,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
+          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11238,6 +11226,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11256,45 +11245,57 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127352822</v>
+        <v>127352829</v>
       </c>
       <c r="B96" t="n">
-        <v>91688</v>
+        <v>57663</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733131</v>
+        <v>732945</v>
       </c>
       <c r="R96" t="n">
-        <v>7102015</v>
+        <v>7102361</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11331,7 +11332,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11340,7 +11341,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>127352841</v>
       </c>
       <c r="B97" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>127352833</v>
       </c>
       <c r="B102" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>127352831</v>
       </c>
       <c r="B104" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>127352857</v>
       </c>
       <c r="B105" t="n">
-        <v>75134</v>
+        <v>75136</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>127352837</v>
       </c>
       <c r="B107" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12447,10 +12447,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127352825</v>
+        <v>127352848</v>
       </c>
       <c r="B108" t="n">
-        <v>91330</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12458,21 +12458,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>733193</v>
+        <v>732920</v>
       </c>
       <c r="R108" t="n">
-        <v>7102147</v>
+        <v>7102396</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12544,10 +12544,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127352848</v>
+        <v>127352825</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>91332</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12555,21 +12555,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732920</v>
+        <v>733193</v>
       </c>
       <c r="R109" t="n">
-        <v>7102396</v>
+        <v>7102147</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12644,7 +12644,7 @@
         <v>127352852</v>
       </c>
       <c r="B110" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>91280</v>
+        <v>91282</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>127352844</v>
       </c>
       <c r="B112" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>127352855</v>
       </c>
       <c r="B113" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>127352834</v>
       </c>
       <c r="B115" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352847</v>
+        <v>127352823</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>91690</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>733006</v>
+        <v>732915</v>
       </c>
       <c r="R116" t="n">
-        <v>7102273</v>
+        <v>7102363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,12 +13304,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13328,10 +13334,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352835</v>
+        <v>127352847</v>
       </c>
       <c r="B117" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13339,42 +13345,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>733013</v>
+        <v>733006</v>
       </c>
       <c r="R117" t="n">
-        <v>7102291</v>
+        <v>7102273</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13433,10 +13431,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352836</v>
+        <v>127352835</v>
       </c>
       <c r="B118" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13476,10 +13474,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732906</v>
+        <v>733013</v>
       </c>
       <c r="R118" t="n">
-        <v>7102369</v>
+        <v>7102291</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13538,45 +13536,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352823</v>
+        <v>127352836</v>
       </c>
       <c r="B119" t="n">
-        <v>91688</v>
+        <v>57660</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732915</v>
+        <v>732906</v>
       </c>
       <c r="R119" t="n">
-        <v>7102363</v>
+        <v>7102369</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13611,18 +13617,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>127352854</v>
       </c>
       <c r="B120" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127169172</v>
+        <v>127209408</v>
       </c>
       <c r="B40" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733225</v>
+        <v>733340</v>
       </c>
       <c r="R40" t="n">
-        <v>7102172</v>
+        <v>7102327</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,19 +5595,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:41</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5622,22 +5617,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5645,16 +5640,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R41" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5705,11 +5700,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5736,48 +5726,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127209391</v>
+        <v>127169172</v>
       </c>
       <c r="B42" t="n">
-        <v>57660</v>
+        <v>97327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733292</v>
+        <v>733225</v>
       </c>
       <c r="R42" t="n">
-        <v>7102236</v>
+        <v>7102172</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5804,9 +5794,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,60 +5821,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R43" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,19 +5901,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,60 +5918,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R44" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,9 +5998,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6134,32 +6134,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209431</v>
+        <v>127209411</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>80159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733392</v>
+        <v>733357</v>
       </c>
       <c r="R46" t="n">
-        <v>7102590</v>
+        <v>7102361</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6231,10 +6231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209411</v>
+        <v>127209434</v>
       </c>
       <c r="B47" t="n">
-        <v>80159</v>
+        <v>92622</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6242,21 +6242,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733357</v>
+        <v>733218</v>
       </c>
       <c r="R47" t="n">
-        <v>7102361</v>
+        <v>7102512</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6328,45 +6328,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127209434</v>
+        <v>127212703</v>
       </c>
       <c r="B48" t="n">
-        <v>92622</v>
+        <v>57660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733218</v>
+        <v>733290</v>
       </c>
       <c r="R48" t="n">
-        <v>7102512</v>
+        <v>7102188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6425,48 +6429,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127170226</v>
+        <v>127209431</v>
       </c>
       <c r="B49" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733338</v>
+        <v>733392</v>
       </c>
       <c r="R49" t="n">
-        <v>7102256</v>
+        <v>7102590</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6493,19 +6497,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6520,64 +6514,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127212703</v>
+        <v>127170226</v>
       </c>
       <c r="B50" t="n">
-        <v>57660</v>
+        <v>80152</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733290</v>
+        <v>733338</v>
       </c>
       <c r="R50" t="n">
-        <v>7102188</v>
+        <v>7102256</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6604,9 +6594,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,12 +6621,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7050,48 +7050,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127171825</v>
+        <v>127209397</v>
       </c>
       <c r="B55" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733389</v>
+        <v>733264</v>
       </c>
       <c r="R55" t="n">
-        <v>7102445</v>
+        <v>7102152</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7118,19 +7118,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7145,12 +7135,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7260,7 +7250,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127209397</v>
+        <v>127209393</v>
       </c>
       <c r="B57" t="n">
         <v>57660</v>
@@ -7295,10 +7285,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733264</v>
+        <v>733129</v>
       </c>
       <c r="R57" t="n">
-        <v>7102152</v>
+        <v>7102002</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7357,48 +7347,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127209393</v>
+        <v>127171825</v>
       </c>
       <c r="B58" t="n">
-        <v>57660</v>
+        <v>91297</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733129</v>
+        <v>733389</v>
       </c>
       <c r="R58" t="n">
-        <v>7102002</v>
+        <v>7102445</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7425,9 +7415,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7442,60 +7442,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127170235</v>
+        <v>127209420</v>
       </c>
       <c r="B59" t="n">
-        <v>80123</v>
+        <v>58033</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733349</v>
+        <v>733290</v>
       </c>
       <c r="R59" t="n">
-        <v>7102356</v>
+        <v>7102188</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7522,19 +7522,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7549,60 +7539,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127209420</v>
+        <v>127170235</v>
       </c>
       <c r="B60" t="n">
-        <v>58033</v>
+        <v>80123</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733290</v>
+        <v>733349</v>
       </c>
       <c r="R60" t="n">
-        <v>7102188</v>
+        <v>7102356</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7629,9 +7619,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7646,44 +7646,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B61" t="n">
-        <v>91297</v>
+        <v>91350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R61" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127169259</v>
+        <v>127168961</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>91297</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733273</v>
+        <v>733165</v>
       </c>
       <c r="R62" t="n">
-        <v>7102237</v>
+        <v>7102177</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7872,10 +7872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172533</v>
+        <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7883,21 +7883,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733058</v>
+        <v>733273</v>
       </c>
       <c r="R63" t="n">
-        <v>7102382</v>
+        <v>7102237</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7979,52 +7979,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172025</v>
+        <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733365</v>
+        <v>733292</v>
       </c>
       <c r="R64" t="n">
-        <v>7102422</v>
+        <v>7102236</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8051,49 +8050,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127213086</v>
+        <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,37 +8091,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733292</v>
+        <v>733357</v>
       </c>
       <c r="R65" t="n">
-        <v>7102236</v>
+        <v>7102357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8172,7 +8159,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8191,48 +8177,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127209409</v>
+        <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733357</v>
+        <v>733365</v>
       </c>
       <c r="R66" t="n">
-        <v>7102357</v>
+        <v>7102422</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8259,9 +8249,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,22 +8276,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127168323</v>
+        <v>127209442</v>
       </c>
       <c r="B67" t="n">
-        <v>91297</v>
+        <v>80158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8299,37 +8299,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733192</v>
+        <v>733349</v>
       </c>
       <c r="R67" t="n">
-        <v>7102111</v>
+        <v>7102353</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8356,39 +8359,30 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8492,48 +8486,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127209442</v>
+        <v>127209388</v>
       </c>
       <c r="B69" t="n">
-        <v>80158</v>
+        <v>79638</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733349</v>
+        <v>733440</v>
       </c>
       <c r="R69" t="n">
-        <v>7102353</v>
+        <v>7102463</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8574,7 +8565,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8593,48 +8583,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127209388</v>
+        <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>79638</v>
+        <v>91297</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>733440</v>
+        <v>733192</v>
       </c>
       <c r="R70" t="n">
-        <v>7102463</v>
+        <v>7102111</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8661,9 +8651,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8678,12 +8678,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9207,52 +9207,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209405</v>
+        <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733153</v>
+        <v>733268</v>
       </c>
       <c r="R76" t="n">
-        <v>7102629</v>
+        <v>7102284</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9279,14 +9275,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9301,60 +9302,63 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127172437</v>
+        <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>98450</v>
+        <v>80158</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733268</v>
+        <v>733324</v>
       </c>
       <c r="R77" t="n">
-        <v>7102284</v>
+        <v>7102432</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9381,66 +9385,57 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209440</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>80158</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9449,19 +9444,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733324</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102432</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9502,7 +9494,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9521,10 +9512,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127209429</v>
+        <v>127209405</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9532,34 +9523,38 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733361</v>
+        <v>733153</v>
       </c>
       <c r="R79" t="n">
-        <v>7102666</v>
+        <v>7102629</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9592,6 +9587,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11142,45 +11142,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127352822</v>
+        <v>127352829</v>
       </c>
       <c r="B95" t="n">
-        <v>91690</v>
+        <v>57663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>733131</v>
+        <v>732945</v>
       </c>
       <c r="R95" t="n">
-        <v>7102015</v>
+        <v>7102361</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11217,7 +11229,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11226,7 +11238,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11245,57 +11256,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127352829</v>
+        <v>127352822</v>
       </c>
       <c r="B96" t="n">
-        <v>57663</v>
+        <v>91690</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>732945</v>
+        <v>733131</v>
       </c>
       <c r="R96" t="n">
-        <v>7102361</v>
+        <v>7102015</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11332,7 +11331,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
+          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11341,6 +11340,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B98" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R98" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B99" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R99" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352857</v>
+        <v>127352830</v>
       </c>
       <c r="B105" t="n">
-        <v>75136</v>
+        <v>57823</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733195</v>
+        <v>732870</v>
       </c>
       <c r="R105" t="n">
-        <v>7102084</v>
+        <v>7102344</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352830</v>
+        <v>127352857</v>
       </c>
       <c r="B106" t="n">
-        <v>57823</v>
+        <v>75136</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732870</v>
+        <v>733195</v>
       </c>
       <c r="R106" t="n">
-        <v>7102344</v>
+        <v>7102084</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127352832</v>
+        <v>127352844</v>
       </c>
       <c r="B111" t="n">
-        <v>91282</v>
+        <v>58033</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732878</v>
+        <v>732900</v>
       </c>
       <c r="R111" t="n">
-        <v>7102347</v>
+        <v>7102348</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12835,32 +12835,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127352844</v>
+        <v>127352832</v>
       </c>
       <c r="B112" t="n">
-        <v>58033</v>
+        <v>91282</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732900</v>
+        <v>732878</v>
       </c>
       <c r="R112" t="n">
-        <v>7102348</v>
+        <v>7102347</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13334,10 +13334,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352847</v>
+        <v>127352854</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>82861</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13345,21 +13345,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13369,10 +13369,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>733006</v>
+        <v>732861</v>
       </c>
       <c r="R117" t="n">
-        <v>7102273</v>
+        <v>7102297</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13431,10 +13431,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352835</v>
+        <v>127352847</v>
       </c>
       <c r="B118" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13442,42 +13442,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733013</v>
+        <v>733006</v>
       </c>
       <c r="R118" t="n">
-        <v>7102291</v>
+        <v>7102273</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13536,7 +13528,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352836</v>
+        <v>127352835</v>
       </c>
       <c r="B119" t="n">
         <v>57660</v>
@@ -13579,10 +13571,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732906</v>
+        <v>733013</v>
       </c>
       <c r="R119" t="n">
-        <v>7102369</v>
+        <v>7102291</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13641,10 +13633,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352854</v>
+        <v>127352836</v>
       </c>
       <c r="B120" t="n">
-        <v>82861</v>
+        <v>57660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13652,34 +13644,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>732861</v>
+        <v>732906</v>
       </c>
       <c r="R120" t="n">
-        <v>7102297</v>
+        <v>7102369</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -6633,48 +6633,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B51" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R51" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6701,9 +6705,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6718,64 +6732,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B52" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R52" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6802,19 +6812,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,12 +6829,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7658,10 +7658,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172533</v>
+        <v>127169259</v>
       </c>
       <c r="B61" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7669,21 +7669,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733058</v>
+        <v>733273</v>
       </c>
       <c r="R61" t="n">
-        <v>7102382</v>
+        <v>7102237</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B62" t="n">
-        <v>91297</v>
+        <v>91350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R62" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7872,32 +7872,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127169259</v>
+        <v>127168961</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>91297</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733273</v>
+        <v>733165</v>
       </c>
       <c r="R63" t="n">
-        <v>7102237</v>
+        <v>7102177</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9207,48 +9207,51 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127172437</v>
+        <v>127209440</v>
       </c>
       <c r="B76" t="n">
-        <v>98450</v>
+        <v>80158</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733268</v>
+        <v>733324</v>
       </c>
       <c r="R76" t="n">
-        <v>7102284</v>
+        <v>7102432</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,66 +9278,57 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209440</v>
+        <v>127209429</v>
       </c>
       <c r="B77" t="n">
-        <v>80158</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9343,19 +9337,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733324</v>
+        <v>733361</v>
       </c>
       <c r="R77" t="n">
-        <v>7102432</v>
+        <v>7102666</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9396,7 +9387,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9415,10 +9405,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127209405</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9426,34 +9416,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733153</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9486,6 +9480,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9512,52 +9511,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127209405</v>
+        <v>127172437</v>
       </c>
       <c r="B79" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733153</v>
+        <v>733268</v>
       </c>
       <c r="R79" t="n">
-        <v>7102629</v>
+        <v>7102284</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9584,14 +9579,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B37" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R37" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,9 +5294,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5311,60 +5321,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R38" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5391,19 +5401,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R53" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6931,22 +6936,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B54" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,37 +6959,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R54" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7979,51 +7979,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127213086</v>
+        <v>127172025</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733292</v>
+        <v>733365</v>
       </c>
       <c r="R64" t="n">
-        <v>7102236</v>
+        <v>7102422</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8050,40 +8051,49 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127209409</v>
+        <v>127213086</v>
       </c>
       <c r="B65" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8091,34 +8101,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733357</v>
+        <v>733292</v>
       </c>
       <c r="R65" t="n">
-        <v>7102357</v>
+        <v>7102236</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8159,6 +8172,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8177,52 +8191,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172025</v>
+        <v>127209409</v>
       </c>
       <c r="B66" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733365</v>
+        <v>733357</v>
       </c>
       <c r="R66" t="n">
-        <v>7102422</v>
+        <v>7102357</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8249,19 +8259,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,12 +8276,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127168623</v>
+        <v>127209403</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733163</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7102182</v>
+        <v>7102321</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,19 +8965,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:18</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8992,22 +8987,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209403</v>
+        <v>127209401</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9015,16 +9010,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9033,16 +9028,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733380</v>
+        <v>733172</v>
       </c>
       <c r="R74" t="n">
-        <v>7102321</v>
+        <v>7102001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9075,11 +9074,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9106,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127209401</v>
+        <v>127168623</v>
       </c>
       <c r="B75" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9117,41 +9111,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733172</v>
+        <v>733163</v>
       </c>
       <c r="R75" t="n">
-        <v>7102001</v>
+        <v>7102182</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9178,9 +9168,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,12 +9195,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -10842,10 +10842,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127352856</v>
+        <v>127352845</v>
       </c>
       <c r="B92" t="n">
-        <v>82861</v>
+        <v>91328</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10853,37 +10853,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>732867</v>
+        <v>733015</v>
       </c>
       <c r="R92" t="n">
-        <v>7102250</v>
+        <v>7102294</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10918,18 +10915,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10948,10 +10939,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127352845</v>
+        <v>127352856</v>
       </c>
       <c r="B93" t="n">
-        <v>91328</v>
+        <v>82861</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10959,34 +10950,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733015</v>
+        <v>732867</v>
       </c>
       <c r="R93" t="n">
-        <v>7102294</v>
+        <v>7102250</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11021,12 +11015,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11142,57 +11142,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127352829</v>
+        <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>57663</v>
+        <v>91690</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>732945</v>
+        <v>733131</v>
       </c>
       <c r="R95" t="n">
-        <v>7102361</v>
+        <v>7102015</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11229,7 +11217,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
+          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11238,6 +11226,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11256,45 +11245,57 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127352822</v>
+        <v>127352829</v>
       </c>
       <c r="B96" t="n">
-        <v>91690</v>
+        <v>57663</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>733131</v>
+        <v>732945</v>
       </c>
       <c r="R96" t="n">
-        <v>7102015</v>
+        <v>7102361</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11331,7 +11332,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ej mikroskoperad. Torde dock var brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+          <t>Födosökande på stående död/döende gran med rikligt av barkfläk.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11340,7 +11341,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R98" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R99" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B100" t="n">
-        <v>82861</v>
+        <v>57660</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,34 +11661,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R100" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11747,10 +11755,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127352846</v>
+        <v>127352853</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>82861</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11758,21 +11766,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11782,10 +11790,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733141</v>
+        <v>733168</v>
       </c>
       <c r="R101" t="n">
-        <v>7102155</v>
+        <v>7102021</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11844,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352833</v>
+        <v>127352846</v>
       </c>
       <c r="B102" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11855,42 +11863,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733067</v>
+        <v>733141</v>
       </c>
       <c r="R102" t="n">
-        <v>7102180</v>
+        <v>7102155</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352830</v>
+        <v>127352857</v>
       </c>
       <c r="B105" t="n">
-        <v>57823</v>
+        <v>75136</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>732870</v>
+        <v>733195</v>
       </c>
       <c r="R105" t="n">
-        <v>7102344</v>
+        <v>7102084</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352857</v>
+        <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>75136</v>
+        <v>57823</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>733195</v>
+        <v>732870</v>
       </c>
       <c r="R106" t="n">
-        <v>7102084</v>
+        <v>7102344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12447,10 +12447,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127352848</v>
+        <v>127352825</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12458,21 +12458,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732920</v>
+        <v>733193</v>
       </c>
       <c r="R108" t="n">
-        <v>7102396</v>
+        <v>7102147</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12544,10 +12544,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127352825</v>
+        <v>127352848</v>
       </c>
       <c r="B109" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12555,21 +12555,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>733193</v>
+        <v>732920</v>
       </c>
       <c r="R109" t="n">
-        <v>7102147</v>
+        <v>7102396</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127352844</v>
+        <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>58033</v>
+        <v>91282</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732900</v>
+        <v>732878</v>
       </c>
       <c r="R111" t="n">
-        <v>7102348</v>
+        <v>7102347</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12835,32 +12835,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127352832</v>
+        <v>127352844</v>
       </c>
       <c r="B112" t="n">
-        <v>91282</v>
+        <v>58033</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732878</v>
+        <v>732900</v>
       </c>
       <c r="R112" t="n">
-        <v>7102347</v>
+        <v>7102348</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352823</v>
+        <v>127352854</v>
       </c>
       <c r="B116" t="n">
-        <v>91690</v>
+        <v>82861</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732915</v>
+        <v>732861</v>
       </c>
       <c r="R116" t="n">
-        <v>7102363</v>
+        <v>7102297</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,18 +13304,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13334,10 +13328,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352854</v>
+        <v>127352847</v>
       </c>
       <c r="B117" t="n">
-        <v>82861</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13345,21 +13339,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13369,10 +13363,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732861</v>
+        <v>733006</v>
       </c>
       <c r="R117" t="n">
-        <v>7102297</v>
+        <v>7102273</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13431,32 +13425,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352847</v>
+        <v>127352823</v>
       </c>
       <c r="B118" t="n">
-        <v>79020</v>
+        <v>91690</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13466,10 +13460,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733006</v>
+        <v>732915</v>
       </c>
       <c r="R118" t="n">
-        <v>7102273</v>
+        <v>7102363</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13504,12 +13498,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5229,7 +5229,7 @@
         <v>127172249</v>
       </c>
       <c r="B37" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>127169172</v>
       </c>
       <c r="B42" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5833,48 +5833,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B43" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R43" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,9 +5901,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,60 +5928,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R44" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5998,19 +6008,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,12 +6025,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6234,7 +6234,7 @@
         <v>127209434</v>
       </c>
       <c r="B47" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>127171706</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>127209436</v>
       </c>
       <c r="B52" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R53" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,19 +6909,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6936,22 +6931,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6959,37 +6954,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R54" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7016,14 +7011,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,60 +7038,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209397</v>
+        <v>127171825</v>
       </c>
       <c r="B55" t="n">
-        <v>57660</v>
+        <v>91303</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733264</v>
+        <v>733389</v>
       </c>
       <c r="R55" t="n">
-        <v>7102152</v>
+        <v>7102445</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7118,9 +7118,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7135,22 +7145,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209427</v>
+        <v>127209397</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7158,21 +7168,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7182,10 +7192,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733364</v>
+        <v>733264</v>
       </c>
       <c r="R56" t="n">
-        <v>7102666</v>
+        <v>7102152</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7220,18 +7230,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7250,10 +7254,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127209393</v>
+        <v>127209427</v>
       </c>
       <c r="B57" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7261,21 +7265,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7285,10 +7289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733129</v>
+        <v>733364</v>
       </c>
       <c r="R57" t="n">
-        <v>7102002</v>
+        <v>7102666</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7323,12 +7327,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7347,48 +7357,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127171825</v>
+        <v>127209393</v>
       </c>
       <c r="B58" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733389</v>
+        <v>733129</v>
       </c>
       <c r="R58" t="n">
-        <v>7102445</v>
+        <v>7102002</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7415,19 +7425,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7442,12 +7442,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7658,32 +7658,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127169259</v>
+        <v>127168961</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>91303</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733273</v>
+        <v>733165</v>
       </c>
       <c r="R61" t="n">
-        <v>7102237</v>
+        <v>7102177</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7768,7 +7768,7 @@
         <v>127172533</v>
       </c>
       <c r="B62" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7872,32 +7872,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127168961</v>
+        <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>91297</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>733165</v>
+        <v>733273</v>
       </c>
       <c r="R63" t="n">
-        <v>7102177</v>
+        <v>7102237</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7979,52 +7979,51 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172025</v>
+        <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>733365</v>
+        <v>733292</v>
       </c>
       <c r="R64" t="n">
-        <v>7102422</v>
+        <v>7102236</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8051,49 +8050,40 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127213086</v>
+        <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8101,37 +8091,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>733292</v>
+        <v>733357</v>
       </c>
       <c r="R65" t="n">
-        <v>7102236</v>
+        <v>7102357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8172,7 +8159,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8191,48 +8177,52 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127209409</v>
+        <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>80123</v>
+        <v>98456</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733357</v>
+        <v>733365</v>
       </c>
       <c r="R66" t="n">
-        <v>7102357</v>
+        <v>7102422</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8259,9 +8249,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8276,12 +8276,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8586,7 +8586,7 @@
         <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127209403</v>
+        <v>127168623</v>
       </c>
       <c r="B73" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733380</v>
+        <v>733163</v>
       </c>
       <c r="R73" t="n">
-        <v>7102321</v>
+        <v>7102182</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,14 +8965,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8987,22 +8992,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209401</v>
+        <v>127209403</v>
       </c>
       <c r="B74" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9010,16 +9015,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9028,20 +9033,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733172</v>
+        <v>733380</v>
       </c>
       <c r="R74" t="n">
-        <v>7102001</v>
+        <v>7102321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9074,6 +9075,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9100,10 +9106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127168623</v>
+        <v>127209401</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9111,37 +9117,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733163</v>
+        <v>733172</v>
       </c>
       <c r="R75" t="n">
-        <v>7102182</v>
+        <v>7102001</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9168,19 +9178,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,63 +9195,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209440</v>
+        <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>80158</v>
+        <v>98456</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733324</v>
+        <v>733268</v>
       </c>
       <c r="R76" t="n">
-        <v>7102432</v>
+        <v>7102284</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9278,57 +9275,66 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127209429</v>
+        <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>80158</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9337,16 +9343,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733361</v>
+        <v>733324</v>
       </c>
       <c r="R77" t="n">
-        <v>7102666</v>
+        <v>7102432</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9387,6 +9396,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9405,10 +9415,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209405</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9416,38 +9426,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733153</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102629</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9480,11 +9486,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9511,48 +9512,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127172437</v>
+        <v>127209405</v>
       </c>
       <c r="B79" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733268</v>
+        <v>733153</v>
       </c>
       <c r="R79" t="n">
-        <v>7102284</v>
+        <v>7102629</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9579,19 +9584,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10842,10 +10842,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127352845</v>
+        <v>127352856</v>
       </c>
       <c r="B92" t="n">
-        <v>91328</v>
+        <v>82861</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10853,34 +10853,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>733015</v>
+        <v>732867</v>
       </c>
       <c r="R92" t="n">
-        <v>7102294</v>
+        <v>7102250</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10915,12 +10918,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10939,10 +10948,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127352856</v>
+        <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>82861</v>
+        <v>91334</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10950,37 +10959,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>732867</v>
+        <v>733015</v>
       </c>
       <c r="R93" t="n">
-        <v>7102250</v>
+        <v>7102294</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11015,18 +11021,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Rikligt med gammelgranskål i detta område. Finns säkerligen på fler träd i närheten.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127352853</v>
+        <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>82861</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11766,21 +11766,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11790,10 +11790,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733168</v>
+        <v>733141</v>
       </c>
       <c r="R101" t="n">
-        <v>7102021</v>
+        <v>7102155</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11852,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352846</v>
+        <v>127352853</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>82861</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,21 +11863,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11887,10 +11887,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733141</v>
+        <v>733168</v>
       </c>
       <c r="R102" t="n">
-        <v>7102155</v>
+        <v>7102021</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352831</v>
+        <v>127352857</v>
       </c>
       <c r="B104" t="n">
-        <v>91282</v>
+        <v>75136</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>733269</v>
+        <v>733195</v>
       </c>
       <c r="R104" t="n">
-        <v>7102176</v>
+        <v>7102084</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352857</v>
+        <v>127352831</v>
       </c>
       <c r="B105" t="n">
-        <v>75136</v>
+        <v>91288</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733195</v>
+        <v>733269</v>
       </c>
       <c r="R105" t="n">
-        <v>7102084</v>
+        <v>7102176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12450,7 +12450,7 @@
         <v>127352825</v>
       </c>
       <c r="B108" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127352832</v>
+        <v>127352844</v>
       </c>
       <c r="B111" t="n">
-        <v>91282</v>
+        <v>58033</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732878</v>
+        <v>732900</v>
       </c>
       <c r="R111" t="n">
-        <v>7102347</v>
+        <v>7102348</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12835,32 +12835,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127352844</v>
+        <v>127352832</v>
       </c>
       <c r="B112" t="n">
-        <v>58033</v>
+        <v>91288</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732900</v>
+        <v>732878</v>
       </c>
       <c r="R112" t="n">
-        <v>7102348</v>
+        <v>7102347</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13029,10 +13029,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127352827</v>
+        <v>127352834</v>
       </c>
       <c r="B114" t="n">
-        <v>91332</v>
+        <v>57660</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13040,34 +13040,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732905</v>
+        <v>732868</v>
       </c>
       <c r="R114" t="n">
-        <v>7102362</v>
+        <v>7102325</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13126,10 +13134,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127352834</v>
+        <v>127352827</v>
       </c>
       <c r="B115" t="n">
-        <v>57660</v>
+        <v>91338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13137,42 +13145,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732868</v>
+        <v>732905</v>
       </c>
       <c r="R115" t="n">
-        <v>7102325</v>
+        <v>7102362</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352854</v>
+        <v>127352836</v>
       </c>
       <c r="B116" t="n">
-        <v>82861</v>
+        <v>57660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13242,34 +13242,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732861</v>
+        <v>732906</v>
       </c>
       <c r="R116" t="n">
-        <v>7102297</v>
+        <v>7102369</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13328,10 +13336,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352847</v>
+        <v>127352835</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13339,34 +13347,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>733006</v>
+        <v>733013</v>
       </c>
       <c r="R117" t="n">
-        <v>7102273</v>
+        <v>7102291</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13428,7 +13444,7 @@
         <v>127352823</v>
       </c>
       <c r="B118" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13528,10 +13544,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352835</v>
+        <v>127352854</v>
       </c>
       <c r="B119" t="n">
-        <v>57660</v>
+        <v>82861</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13539,42 +13555,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>733013</v>
+        <v>732861</v>
       </c>
       <c r="R119" t="n">
-        <v>7102291</v>
+        <v>7102297</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13633,10 +13641,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352836</v>
+        <v>127352847</v>
       </c>
       <c r="B120" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13644,42 +13652,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>732906</v>
+        <v>733006</v>
       </c>
       <c r="R120" t="n">
-        <v>7102369</v>
+        <v>7102273</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5226,48 +5226,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127172249</v>
+        <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733320</v>
+        <v>733387</v>
       </c>
       <c r="R37" t="n">
-        <v>7102278</v>
+        <v>7102795</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5294,19 +5294,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5321,60 +5311,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127209390</v>
+        <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>79638</v>
+        <v>92631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733387</v>
+        <v>733320</v>
       </c>
       <c r="R38" t="n">
-        <v>7102795</v>
+        <v>7102278</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5401,9 +5391,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5433,7 +5433,7 @@
         <v>127209396</v>
       </c>
       <c r="B39" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127209408</v>
+        <v>127169172</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>97336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733340</v>
+        <v>733225</v>
       </c>
       <c r="R40" t="n">
-        <v>7102327</v>
+        <v>7102172</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,14 +5595,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5617,22 +5622,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209391</v>
+        <v>127209408</v>
       </c>
       <c r="B41" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5640,16 +5645,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733292</v>
+        <v>733340</v>
       </c>
       <c r="R41" t="n">
-        <v>7102236</v>
+        <v>7102327</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5700,6 +5705,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5726,48 +5736,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127169172</v>
+        <v>127209391</v>
       </c>
       <c r="B42" t="n">
-        <v>97333</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733225</v>
+        <v>733292</v>
       </c>
       <c r="R42" t="n">
-        <v>7102172</v>
+        <v>7102236</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5794,19 +5804,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,60 +5821,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127170430</v>
+        <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733334</v>
+        <v>733439</v>
       </c>
       <c r="R43" t="n">
-        <v>7102466</v>
+        <v>7102327</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5901,19 +5901,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5928,60 +5918,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127209423</v>
+        <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733439</v>
+        <v>733334</v>
       </c>
       <c r="R44" t="n">
-        <v>7102327</v>
+        <v>7102466</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,9 +5998,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6025,60 +6025,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127209432</v>
+        <v>127170226</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>80155</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733313</v>
+        <v>733338</v>
       </c>
       <c r="R45" t="n">
-        <v>7102466</v>
+        <v>7102256</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,9 +6105,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6122,44 +6132,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209411</v>
+        <v>127209432</v>
       </c>
       <c r="B46" t="n">
-        <v>80159</v>
+        <v>79023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6169,10 +6179,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733357</v>
+        <v>733313</v>
       </c>
       <c r="R46" t="n">
-        <v>7102361</v>
+        <v>7102466</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6231,10 +6241,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209434</v>
+        <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>92628</v>
+        <v>80162</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6242,21 +6252,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6266,10 +6276,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733218</v>
+        <v>733357</v>
       </c>
       <c r="R47" t="n">
-        <v>7102512</v>
+        <v>7102361</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6328,49 +6338,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127212703</v>
+        <v>127209434</v>
       </c>
       <c r="B48" t="n">
-        <v>57660</v>
+        <v>92631</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733290</v>
+        <v>733218</v>
       </c>
       <c r="R48" t="n">
-        <v>7102188</v>
+        <v>7102512</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6429,10 +6435,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127209431</v>
+        <v>127212703</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6440,34 +6446,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733392</v>
+        <v>733290</v>
       </c>
       <c r="R49" t="n">
-        <v>7102590</v>
+        <v>7102188</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6526,48 +6536,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127170226</v>
+        <v>127209431</v>
       </c>
       <c r="B50" t="n">
-        <v>80152</v>
+        <v>79023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733338</v>
+        <v>733392</v>
       </c>
       <c r="R50" t="n">
-        <v>7102256</v>
+        <v>7102590</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6594,19 +6604,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,64 +6621,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127171706</v>
+        <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>98456</v>
+        <v>92631</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733389</v>
+        <v>733360</v>
       </c>
       <c r="R51" t="n">
-        <v>7102445</v>
+        <v>7102776</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6705,19 +6701,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6732,60 +6718,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127209436</v>
+        <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>92628</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733360</v>
+        <v>733389</v>
       </c>
       <c r="R52" t="n">
-        <v>7102776</v>
+        <v>7102445</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6812,9 +6802,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6829,12 +6829,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6844,7 +6844,7 @@
         <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7050,48 +7050,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127171825</v>
+        <v>127209397</v>
       </c>
       <c r="B55" t="n">
-        <v>91303</v>
+        <v>57663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733389</v>
+        <v>733264</v>
       </c>
       <c r="R55" t="n">
-        <v>7102445</v>
+        <v>7102152</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7118,19 +7118,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7145,22 +7135,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209397</v>
+        <v>127209427</v>
       </c>
       <c r="B56" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7168,21 +7158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7192,10 +7182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733264</v>
+        <v>733364</v>
       </c>
       <c r="R56" t="n">
-        <v>7102152</v>
+        <v>7102666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7230,12 +7220,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7254,10 +7250,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127209427</v>
+        <v>127209393</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7265,21 +7261,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7289,10 +7285,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733364</v>
+        <v>733129</v>
       </c>
       <c r="R57" t="n">
-        <v>7102666</v>
+        <v>7102002</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7327,18 +7323,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7357,48 +7347,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127209393</v>
+        <v>127171825</v>
       </c>
       <c r="B58" t="n">
-        <v>57660</v>
+        <v>91306</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733129</v>
+        <v>733389</v>
       </c>
       <c r="R58" t="n">
-        <v>7102002</v>
+        <v>7102445</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7425,9 +7415,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7442,12 +7442,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
         <v>127209420</v>
       </c>
       <c r="B59" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>127170235</v>
       </c>
       <c r="B60" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7658,32 +7658,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B61" t="n">
-        <v>91303</v>
+        <v>91359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R61" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172533</v>
+        <v>127168961</v>
       </c>
       <c r="B62" t="n">
-        <v>91356</v>
+        <v>91306</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733058</v>
+        <v>733165</v>
       </c>
       <c r="R62" t="n">
-        <v>7102382</v>
+        <v>7102177</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7875,7 +7875,7 @@
         <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>127209442</v>
       </c>
       <c r="B67" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>127209388</v>
       </c>
       <c r="B69" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>127209444</v>
       </c>
       <c r="B72" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>127168623</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>127209403</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>127209401</v>
       </c>
       <c r="B75" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>127209405</v>
       </c>
       <c r="B79" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>127265350</v>
       </c>
       <c r="B83" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>127265357</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>127265352</v>
       </c>
       <c r="B85" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>127265351</v>
       </c>
       <c r="B87" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>127265358</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>127265349</v>
       </c>
       <c r="B89" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>127265353</v>
       </c>
       <c r="B90" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>127352850</v>
       </c>
       <c r="B91" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>127352856</v>
       </c>
       <c r="B92" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>127352849</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>127352829</v>
       </c>
       <c r="B96" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>127352841</v>
       </c>
       <c r="B97" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352833</v>
+        <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>57660</v>
+        <v>82864</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,42 +11661,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733067</v>
+        <v>733168</v>
       </c>
       <c r="R100" t="n">
-        <v>7102180</v>
+        <v>7102021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11758,7 +11750,7 @@
         <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11852,10 +11844,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B102" t="n">
-        <v>82861</v>
+        <v>57663</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,34 +11855,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R102" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352857</v>
+        <v>127352831</v>
       </c>
       <c r="B104" t="n">
-        <v>75136</v>
+        <v>91291</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>733195</v>
+        <v>733269</v>
       </c>
       <c r="R104" t="n">
-        <v>7102084</v>
+        <v>7102176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352831</v>
+        <v>127352857</v>
       </c>
       <c r="B105" t="n">
-        <v>91288</v>
+        <v>75139</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733269</v>
+        <v>733195</v>
       </c>
       <c r="R105" t="n">
-        <v>7102176</v>
+        <v>7102084</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
         <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>127352837</v>
       </c>
       <c r="B107" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>127352825</v>
       </c>
       <c r="B108" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>127352848</v>
       </c>
       <c r="B109" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>127352852</v>
       </c>
       <c r="B110" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127352844</v>
+        <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>58033</v>
+        <v>91291</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732900</v>
+        <v>732878</v>
       </c>
       <c r="R111" t="n">
-        <v>7102348</v>
+        <v>7102347</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12835,32 +12835,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127352832</v>
+        <v>127352844</v>
       </c>
       <c r="B112" t="n">
-        <v>91288</v>
+        <v>58036</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732878</v>
+        <v>732900</v>
       </c>
       <c r="R112" t="n">
-        <v>7102347</v>
+        <v>7102348</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12935,7 +12935,7 @@
         <v>127352855</v>
       </c>
       <c r="B113" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13029,10 +13029,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127352834</v>
+        <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>57660</v>
+        <v>91341</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13040,42 +13040,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732868</v>
+        <v>732905</v>
       </c>
       <c r="R114" t="n">
-        <v>7102325</v>
+        <v>7102362</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13134,10 +13126,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127352827</v>
+        <v>127352834</v>
       </c>
       <c r="B115" t="n">
-        <v>91338</v>
+        <v>57663</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13145,34 +13137,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732905</v>
+        <v>732868</v>
       </c>
       <c r="R115" t="n">
-        <v>7102362</v>
+        <v>7102325</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352836</v>
+        <v>127352847</v>
       </c>
       <c r="B116" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13242,42 +13242,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732906</v>
+        <v>733006</v>
       </c>
       <c r="R116" t="n">
-        <v>7102369</v>
+        <v>7102273</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13336,53 +13328,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352835</v>
+        <v>127352823</v>
       </c>
       <c r="B117" t="n">
-        <v>57660</v>
+        <v>91699</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>733013</v>
+        <v>732915</v>
       </c>
       <c r="R117" t="n">
-        <v>7102291</v>
+        <v>7102363</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13417,12 +13401,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13441,32 +13431,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352823</v>
+        <v>127352854</v>
       </c>
       <c r="B118" t="n">
-        <v>91696</v>
+        <v>82864</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13476,10 +13466,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732915</v>
+        <v>732861</v>
       </c>
       <c r="R118" t="n">
-        <v>7102363</v>
+        <v>7102297</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13514,18 +13504,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13544,10 +13528,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352854</v>
+        <v>127352835</v>
       </c>
       <c r="B119" t="n">
-        <v>82861</v>
+        <v>57663</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13555,34 +13539,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732861</v>
+        <v>733013</v>
       </c>
       <c r="R119" t="n">
-        <v>7102297</v>
+        <v>7102291</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13641,10 +13633,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352847</v>
+        <v>127352836</v>
       </c>
       <c r="B120" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13652,34 +13644,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>733006</v>
+        <v>732906</v>
       </c>
       <c r="R120" t="n">
-        <v>7102273</v>
+        <v>7102369</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AY152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5229,7 +5229,7 @@
         <v>127209390</v>
       </c>
       <c r="B37" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>127209396</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>127169172</v>
       </c>
       <c r="B40" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>127209408</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>127209391</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>127170430</v>
       </c>
       <c r="B44" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6037,48 +6037,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127170226</v>
+        <v>127209432</v>
       </c>
       <c r="B45" t="n">
-        <v>80155</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733338</v>
+        <v>733313</v>
       </c>
       <c r="R45" t="n">
-        <v>7102256</v>
+        <v>7102466</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,19 +6105,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6132,44 +6122,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209432</v>
+        <v>127209434</v>
       </c>
       <c r="B46" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6179,10 +6169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733313</v>
+        <v>733218</v>
       </c>
       <c r="R46" t="n">
-        <v>7102466</v>
+        <v>7102512</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6244,7 +6234,7 @@
         <v>127209411</v>
       </c>
       <c r="B47" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6338,45 +6328,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127209434</v>
+        <v>127212703</v>
       </c>
       <c r="B48" t="n">
-        <v>92631</v>
+        <v>57669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733218</v>
+        <v>733290</v>
       </c>
       <c r="R48" t="n">
-        <v>7102512</v>
+        <v>7102188</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6435,10 +6429,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127212703</v>
+        <v>127209431</v>
       </c>
       <c r="B49" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6446,38 +6440,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733290</v>
+        <v>733392</v>
       </c>
       <c r="R49" t="n">
-        <v>7102188</v>
+        <v>7102590</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6536,48 +6526,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127209431</v>
+        <v>127170226</v>
       </c>
       <c r="B50" t="n">
-        <v>79023</v>
+        <v>80161</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733392</v>
+        <v>733338</v>
       </c>
       <c r="R50" t="n">
-        <v>7102590</v>
+        <v>7102256</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6604,9 +6594,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,12 +6621,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6636,7 +6636,7 @@
         <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>127209406</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>127170966</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7050,10 +7050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209397</v>
+        <v>127209427</v>
       </c>
       <c r="B55" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733264</v>
+        <v>733364</v>
       </c>
       <c r="R55" t="n">
-        <v>7102152</v>
+        <v>7102666</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7123,12 +7123,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7147,10 +7153,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209427</v>
+        <v>127209397</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7158,21 +7164,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7182,10 +7188,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733364</v>
+        <v>733264</v>
       </c>
       <c r="R56" t="n">
-        <v>7102666</v>
+        <v>7102152</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7220,18 +7226,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>127209393</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>127171825</v>
       </c>
       <c r="B58" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>127209420</v>
       </c>
       <c r="B59" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>127170235</v>
       </c>
       <c r="B60" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7658,32 +7658,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172533</v>
+        <v>127168961</v>
       </c>
       <c r="B61" t="n">
-        <v>91359</v>
+        <v>91314</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733058</v>
+        <v>733165</v>
       </c>
       <c r="R61" t="n">
-        <v>7102382</v>
+        <v>7102177</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B62" t="n">
-        <v>91306</v>
+        <v>91367</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R62" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7875,7 +7875,7 @@
         <v>127169259</v>
       </c>
       <c r="B63" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>127213086</v>
       </c>
       <c r="B64" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>127209409</v>
       </c>
       <c r="B65" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>127209442</v>
       </c>
       <c r="B67" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>127209399</v>
       </c>
       <c r="B68" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>127209388</v>
       </c>
       <c r="B69" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>127209444</v>
       </c>
       <c r="B72" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127168623</v>
+        <v>127209403</v>
       </c>
       <c r="B73" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8908,37 +8908,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bjännmyran, Bjännmyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733163</v>
+        <v>733380</v>
       </c>
       <c r="R73" t="n">
-        <v>7102182</v>
+        <v>7102321</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8965,19 +8965,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:18</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8992,22 +8987,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127209403</v>
+        <v>127209401</v>
       </c>
       <c r="B74" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9015,16 +9010,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9033,16 +9028,20 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733380</v>
+        <v>733172</v>
       </c>
       <c r="R74" t="n">
-        <v>7102321</v>
+        <v>7102001</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9075,11 +9074,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9106,10 +9100,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127209401</v>
+        <v>127168623</v>
       </c>
       <c r="B75" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9117,41 +9111,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Bjännmyran, Bjännmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>733172</v>
+        <v>733163</v>
       </c>
       <c r="R75" t="n">
-        <v>7102001</v>
+        <v>7102182</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9178,9 +9168,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9195,60 +9195,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127172437</v>
+        <v>127209429</v>
       </c>
       <c r="B76" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733268</v>
+        <v>733361</v>
       </c>
       <c r="R76" t="n">
-        <v>7102284</v>
+        <v>7102666</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,19 +9275,9 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9302,12 +9292,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9317,7 +9307,7 @@
         <v>127209440</v>
       </c>
       <c r="B77" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9415,10 +9405,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209429</v>
+        <v>127209405</v>
       </c>
       <c r="B78" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9426,34 +9416,38 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733361</v>
+        <v>733153</v>
       </c>
       <c r="R78" t="n">
-        <v>7102666</v>
+        <v>7102629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9486,6 +9480,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9512,52 +9511,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127209405</v>
+        <v>127172437</v>
       </c>
       <c r="B79" t="n">
-        <v>57666</v>
+        <v>98467</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733153</v>
+        <v>733268</v>
       </c>
       <c r="R79" t="n">
-        <v>7102629</v>
+        <v>7102284</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9584,14 +9579,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>127265350</v>
       </c>
       <c r="B83" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>127265357</v>
       </c>
       <c r="B84" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10116,45 +10116,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B85" t="n">
-        <v>57663</v>
+        <v>98467</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R85" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10191,7 +10199,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10200,6 +10208,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10218,53 +10227,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B86" t="n">
-        <v>98459</v>
+        <v>57669</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R86" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10301,7 +10302,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10310,7 +10311,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>127265351</v>
       </c>
       <c r="B87" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>127265358</v>
       </c>
       <c r="B88" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>127265349</v>
       </c>
       <c r="B89" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>127265353</v>
       </c>
       <c r="B90" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>127352850</v>
       </c>
       <c r="B91" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>127352856</v>
       </c>
       <c r="B92" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>127352849</v>
       </c>
       <c r="B94" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>127352829</v>
       </c>
       <c r="B96" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>127352841</v>
       </c>
       <c r="B97" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>127352833</v>
       </c>
       <c r="B102" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>127352831</v>
       </c>
       <c r="B104" t="n">
-        <v>91291</v>
+        <v>91299</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>127352857</v>
       </c>
       <c r="B105" t="n">
-        <v>75139</v>
+        <v>75145</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>127352837</v>
       </c>
       <c r="B107" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12447,10 +12447,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127352825</v>
+        <v>127352848</v>
       </c>
       <c r="B108" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12458,21 +12458,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>733193</v>
+        <v>732920</v>
       </c>
       <c r="R108" t="n">
-        <v>7102147</v>
+        <v>7102396</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12544,10 +12544,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127352848</v>
+        <v>127352825</v>
       </c>
       <c r="B109" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12555,21 +12555,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732920</v>
+        <v>733193</v>
       </c>
       <c r="R109" t="n">
-        <v>7102396</v>
+        <v>7102147</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12644,7 +12644,7 @@
         <v>127352852</v>
       </c>
       <c r="B110" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>91291</v>
+        <v>91299</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>127352844</v>
       </c>
       <c r="B112" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>127352855</v>
       </c>
       <c r="B113" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>127352834</v>
       </c>
       <c r="B115" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13231,10 +13231,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352847</v>
+        <v>127352854</v>
       </c>
       <c r="B116" t="n">
-        <v>79023</v>
+        <v>82870</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13242,21 +13242,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>733006</v>
+        <v>732861</v>
       </c>
       <c r="R116" t="n">
-        <v>7102273</v>
+        <v>7102297</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13328,32 +13328,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352823</v>
+        <v>127352847</v>
       </c>
       <c r="B117" t="n">
-        <v>91699</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732915</v>
+        <v>733006</v>
       </c>
       <c r="R117" t="n">
-        <v>7102363</v>
+        <v>7102273</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13401,18 +13401,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13431,32 +13425,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352854</v>
+        <v>127352823</v>
       </c>
       <c r="B118" t="n">
-        <v>82864</v>
+        <v>91707</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13466,10 +13460,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732861</v>
+        <v>732915</v>
       </c>
       <c r="R118" t="n">
-        <v>7102297</v>
+        <v>7102363</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13504,12 +13498,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>127352835</v>
       </c>
       <c r="B119" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>127352836</v>
       </c>
       <c r="B120" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13735,6 +13735,3103 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128092215</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>733389</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7102265</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>128092220</v>
+      </c>
+      <c r="B122" t="n">
+        <v>75153</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>733382</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7102436</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128092251</v>
+      </c>
+      <c r="B123" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>732901</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7102197</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128092223</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91349</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>733389</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7102564</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128092222</v>
+      </c>
+      <c r="B125" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>733395</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7102558</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128092239</v>
+      </c>
+      <c r="B126" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>733324</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7102525</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128092231</v>
+      </c>
+      <c r="B127" t="n">
+        <v>91367</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>733194</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7102684</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128092202</v>
+      </c>
+      <c r="B128" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>733128</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7102020</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128092244</v>
+      </c>
+      <c r="B129" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>733054</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7102357</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128092206</v>
+      </c>
+      <c r="B130" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>733214</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7102100</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128092235</v>
+      </c>
+      <c r="B131" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>733171</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7102645</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128092238</v>
+      </c>
+      <c r="B132" t="n">
+        <v>105505</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>733339</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7102561</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128092240</v>
+      </c>
+      <c r="B133" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>733256</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7102476</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128092224</v>
+      </c>
+      <c r="B134" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>733431</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7102575</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128092247</v>
+      </c>
+      <c r="B135" t="n">
+        <v>82870</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>732914</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7102401</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128092249</v>
+      </c>
+      <c r="B136" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>732847</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7102277</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128092203</v>
+      </c>
+      <c r="B137" t="n">
+        <v>91349</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>733128</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7102020</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128092219</v>
+      </c>
+      <c r="B138" t="n">
+        <v>82870</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>733363</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7102450</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128092237</v>
+      </c>
+      <c r="B139" t="n">
+        <v>91367</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>733337</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7102597</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128092246</v>
+      </c>
+      <c r="B140" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>732940</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7102409</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128092221</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>733376</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7102482</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128092208</v>
+      </c>
+      <c r="B142" t="n">
+        <v>91707</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>733269</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7102181</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128092211</v>
+      </c>
+      <c r="B143" t="n">
+        <v>91299</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>112</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>733266</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7102189</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128092213</v>
+      </c>
+      <c r="B144" t="n">
+        <v>88752</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>510</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>733347</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7102250</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128092229</v>
+      </c>
+      <c r="B145" t="n">
+        <v>82870</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>733361</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7102699</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128092212</v>
+      </c>
+      <c r="B146" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>733283</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7102190</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128092214</v>
+      </c>
+      <c r="B147" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>733358</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7102265</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128092227</v>
+      </c>
+      <c r="B148" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>733385</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7102616</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128092233</v>
+      </c>
+      <c r="B149" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>733179</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7102677</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>128092205</v>
+      </c>
+      <c r="B150" t="n">
+        <v>91349</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>733214</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7102100</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>128092241</v>
+      </c>
+      <c r="B151" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>733206</v>
+      </c>
+      <c r="R151" t="n">
+        <v>7102446</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>128092218</v>
+      </c>
+      <c r="B152" t="n">
+        <v>100622</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Stennäs, Vb</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>733367</v>
+      </c>
+      <c r="R152" t="n">
+        <v>7102430</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -5326,7 +5326,7 @@
         <v>127172249</v>
       </c>
       <c r="B38" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5527,48 +5527,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127169172</v>
+        <v>127209408</v>
       </c>
       <c r="B40" t="n">
-        <v>97344</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733225</v>
+        <v>733340</v>
       </c>
       <c r="R40" t="n">
-        <v>7102172</v>
+        <v>7102327</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5595,19 +5595,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:41</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5622,22 +5617,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127209408</v>
+        <v>127209391</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5645,16 +5640,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733340</v>
+        <v>733292</v>
       </c>
       <c r="R41" t="n">
-        <v>7102327</v>
+        <v>7102236</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5705,11 +5700,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5736,48 +5726,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127209391</v>
+        <v>127169172</v>
       </c>
       <c r="B42" t="n">
-        <v>57669</v>
+        <v>97345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733292</v>
+        <v>733225</v>
       </c>
       <c r="R42" t="n">
-        <v>7102236</v>
+        <v>7102172</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5804,9 +5794,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5821,12 +5821,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5836,7 +5836,7 @@
         <v>127209423</v>
       </c>
       <c r="B43" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6134,10 +6134,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127209434</v>
+        <v>127209411</v>
       </c>
       <c r="B46" t="n">
-        <v>92639</v>
+        <v>80168</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733218</v>
+        <v>733357</v>
       </c>
       <c r="R46" t="n">
-        <v>7102512</v>
+        <v>7102361</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6231,10 +6231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127209411</v>
+        <v>127209434</v>
       </c>
       <c r="B47" t="n">
-        <v>80168</v>
+        <v>92640</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6242,21 +6242,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6266,10 +6266,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733357</v>
+        <v>733218</v>
       </c>
       <c r="R47" t="n">
-        <v>7102361</v>
+        <v>7102512</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6636,7 +6636,7 @@
         <v>127209436</v>
       </c>
       <c r="B51" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>127171706</v>
       </c>
       <c r="B52" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127209406</v>
+        <v>127170966</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6852,37 +6852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733380</v>
+        <v>733334</v>
       </c>
       <c r="R53" t="n">
-        <v>7102381</v>
+        <v>7102466</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6909,14 +6909,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6931,22 +6936,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127170966</v>
+        <v>127209406</v>
       </c>
       <c r="B54" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6954,37 +6959,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733334</v>
+        <v>733380</v>
       </c>
       <c r="R54" t="n">
-        <v>7102466</v>
+        <v>7102381</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7011,19 +7016,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127209427</v>
+        <v>127209397</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733364</v>
+        <v>733264</v>
       </c>
       <c r="R55" t="n">
-        <v>7102666</v>
+        <v>7102152</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7123,18 +7123,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7153,10 +7147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127209397</v>
+        <v>127209427</v>
       </c>
       <c r="B56" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7164,21 +7158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7188,10 +7182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733264</v>
+        <v>733364</v>
       </c>
       <c r="R56" t="n">
-        <v>7102152</v>
+        <v>7102666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7226,12 +7220,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>127171825</v>
       </c>
       <c r="B58" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7658,32 +7658,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127168961</v>
+        <v>127172533</v>
       </c>
       <c r="B61" t="n">
-        <v>91314</v>
+        <v>91368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>733165</v>
+        <v>733058</v>
       </c>
       <c r="R61" t="n">
-        <v>7102177</v>
+        <v>7102382</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7765,32 +7765,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172533</v>
+        <v>127168961</v>
       </c>
       <c r="B62" t="n">
-        <v>91367</v>
+        <v>91315</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>733058</v>
+        <v>733165</v>
       </c>
       <c r="R62" t="n">
-        <v>7102382</v>
+        <v>7102177</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8180,7 +8180,7 @@
         <v>127172025</v>
       </c>
       <c r="B66" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>127168323</v>
       </c>
       <c r="B70" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>127209387</v>
       </c>
       <c r="B71" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9207,48 +9207,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127209429</v>
+        <v>127172437</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stennäs, Vb</t>
+          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733361</v>
+        <v>733268</v>
       </c>
       <c r="R76" t="n">
-        <v>7102666</v>
+        <v>7102284</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,9 +9275,19 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9292,12 +9302,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9405,10 +9415,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127209405</v>
+        <v>127209429</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9416,38 +9426,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733153</v>
+        <v>733361</v>
       </c>
       <c r="R78" t="n">
-        <v>7102629</v>
+        <v>7102666</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9480,11 +9486,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9511,48 +9512,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127172437</v>
+        <v>127209405</v>
       </c>
       <c r="B79" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lill-Snottermyran, Lill-Snottermyran, Vb</t>
+          <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733268</v>
+        <v>733153</v>
       </c>
       <c r="R79" t="n">
-        <v>7102284</v>
+        <v>7102629</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9579,19 +9584,14 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:02</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9606,12 +9606,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9621,7 +9621,7 @@
         <v>127209438</v>
       </c>
       <c r="B80" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>127173185</v>
       </c>
       <c r="B81" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>127168984</v>
       </c>
       <c r="B82" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>127265356</v>
       </c>
       <c r="B85" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10948,10 +10948,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127352845</v>
+        <v>127352849</v>
       </c>
       <c r="B93" t="n">
-        <v>91345</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10959,21 +10959,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10983,10 +10983,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>733015</v>
+        <v>732858</v>
       </c>
       <c r="R93" t="n">
-        <v>7102294</v>
+        <v>7102299</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11045,10 +11045,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127352849</v>
+        <v>127352845</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>91346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11056,21 +11056,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11080,10 +11080,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>732858</v>
+        <v>733015</v>
       </c>
       <c r="R94" t="n">
-        <v>7102299</v>
+        <v>7102294</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11145,7 +11145,7 @@
         <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B98" t="n">
-        <v>91349</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R98" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R99" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>127352831</v>
       </c>
       <c r="B104" t="n">
-        <v>91299</v>
+        <v>91300</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>127352825</v>
       </c>
       <c r="B109" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>91299</v>
+        <v>91300</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352854</v>
+        <v>127352823</v>
       </c>
       <c r="B116" t="n">
-        <v>82870</v>
+        <v>91708</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732861</v>
+        <v>732915</v>
       </c>
       <c r="R116" t="n">
-        <v>7102297</v>
+        <v>7102363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,12 +13304,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13328,10 +13334,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352847</v>
+        <v>127352854</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13339,21 +13345,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13363,10 +13369,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>733006</v>
+        <v>732861</v>
       </c>
       <c r="R117" t="n">
-        <v>7102273</v>
+        <v>7102297</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13425,32 +13431,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352823</v>
+        <v>127352847</v>
       </c>
       <c r="B118" t="n">
-        <v>91707</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13460,10 +13466,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732915</v>
+        <v>733006</v>
       </c>
       <c r="R118" t="n">
-        <v>7102363</v>
+        <v>7102273</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13498,18 +13504,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13741,7 +13741,7 @@
         <v>128092215</v>
       </c>
       <c r="B121" t="n">
-        <v>91756</v>
+        <v>91757</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>128092251</v>
       </c>
       <c r="B123" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092223</v>
+        <v>128092231</v>
       </c>
       <c r="B124" t="n">
-        <v>91349</v>
+        <v>91368</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,21 +14035,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733389</v>
+        <v>733194</v>
       </c>
       <c r="R124" t="n">
-        <v>7102564</v>
+        <v>7102684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092222</v>
+        <v>128092223</v>
       </c>
       <c r="B125" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,42 +14132,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733395</v>
+        <v>733389</v>
       </c>
       <c r="R125" t="n">
-        <v>7102558</v>
+        <v>7102564</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,11 +14192,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14231,10 +14218,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092239</v>
+        <v>128092222</v>
       </c>
       <c r="B126" t="n">
-        <v>91756</v>
+        <v>57672</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14242,29 +14229,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733324</v>
+        <v>733395</v>
       </c>
       <c r="R126" t="n">
-        <v>7102525</v>
+        <v>7102558</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14297,6 +14297,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14323,10 +14328,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092231</v>
+        <v>128092239</v>
       </c>
       <c r="B127" t="n">
-        <v>91367</v>
+        <v>91757</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14334,21 +14339,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733194</v>
+        <v>733324</v>
       </c>
       <c r="R127" t="n">
-        <v>7102684</v>
+        <v>7102525</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14423,7 +14423,7 @@
         <v>128092202</v>
       </c>
       <c r="B128" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>128092244</v>
       </c>
       <c r="B129" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14614,10 +14614,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092206</v>
+        <v>128092235</v>
       </c>
       <c r="B130" t="n">
-        <v>91756</v>
+        <v>57669</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14625,29 +14625,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733214</v>
+        <v>733171</v>
       </c>
       <c r="R130" t="n">
-        <v>7102100</v>
+        <v>7102645</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14706,10 +14716,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092235</v>
+        <v>128092206</v>
       </c>
       <c r="B131" t="n">
-        <v>57669</v>
+        <v>91757</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14717,39 +14727,29 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733171</v>
+        <v>733214</v>
       </c>
       <c r="R131" t="n">
-        <v>7102645</v>
+        <v>7102100</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14811,7 +14811,7 @@
         <v>128092238</v>
       </c>
       <c r="B132" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>128092240</v>
       </c>
       <c r="B133" t="n">
-        <v>91756</v>
+        <v>91757</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>128092224</v>
       </c>
       <c r="B134" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>128092249</v>
       </c>
       <c r="B136" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15288,10 +15288,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128092203</v>
+        <v>128092219</v>
       </c>
       <c r="B137" t="n">
-        <v>91349</v>
+        <v>82870</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15299,21 +15299,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>733128</v>
+        <v>733363</v>
       </c>
       <c r="R137" t="n">
-        <v>7102020</v>
+        <v>7102450</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15385,10 +15385,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128092219</v>
+        <v>128092203</v>
       </c>
       <c r="B138" t="n">
-        <v>82870</v>
+        <v>91350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15396,21 +15396,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15420,10 +15420,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>733363</v>
+        <v>733128</v>
       </c>
       <c r="R138" t="n">
-        <v>7102450</v>
+        <v>7102020</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15485,7 +15485,7 @@
         <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>91756</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,16 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R140" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092221</v>
+        <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>79029</v>
+        <v>91757</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15687,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733376</v>
+        <v>732940</v>
       </c>
       <c r="R141" t="n">
-        <v>7102482</v>
+        <v>7102409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15771,7 +15771,7 @@
         <v>128092208</v>
       </c>
       <c r="B142" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>128092211</v>
       </c>
       <c r="B143" t="n">
-        <v>91299</v>
+        <v>91300</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092213</v>
+        <v>128092229</v>
       </c>
       <c r="B144" t="n">
-        <v>88752</v>
+        <v>82870</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,21 +15973,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733347</v>
+        <v>733361</v>
       </c>
       <c r="R144" t="n">
-        <v>7102250</v>
+        <v>7102699</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16059,10 +16059,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092229</v>
+        <v>128092214</v>
       </c>
       <c r="B145" t="n">
-        <v>82870</v>
+        <v>57669</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16070,34 +16070,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733361</v>
+        <v>733358</v>
       </c>
       <c r="R145" t="n">
-        <v>7102699</v>
+        <v>7102265</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16156,32 +16161,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092212</v>
+        <v>128092213</v>
       </c>
       <c r="B146" t="n">
-        <v>91314</v>
+        <v>88753</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16191,10 +16196,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733283</v>
+        <v>733347</v>
       </c>
       <c r="R146" t="n">
-        <v>7102190</v>
+        <v>7102250</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16253,50 +16258,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092214</v>
+        <v>128092212</v>
       </c>
       <c r="B147" t="n">
-        <v>57669</v>
+        <v>91315</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733358</v>
+        <v>733283</v>
       </c>
       <c r="R147" t="n">
-        <v>7102265</v>
+        <v>7102190</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16455,7 +16455,7 @@
         <v>128092233</v>
       </c>
       <c r="B149" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16549,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B150" t="n">
-        <v>91349</v>
+        <v>100623</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R150" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092241</v>
+        <v>128092205</v>
       </c>
       <c r="B151" t="n">
-        <v>91756</v>
+        <v>91350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16657,16 +16657,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16676,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733206</v>
+        <v>733214</v>
       </c>
       <c r="R151" t="n">
-        <v>7102446</v>
+        <v>7102100</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16738,32 +16743,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092218</v>
+        <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>100622</v>
+        <v>91757</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1365</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733367</v>
+        <v>733206</v>
       </c>
       <c r="R152" t="n">
-        <v>7102430</v>
+        <v>7102446</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -10948,10 +10948,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127352849</v>
+        <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>91346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10959,21 +10959,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10983,10 +10983,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>732858</v>
+        <v>733015</v>
       </c>
       <c r="R93" t="n">
-        <v>7102299</v>
+        <v>7102294</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11045,10 +11045,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127352845</v>
+        <v>127352849</v>
       </c>
       <c r="B94" t="n">
-        <v>91346</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11056,21 +11056,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11080,10 +11080,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>733015</v>
+        <v>732858</v>
       </c>
       <c r="R94" t="n">
-        <v>7102294</v>
+        <v>7102299</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127352851</v>
+        <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11467,21 +11467,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>733008</v>
+        <v>732881</v>
       </c>
       <c r="R98" t="n">
-        <v>7102279</v>
+        <v>7102356</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127352828</v>
+        <v>127352851</v>
       </c>
       <c r="B99" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>732881</v>
+        <v>733008</v>
       </c>
       <c r="R99" t="n">
-        <v>7102356</v>
+        <v>7102279</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352853</v>
+        <v>127352833</v>
       </c>
       <c r="B100" t="n">
-        <v>82870</v>
+        <v>57669</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,34 +11661,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733168</v>
+        <v>733067</v>
       </c>
       <c r="R100" t="n">
-        <v>7102021</v>
+        <v>7102180</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11747,10 +11755,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127352846</v>
+        <v>127352853</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11758,21 +11766,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11782,10 +11790,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733141</v>
+        <v>733168</v>
       </c>
       <c r="R101" t="n">
-        <v>7102155</v>
+        <v>7102021</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11844,10 +11852,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352833</v>
+        <v>127352846</v>
       </c>
       <c r="B102" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11855,42 +11863,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733067</v>
+        <v>733141</v>
       </c>
       <c r="R102" t="n">
-        <v>7102180</v>
+        <v>7102155</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352823</v>
+        <v>127352854</v>
       </c>
       <c r="B116" t="n">
-        <v>91708</v>
+        <v>82870</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732915</v>
+        <v>732861</v>
       </c>
       <c r="R116" t="n">
-        <v>7102363</v>
+        <v>7102297</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,18 +13304,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13334,10 +13328,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352854</v>
+        <v>127352847</v>
       </c>
       <c r="B117" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13345,21 +13339,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13369,10 +13363,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>732861</v>
+        <v>733006</v>
       </c>
       <c r="R117" t="n">
-        <v>7102297</v>
+        <v>7102273</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13431,10 +13425,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352847</v>
+        <v>127352835</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13442,34 +13436,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733006</v>
+        <v>733013</v>
       </c>
       <c r="R118" t="n">
-        <v>7102273</v>
+        <v>7102291</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13528,7 +13530,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352835</v>
+        <v>127352836</v>
       </c>
       <c r="B119" t="n">
         <v>57669</v>
@@ -13571,10 +13573,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>733013</v>
+        <v>732906</v>
       </c>
       <c r="R119" t="n">
-        <v>7102291</v>
+        <v>7102369</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13633,53 +13635,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352836</v>
+        <v>127352823</v>
       </c>
       <c r="B120" t="n">
-        <v>57669</v>
+        <v>91708</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>732906</v>
+        <v>732915</v>
       </c>
       <c r="R120" t="n">
-        <v>7102369</v>
+        <v>7102363</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13714,12 +13708,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B121" t="n">
-        <v>91757</v>
+        <v>75153</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,16 +13749,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13768,10 +13773,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R121" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13830,10 +13835,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B122" t="n">
-        <v>75153</v>
+        <v>91757</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13841,21 +13846,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R122" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092223</v>
+        <v>128092222</v>
       </c>
       <c r="B125" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,34 +14132,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733389</v>
+        <v>733395</v>
       </c>
       <c r="R125" t="n">
-        <v>7102564</v>
+        <v>7102558</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14192,6 +14200,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14218,10 +14231,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092222</v>
+        <v>128092223</v>
       </c>
       <c r="B126" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14229,42 +14242,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733395</v>
+        <v>733389</v>
       </c>
       <c r="R126" t="n">
-        <v>7102558</v>
+        <v>7102564</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14297,11 +14302,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15288,10 +15288,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128092219</v>
+        <v>128092203</v>
       </c>
       <c r="B137" t="n">
-        <v>82870</v>
+        <v>91350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15299,21 +15299,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>733363</v>
+        <v>733128</v>
       </c>
       <c r="R137" t="n">
-        <v>7102450</v>
+        <v>7102020</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15385,10 +15385,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128092203</v>
+        <v>128092219</v>
       </c>
       <c r="B138" t="n">
-        <v>91350</v>
+        <v>82870</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15396,21 +15396,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15420,10 +15420,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>733128</v>
+        <v>733363</v>
       </c>
       <c r="R138" t="n">
-        <v>7102020</v>
+        <v>7102450</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092221</v>
+        <v>128092246</v>
       </c>
       <c r="B140" t="n">
-        <v>79029</v>
+        <v>91757</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,21 +15590,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15614,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733376</v>
+        <v>732940</v>
       </c>
       <c r="R140" t="n">
-        <v>7102482</v>
+        <v>7102409</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15676,10 +15671,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B141" t="n">
-        <v>91757</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15687,16 +15682,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R141" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,32 +15962,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092229</v>
+        <v>128092212</v>
       </c>
       <c r="B144" t="n">
-        <v>82870</v>
+        <v>91315</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733361</v>
+        <v>733283</v>
       </c>
       <c r="R144" t="n">
-        <v>7102699</v>
+        <v>7102190</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16258,32 +16258,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092212</v>
+        <v>128092229</v>
       </c>
       <c r="B147" t="n">
-        <v>91315</v>
+        <v>82870</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733283</v>
+        <v>733361</v>
       </c>
       <c r="R147" t="n">
-        <v>7102190</v>
+        <v>7102699</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16452,32 +16452,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092233</v>
+        <v>128092205</v>
       </c>
       <c r="B149" t="n">
-        <v>91315</v>
+        <v>91350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733179</v>
+        <v>733214</v>
       </c>
       <c r="R149" t="n">
-        <v>7102677</v>
+        <v>7102100</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16646,32 +16646,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092205</v>
+        <v>128092233</v>
       </c>
       <c r="B151" t="n">
-        <v>91350</v>
+        <v>91315</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733214</v>
+        <v>733179</v>
       </c>
       <c r="R151" t="n">
-        <v>7102100</v>
+        <v>7102677</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -10116,53 +10116,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127265356</v>
+        <v>127265352</v>
       </c>
       <c r="B85" t="n">
-        <v>98468</v>
+        <v>57669</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733288</v>
+        <v>733152</v>
       </c>
       <c r="R85" t="n">
-        <v>7102194</v>
+        <v>7101994</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10199,7 +10191,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
+          <t>Färska hål</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10208,7 +10200,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10227,45 +10218,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127265352</v>
+        <v>127265356</v>
       </c>
       <c r="B86" t="n">
-        <v>57669</v>
+        <v>98469</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733152</v>
+        <v>733288</v>
       </c>
       <c r="R86" t="n">
-        <v>7101994</v>
+        <v>7102194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10302,7 +10301,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska hål</t>
+          <t>Stort antal plantor på en yta ca 5-10 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10311,6 +10310,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10951,7 +10951,7 @@
         <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352833</v>
+        <v>127352846</v>
       </c>
       <c r="B100" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,42 +11661,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733067</v>
+        <v>733141</v>
       </c>
       <c r="R100" t="n">
-        <v>7102180</v>
+        <v>7102155</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11852,10 +11844,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127352846</v>
+        <v>127352833</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11863,34 +11855,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>733141</v>
+        <v>733067</v>
       </c>
       <c r="R102" t="n">
-        <v>7102155</v>
+        <v>7102180</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352831</v>
+        <v>127352830</v>
       </c>
       <c r="B104" t="n">
-        <v>91300</v>
+        <v>57832</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>733269</v>
+        <v>732870</v>
       </c>
       <c r="R104" t="n">
-        <v>7102176</v>
+        <v>7102344</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352857</v>
+        <v>127352831</v>
       </c>
       <c r="B105" t="n">
-        <v>75145</v>
+        <v>91301</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733195</v>
+        <v>733269</v>
       </c>
       <c r="R105" t="n">
-        <v>7102084</v>
+        <v>7102176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352830</v>
+        <v>127352857</v>
       </c>
       <c r="B106" t="n">
-        <v>57832</v>
+        <v>75145</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732870</v>
+        <v>733195</v>
       </c>
       <c r="R106" t="n">
-        <v>7102344</v>
+        <v>7102084</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12447,10 +12447,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127352848</v>
+        <v>127352825</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12458,21 +12458,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12482,10 +12482,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732920</v>
+        <v>733193</v>
       </c>
       <c r="R108" t="n">
-        <v>7102396</v>
+        <v>7102147</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12544,10 +12544,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127352825</v>
+        <v>127352848</v>
       </c>
       <c r="B109" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12555,21 +12555,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12579,10 +12579,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>733193</v>
+        <v>732920</v>
       </c>
       <c r="R109" t="n">
-        <v>7102147</v>
+        <v>7102396</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12741,7 +12741,7 @@
         <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>91300</v>
+        <v>91301</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13425,53 +13425,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352835</v>
+        <v>127352823</v>
       </c>
       <c r="B118" t="n">
-        <v>57669</v>
+        <v>91709</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>733013</v>
+        <v>732915</v>
       </c>
       <c r="R118" t="n">
-        <v>7102291</v>
+        <v>7102363</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13506,12 +13498,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13530,7 +13528,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127352836</v>
+        <v>127352835</v>
       </c>
       <c r="B119" t="n">
         <v>57669</v>
@@ -13573,10 +13571,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>732906</v>
+        <v>733013</v>
       </c>
       <c r="R119" t="n">
-        <v>7102369</v>
+        <v>7102291</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13635,45 +13633,53 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127352823</v>
+        <v>127352836</v>
       </c>
       <c r="B120" t="n">
-        <v>91708</v>
+        <v>57669</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>732915</v>
+        <v>732906</v>
       </c>
       <c r="R120" t="n">
-        <v>7102363</v>
+        <v>7102369</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13708,18 +13714,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>128092215</v>
       </c>
       <c r="B122" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>128092251</v>
       </c>
       <c r="B123" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>128092231</v>
       </c>
       <c r="B124" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092222</v>
+        <v>128092239</v>
       </c>
       <c r="B125" t="n">
-        <v>57672</v>
+        <v>91758</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,42 +14132,29 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733395</v>
+        <v>733324</v>
       </c>
       <c r="R125" t="n">
-        <v>7102558</v>
+        <v>7102525</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,11 +14187,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14234,7 +14216,7 @@
         <v>128092223</v>
       </c>
       <c r="B126" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14328,10 +14310,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092239</v>
+        <v>128092222</v>
       </c>
       <c r="B127" t="n">
-        <v>91757</v>
+        <v>57672</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14339,29 +14321,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733324</v>
+        <v>733395</v>
       </c>
       <c r="R127" t="n">
-        <v>7102525</v>
+        <v>7102558</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14394,6 +14389,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14423,7 +14423,7 @@
         <v>128092202</v>
       </c>
       <c r="B128" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>128092244</v>
       </c>
       <c r="B129" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14716,27 +14716,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092206</v>
+        <v>128092238</v>
       </c>
       <c r="B131" t="n">
-        <v>91757</v>
+        <v>105507</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6040186</v>
+        <v>221144</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14746,10 +14751,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733214</v>
+        <v>733339</v>
       </c>
       <c r="R131" t="n">
-        <v>7102100</v>
+        <v>7102561</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14808,32 +14813,27 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092238</v>
+        <v>128092206</v>
       </c>
       <c r="B132" t="n">
-        <v>105506</v>
+        <v>91758</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733339</v>
+        <v>733214</v>
       </c>
       <c r="R132" t="n">
-        <v>7102561</v>
+        <v>7102100</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14908,7 +14908,7 @@
         <v>128092240</v>
       </c>
       <c r="B133" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>128092224</v>
       </c>
       <c r="B134" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>128092249</v>
       </c>
       <c r="B136" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15288,10 +15288,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128092203</v>
+        <v>128092219</v>
       </c>
       <c r="B137" t="n">
-        <v>91350</v>
+        <v>82870</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15299,21 +15299,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>733128</v>
+        <v>733363</v>
       </c>
       <c r="R137" t="n">
-        <v>7102020</v>
+        <v>7102450</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15385,10 +15385,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128092219</v>
+        <v>128092203</v>
       </c>
       <c r="B138" t="n">
-        <v>82870</v>
+        <v>91351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15396,21 +15396,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15420,10 +15420,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>733363</v>
+        <v>733128</v>
       </c>
       <c r="R138" t="n">
-        <v>7102450</v>
+        <v>7102020</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B139" t="n">
-        <v>91368</v>
+        <v>91758</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15512,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R139" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15574,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092246</v>
+        <v>128092237</v>
       </c>
       <c r="B140" t="n">
-        <v>91757</v>
+        <v>91369</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,16 +15585,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>732940</v>
+        <v>733337</v>
       </c>
       <c r="R140" t="n">
-        <v>7102409</v>
+        <v>7102597</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15771,7 +15771,7 @@
         <v>128092208</v>
       </c>
       <c r="B142" t="n">
-        <v>91708</v>
+        <v>91709</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>128092211</v>
       </c>
       <c r="B143" t="n">
-        <v>91300</v>
+        <v>91301</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>128092212</v>
       </c>
       <c r="B144" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16161,10 +16161,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092213</v>
+        <v>128092229</v>
       </c>
       <c r="B146" t="n">
-        <v>88753</v>
+        <v>82870</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16172,21 +16172,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733347</v>
+        <v>733361</v>
       </c>
       <c r="R146" t="n">
-        <v>7102250</v>
+        <v>7102699</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16258,10 +16258,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092229</v>
+        <v>128092213</v>
       </c>
       <c r="B147" t="n">
-        <v>82870</v>
+        <v>88754</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16269,21 +16269,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16293,10 +16293,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733361</v>
+        <v>733347</v>
       </c>
       <c r="R147" t="n">
-        <v>7102699</v>
+        <v>7102250</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16452,32 +16452,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B149" t="n">
-        <v>91350</v>
+        <v>100624</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R149" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092218</v>
+        <v>128092205</v>
       </c>
       <c r="B150" t="n">
-        <v>100623</v>
+        <v>91351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733367</v>
+        <v>733214</v>
       </c>
       <c r="R150" t="n">
-        <v>7102430</v>
+        <v>7102100</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16649,7 +16649,7 @@
         <v>128092233</v>
       </c>
       <c r="B151" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -10951,7 +10951,7 @@
         <v>127352845</v>
       </c>
       <c r="B93" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>127352822</v>
       </c>
       <c r="B95" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>127352828</v>
       </c>
       <c r="B98" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127352846</v>
+        <v>127352853</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11661,21 +11661,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11685,10 +11685,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>733141</v>
+        <v>733168</v>
       </c>
       <c r="R100" t="n">
-        <v>7102155</v>
+        <v>7102021</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11747,10 +11747,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127352853</v>
+        <v>127352846</v>
       </c>
       <c r="B101" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11758,21 +11758,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>733168</v>
+        <v>733141</v>
       </c>
       <c r="R101" t="n">
-        <v>7102021</v>
+        <v>7102155</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11952,7 +11952,7 @@
         <v>127352824</v>
       </c>
       <c r="B103" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127352830</v>
+        <v>127352831</v>
       </c>
       <c r="B104" t="n">
-        <v>57832</v>
+        <v>91302</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12057,21 +12057,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>112</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12081,10 +12081,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>732870</v>
+        <v>733269</v>
       </c>
       <c r="R104" t="n">
-        <v>7102344</v>
+        <v>7102176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12143,10 +12143,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127352831</v>
+        <v>127352857</v>
       </c>
       <c r="B105" t="n">
-        <v>91301</v>
+        <v>75145</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12154,21 +12154,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12178,10 +12178,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>733269</v>
+        <v>733195</v>
       </c>
       <c r="R105" t="n">
-        <v>7102176</v>
+        <v>7102084</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127352857</v>
+        <v>127352830</v>
       </c>
       <c r="B106" t="n">
-        <v>75145</v>
+        <v>57832</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12251,21 +12251,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>733195</v>
+        <v>732870</v>
       </c>
       <c r="R106" t="n">
-        <v>7102084</v>
+        <v>7102344</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12450,7 +12450,7 @@
         <v>127352825</v>
       </c>
       <c r="B108" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>127352832</v>
       </c>
       <c r="B111" t="n">
-        <v>91301</v>
+        <v>91302</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>127352827</v>
       </c>
       <c r="B114" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13231,32 +13231,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127352854</v>
+        <v>127352823</v>
       </c>
       <c r="B116" t="n">
-        <v>82870</v>
+        <v>91710</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>732861</v>
+        <v>732915</v>
       </c>
       <c r="R116" t="n">
-        <v>7102297</v>
+        <v>7102363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13304,12 +13304,18 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13328,10 +13334,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127352847</v>
+        <v>127352854</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13339,21 +13345,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13363,10 +13369,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>733006</v>
+        <v>732861</v>
       </c>
       <c r="R117" t="n">
-        <v>7102273</v>
+        <v>7102297</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13425,32 +13431,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127352823</v>
+        <v>127352847</v>
       </c>
       <c r="B118" t="n">
-        <v>91709</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13460,10 +13466,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>732915</v>
+        <v>733006</v>
       </c>
       <c r="R118" t="n">
-        <v>7102363</v>
+        <v>7102273</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13498,18 +13504,12 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ej mikroskoperad. Torde dock var Brevispora eller exilis. Alla ulltickeporingarna har liknande miljökrav och föreslås rödlistas till nästa rödlista.</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>128092215</v>
       </c>
       <c r="B122" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>128092251</v>
       </c>
       <c r="B123" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092231</v>
+        <v>128092223</v>
       </c>
       <c r="B124" t="n">
-        <v>91369</v>
+        <v>91352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,21 +14035,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733194</v>
+        <v>733389</v>
       </c>
       <c r="R124" t="n">
-        <v>7102684</v>
+        <v>7102564</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092239</v>
+        <v>128092231</v>
       </c>
       <c r="B125" t="n">
-        <v>91758</v>
+        <v>91370</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,16 +14132,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14151,10 +14156,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733324</v>
+        <v>733194</v>
       </c>
       <c r="R125" t="n">
-        <v>7102525</v>
+        <v>7102684</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14213,10 +14218,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092223</v>
+        <v>128092222</v>
       </c>
       <c r="B126" t="n">
-        <v>91351</v>
+        <v>57672</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14224,34 +14229,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733389</v>
+        <v>733395</v>
       </c>
       <c r="R126" t="n">
-        <v>7102564</v>
+        <v>7102558</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14284,6 +14297,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14310,10 +14328,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092222</v>
+        <v>128092239</v>
       </c>
       <c r="B127" t="n">
-        <v>57672</v>
+        <v>91759</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14321,42 +14339,29 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733395</v>
+        <v>733324</v>
       </c>
       <c r="R127" t="n">
-        <v>7102558</v>
+        <v>7102525</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14389,11 +14394,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14423,7 +14423,7 @@
         <v>128092202</v>
       </c>
       <c r="B128" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>128092244</v>
       </c>
       <c r="B129" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14614,50 +14614,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092235</v>
+        <v>128092238</v>
       </c>
       <c r="B130" t="n">
-        <v>57669</v>
+        <v>105508</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733171</v>
+        <v>733339</v>
       </c>
       <c r="R130" t="n">
-        <v>7102645</v>
+        <v>7102561</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14716,45 +14711,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B131" t="n">
-        <v>105507</v>
+        <v>57669</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R131" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14816,7 +14816,7 @@
         <v>128092206</v>
       </c>
       <c r="B132" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>128092240</v>
       </c>
       <c r="B133" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>128092224</v>
       </c>
       <c r="B134" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15094,32 +15094,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128092247</v>
+        <v>128092249</v>
       </c>
       <c r="B135" t="n">
-        <v>82870</v>
+        <v>92642</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>732914</v>
+        <v>732847</v>
       </c>
       <c r="R135" t="n">
-        <v>7102401</v>
+        <v>7102277</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15191,32 +15191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128092249</v>
+        <v>128092247</v>
       </c>
       <c r="B136" t="n">
-        <v>92641</v>
+        <v>82870</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15226,10 +15226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>732847</v>
+        <v>732914</v>
       </c>
       <c r="R136" t="n">
-        <v>7102277</v>
+        <v>7102401</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15288,10 +15288,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128092219</v>
+        <v>128092203</v>
       </c>
       <c r="B137" t="n">
-        <v>82870</v>
+        <v>91352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15299,21 +15299,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>733363</v>
+        <v>733128</v>
       </c>
       <c r="R137" t="n">
-        <v>7102450</v>
+        <v>7102020</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15385,10 +15385,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128092203</v>
+        <v>128092219</v>
       </c>
       <c r="B138" t="n">
-        <v>91351</v>
+        <v>82870</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15396,21 +15396,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15420,10 +15420,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>733128</v>
+        <v>733363</v>
       </c>
       <c r="R138" t="n">
-        <v>7102020</v>
+        <v>7102450</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092246</v>
+        <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>91758</v>
+        <v>91370</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,16 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15512,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>732940</v>
+        <v>733337</v>
       </c>
       <c r="R139" t="n">
-        <v>7102409</v>
+        <v>7102597</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15574,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B140" t="n">
-        <v>91369</v>
+        <v>91759</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15585,21 +15590,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R140" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15771,7 +15771,7 @@
         <v>128092208</v>
       </c>
       <c r="B142" t="n">
-        <v>91709</v>
+        <v>91710</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>128092211</v>
       </c>
       <c r="B143" t="n">
-        <v>91301</v>
+        <v>91302</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15962,32 +15962,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092212</v>
+        <v>128092229</v>
       </c>
       <c r="B144" t="n">
-        <v>91316</v>
+        <v>82870</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733283</v>
+        <v>733361</v>
       </c>
       <c r="R144" t="n">
-        <v>7102190</v>
+        <v>7102699</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16059,10 +16059,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092214</v>
+        <v>128092213</v>
       </c>
       <c r="B145" t="n">
-        <v>57669</v>
+        <v>88755</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16070,39 +16070,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733358</v>
+        <v>733347</v>
       </c>
       <c r="R145" t="n">
-        <v>7102265</v>
+        <v>7102250</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16161,32 +16156,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092229</v>
+        <v>128092212</v>
       </c>
       <c r="B146" t="n">
-        <v>82870</v>
+        <v>91317</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16196,10 +16191,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733361</v>
+        <v>733283</v>
       </c>
       <c r="R146" t="n">
-        <v>7102699</v>
+        <v>7102190</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16258,10 +16253,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092213</v>
+        <v>128092214</v>
       </c>
       <c r="B147" t="n">
-        <v>88754</v>
+        <v>57669</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16269,34 +16264,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733347</v>
+        <v>733358</v>
       </c>
       <c r="R147" t="n">
-        <v>7102250</v>
+        <v>7102265</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16452,32 +16452,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092218</v>
+        <v>128092241</v>
       </c>
       <c r="B149" t="n">
-        <v>100624</v>
+        <v>91759</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1365</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16482,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733367</v>
+        <v>733206</v>
       </c>
       <c r="R149" t="n">
-        <v>7102430</v>
+        <v>7102446</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16552,7 +16547,7 @@
         <v>128092205</v>
       </c>
       <c r="B150" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16646,10 +16641,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092233</v>
+        <v>128092218</v>
       </c>
       <c r="B151" t="n">
-        <v>91316</v>
+        <v>100625</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16657,21 +16652,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16676,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733179</v>
+        <v>733367</v>
       </c>
       <c r="R151" t="n">
-        <v>7102677</v>
+        <v>7102430</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16743,27 +16738,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092241</v>
+        <v>128092233</v>
       </c>
       <c r="B152" t="n">
-        <v>91758</v>
+        <v>91317</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733206</v>
+        <v>733179</v>
       </c>
       <c r="R152" t="n">
-        <v>7102446</v>
+        <v>7102677</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092223</v>
+        <v>128092222</v>
       </c>
       <c r="B124" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,34 +14035,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733389</v>
+        <v>733395</v>
       </c>
       <c r="R124" t="n">
-        <v>7102564</v>
+        <v>7102558</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14095,6 +14103,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14121,10 +14134,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092231</v>
+        <v>128092223</v>
       </c>
       <c r="B125" t="n">
-        <v>91370</v>
+        <v>91352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,21 +14145,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14156,10 +14169,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733194</v>
+        <v>733389</v>
       </c>
       <c r="R125" t="n">
-        <v>7102684</v>
+        <v>7102564</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14218,10 +14231,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092222</v>
+        <v>128092231</v>
       </c>
       <c r="B126" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14229,42 +14242,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733395</v>
+        <v>733194</v>
       </c>
       <c r="R126" t="n">
-        <v>7102558</v>
+        <v>7102684</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14297,11 +14302,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14614,32 +14614,27 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092238</v>
+        <v>128092206</v>
       </c>
       <c r="B130" t="n">
-        <v>105508</v>
+        <v>91759</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14649,10 +14644,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733339</v>
+        <v>733214</v>
       </c>
       <c r="R130" t="n">
-        <v>7102561</v>
+        <v>7102100</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14813,27 +14808,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092206</v>
+        <v>128092238</v>
       </c>
       <c r="B132" t="n">
-        <v>91759</v>
+        <v>105508</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6040186</v>
+        <v>221144</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733214</v>
+        <v>733339</v>
       </c>
       <c r="R132" t="n">
-        <v>7102100</v>
+        <v>7102561</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15094,32 +15094,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128092249</v>
+        <v>128092247</v>
       </c>
       <c r="B135" t="n">
-        <v>92642</v>
+        <v>82870</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>732847</v>
+        <v>732914</v>
       </c>
       <c r="R135" t="n">
-        <v>7102277</v>
+        <v>7102401</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15191,32 +15191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128092247</v>
+        <v>128092249</v>
       </c>
       <c r="B136" t="n">
-        <v>82870</v>
+        <v>92642</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15226,10 +15226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>732914</v>
+        <v>732847</v>
       </c>
       <c r="R136" t="n">
-        <v>7102401</v>
+        <v>7102277</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,16 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R140" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092221</v>
+        <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15687,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733376</v>
+        <v>732940</v>
       </c>
       <c r="R141" t="n">
-        <v>7102482</v>
+        <v>7102409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092229</v>
+        <v>128092213</v>
       </c>
       <c r="B144" t="n">
-        <v>82870</v>
+        <v>88755</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,21 +15973,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15997,10 +15997,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733361</v>
+        <v>733347</v>
       </c>
       <c r="R144" t="n">
-        <v>7102699</v>
+        <v>7102250</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16059,10 +16059,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092213</v>
+        <v>128092229</v>
       </c>
       <c r="B145" t="n">
-        <v>88755</v>
+        <v>82870</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16070,21 +16070,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16094,10 +16094,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733347</v>
+        <v>733361</v>
       </c>
       <c r="R145" t="n">
-        <v>7102250</v>
+        <v>7102699</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16452,10 +16452,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092241</v>
+        <v>128092205</v>
       </c>
       <c r="B149" t="n">
-        <v>91759</v>
+        <v>91352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16463,16 +16463,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16482,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733206</v>
+        <v>733214</v>
       </c>
       <c r="R149" t="n">
-        <v>7102446</v>
+        <v>7102100</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16544,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B150" t="n">
-        <v>91352</v>
+        <v>100625</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16579,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R150" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16641,10 +16646,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092218</v>
+        <v>128092233</v>
       </c>
       <c r="B151" t="n">
-        <v>100625</v>
+        <v>91317</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16652,21 +16657,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16676,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733367</v>
+        <v>733179</v>
       </c>
       <c r="R151" t="n">
-        <v>7102430</v>
+        <v>7102677</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16738,32 +16743,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092233</v>
+        <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>91317</v>
+        <v>91759</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733179</v>
+        <v>733206</v>
       </c>
       <c r="R152" t="n">
-        <v>7102677</v>
+        <v>7102446</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B139" t="n">
-        <v>91370</v>
+        <v>91759</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15512,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R139" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15574,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B140" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,21 +15585,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15614,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R140" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15676,10 +15671,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B141" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15687,16 +15682,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R141" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092213</v>
+        <v>128092214</v>
       </c>
       <c r="B144" t="n">
-        <v>88755</v>
+        <v>57669</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,34 +15973,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733347</v>
+        <v>733358</v>
       </c>
       <c r="R144" t="n">
-        <v>7102250</v>
+        <v>7102265</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16059,10 +16064,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092229</v>
+        <v>128092213</v>
       </c>
       <c r="B145" t="n">
-        <v>82870</v>
+        <v>88755</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16070,21 +16075,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16094,10 +16099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733361</v>
+        <v>733347</v>
       </c>
       <c r="R145" t="n">
-        <v>7102699</v>
+        <v>7102250</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16156,32 +16161,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092212</v>
+        <v>128092229</v>
       </c>
       <c r="B146" t="n">
-        <v>91317</v>
+        <v>82870</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16191,10 +16196,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733283</v>
+        <v>733361</v>
       </c>
       <c r="R146" t="n">
-        <v>7102190</v>
+        <v>7102699</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16253,50 +16258,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092214</v>
+        <v>128092212</v>
       </c>
       <c r="B147" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733358</v>
+        <v>733283</v>
       </c>
       <c r="R147" t="n">
-        <v>7102265</v>
+        <v>7102190</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092246</v>
+        <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>91759</v>
+        <v>91370</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,16 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15512,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>732940</v>
+        <v>733337</v>
       </c>
       <c r="R139" t="n">
-        <v>7102409</v>
+        <v>7102597</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15574,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092237</v>
+        <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15585,21 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733337</v>
+        <v>733376</v>
       </c>
       <c r="R140" t="n">
-        <v>7102597</v>
+        <v>7102482</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092221</v>
+        <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15687,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733376</v>
+        <v>732940</v>
       </c>
       <c r="R141" t="n">
-        <v>7102482</v>
+        <v>7102409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092214</v>
+        <v>128092213</v>
       </c>
       <c r="B144" t="n">
-        <v>57669</v>
+        <v>88755</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,39 +15973,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733358</v>
+        <v>733347</v>
       </c>
       <c r="R144" t="n">
-        <v>7102265</v>
+        <v>7102250</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16064,10 +16059,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092213</v>
+        <v>128092229</v>
       </c>
       <c r="B145" t="n">
-        <v>88755</v>
+        <v>82870</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16075,21 +16070,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16099,10 +16094,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733347</v>
+        <v>733361</v>
       </c>
       <c r="R145" t="n">
-        <v>7102250</v>
+        <v>7102699</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16161,32 +16156,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092229</v>
+        <v>128092212</v>
       </c>
       <c r="B146" t="n">
-        <v>82870</v>
+        <v>91317</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16196,10 +16191,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733361</v>
+        <v>733283</v>
       </c>
       <c r="R146" t="n">
-        <v>7102699</v>
+        <v>7102190</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16258,45 +16253,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092212</v>
+        <v>128092214</v>
       </c>
       <c r="B147" t="n">
-        <v>91317</v>
+        <v>57669</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733283</v>
+        <v>733358</v>
       </c>
       <c r="R147" t="n">
-        <v>7102190</v>
+        <v>7102265</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092222</v>
+        <v>128092231</v>
       </c>
       <c r="B124" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,42 +14035,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733395</v>
+        <v>733194</v>
       </c>
       <c r="R124" t="n">
-        <v>7102558</v>
+        <v>7102684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14103,11 +14095,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14134,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092223</v>
+        <v>128092222</v>
       </c>
       <c r="B125" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14145,34 +14132,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733389</v>
+        <v>733395</v>
       </c>
       <c r="R125" t="n">
-        <v>7102564</v>
+        <v>7102558</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14205,6 +14200,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14231,10 +14231,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092231</v>
+        <v>128092223</v>
       </c>
       <c r="B126" t="n">
-        <v>91370</v>
+        <v>91352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14242,21 +14242,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733194</v>
+        <v>733389</v>
       </c>
       <c r="R126" t="n">
-        <v>7102684</v>
+        <v>7102564</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14614,10 +14614,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092206</v>
+        <v>128092235</v>
       </c>
       <c r="B130" t="n">
-        <v>91759</v>
+        <v>57669</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14625,29 +14625,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733214</v>
+        <v>733171</v>
       </c>
       <c r="R130" t="n">
-        <v>7102100</v>
+        <v>7102645</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14706,50 +14716,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092235</v>
+        <v>128092238</v>
       </c>
       <c r="B131" t="n">
-        <v>57669</v>
+        <v>105508</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733171</v>
+        <v>733339</v>
       </c>
       <c r="R131" t="n">
-        <v>7102645</v>
+        <v>7102561</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14808,32 +14813,27 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092238</v>
+        <v>128092206</v>
       </c>
       <c r="B132" t="n">
-        <v>105508</v>
+        <v>91759</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733339</v>
+        <v>733214</v>
       </c>
       <c r="R132" t="n">
-        <v>7102561</v>
+        <v>7102100</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B139" t="n">
-        <v>91370</v>
+        <v>91759</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15512,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R139" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15574,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B140" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,21 +15585,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15614,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R140" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15676,10 +15671,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B141" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15687,16 +15682,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R141" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16452,10 +16452,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092205</v>
+        <v>128092241</v>
       </c>
       <c r="B149" t="n">
-        <v>91352</v>
+        <v>91759</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16463,21 +16463,16 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16482,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733214</v>
+        <v>733206</v>
       </c>
       <c r="R149" t="n">
-        <v>7102100</v>
+        <v>7102446</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16544,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092218</v>
+        <v>128092205</v>
       </c>
       <c r="B150" t="n">
-        <v>100625</v>
+        <v>91352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16579,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733367</v>
+        <v>733214</v>
       </c>
       <c r="R150" t="n">
-        <v>7102430</v>
+        <v>7102100</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,10 +16641,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092233</v>
+        <v>128092218</v>
       </c>
       <c r="B151" t="n">
-        <v>91317</v>
+        <v>100625</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16657,21 +16652,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16676,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733179</v>
+        <v>733367</v>
       </c>
       <c r="R151" t="n">
-        <v>7102677</v>
+        <v>7102430</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16743,27 +16738,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092241</v>
+        <v>128092233</v>
       </c>
       <c r="B152" t="n">
-        <v>91759</v>
+        <v>91317</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733206</v>
+        <v>733179</v>
       </c>
       <c r="R152" t="n">
-        <v>7102446</v>
+        <v>7102677</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -14614,10 +14614,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092235</v>
+        <v>128092206</v>
       </c>
       <c r="B130" t="n">
-        <v>57669</v>
+        <v>91759</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14625,39 +14625,29 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733171</v>
+        <v>733214</v>
       </c>
       <c r="R130" t="n">
-        <v>7102645</v>
+        <v>7102100</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14716,45 +14706,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B131" t="n">
-        <v>105508</v>
+        <v>57669</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R131" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14813,27 +14808,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092206</v>
+        <v>128092238</v>
       </c>
       <c r="B132" t="n">
-        <v>91759</v>
+        <v>105508</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6040186</v>
+        <v>221144</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733214</v>
+        <v>733339</v>
       </c>
       <c r="R132" t="n">
-        <v>7102100</v>
+        <v>7102561</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092246</v>
+        <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>91759</v>
+        <v>91370</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,16 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15512,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>732940</v>
+        <v>733337</v>
       </c>
       <c r="R139" t="n">
-        <v>7102409</v>
+        <v>7102597</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15574,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092237</v>
+        <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15585,21 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733337</v>
+        <v>733376</v>
       </c>
       <c r="R140" t="n">
-        <v>7102597</v>
+        <v>7102482</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092221</v>
+        <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15687,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733376</v>
+        <v>732940</v>
       </c>
       <c r="R141" t="n">
-        <v>7102482</v>
+        <v>7102409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16452,10 +16452,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092241</v>
+        <v>128092205</v>
       </c>
       <c r="B149" t="n">
-        <v>91759</v>
+        <v>91352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16463,16 +16463,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16482,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733206</v>
+        <v>733214</v>
       </c>
       <c r="R149" t="n">
-        <v>7102446</v>
+        <v>7102100</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16544,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B150" t="n">
-        <v>91352</v>
+        <v>100625</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16579,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R150" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16641,10 +16646,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092218</v>
+        <v>128092233</v>
       </c>
       <c r="B151" t="n">
-        <v>100625</v>
+        <v>91317</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16652,21 +16657,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16676,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733367</v>
+        <v>733179</v>
       </c>
       <c r="R151" t="n">
-        <v>7102430</v>
+        <v>7102677</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16738,32 +16743,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092233</v>
+        <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>91317</v>
+        <v>91759</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733179</v>
+        <v>733206</v>
       </c>
       <c r="R152" t="n">
-        <v>7102677</v>
+        <v>7102446</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092231</v>
+        <v>128092222</v>
       </c>
       <c r="B124" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,34 +14035,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733194</v>
+        <v>733395</v>
       </c>
       <c r="R124" t="n">
-        <v>7102684</v>
+        <v>7102558</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14095,6 +14103,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14121,10 +14134,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092222</v>
+        <v>128092223</v>
       </c>
       <c r="B125" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,42 +14145,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733395</v>
+        <v>733389</v>
       </c>
       <c r="R125" t="n">
-        <v>7102558</v>
+        <v>7102564</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,11 +14205,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14231,10 +14231,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092223</v>
+        <v>128092231</v>
       </c>
       <c r="B126" t="n">
-        <v>91352</v>
+        <v>91370</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14242,21 +14242,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733389</v>
+        <v>733194</v>
       </c>
       <c r="R126" t="n">
-        <v>7102564</v>
+        <v>7102684</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B139" t="n">
-        <v>91370</v>
+        <v>91759</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15512,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R139" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15574,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B140" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,21 +15585,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15614,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R140" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15676,10 +15671,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B141" t="n">
-        <v>91759</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15687,16 +15682,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R141" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092213</v>
+        <v>128092214</v>
       </c>
       <c r="B144" t="n">
-        <v>88755</v>
+        <v>57669</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,34 +15973,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733347</v>
+        <v>733358</v>
       </c>
       <c r="R144" t="n">
-        <v>7102250</v>
+        <v>7102265</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16059,10 +16064,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092229</v>
+        <v>128092213</v>
       </c>
       <c r="B145" t="n">
-        <v>82870</v>
+        <v>88755</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16070,21 +16075,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16094,10 +16099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733361</v>
+        <v>733347</v>
       </c>
       <c r="R145" t="n">
-        <v>7102699</v>
+        <v>7102250</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16156,32 +16161,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092212</v>
+        <v>128092229</v>
       </c>
       <c r="B146" t="n">
-        <v>91317</v>
+        <v>82870</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16191,10 +16196,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733283</v>
+        <v>733361</v>
       </c>
       <c r="R146" t="n">
-        <v>7102190</v>
+        <v>7102699</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16253,50 +16258,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092214</v>
+        <v>128092212</v>
       </c>
       <c r="B147" t="n">
-        <v>57669</v>
+        <v>91317</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733358</v>
+        <v>733283</v>
       </c>
       <c r="R147" t="n">
-        <v>7102265</v>
+        <v>7102190</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092246</v>
+        <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>91759</v>
+        <v>91370</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,16 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15512,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>732940</v>
+        <v>733337</v>
       </c>
       <c r="R139" t="n">
-        <v>7102409</v>
+        <v>7102597</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15574,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092237</v>
+        <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15585,21 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733337</v>
+        <v>733376</v>
       </c>
       <c r="R140" t="n">
-        <v>7102597</v>
+        <v>7102482</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092221</v>
+        <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>79029</v>
+        <v>91759</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15687,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733376</v>
+        <v>732940</v>
       </c>
       <c r="R141" t="n">
-        <v>7102482</v>
+        <v>7102409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B121" t="n">
-        <v>75153</v>
+        <v>91767</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,21 +13749,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13773,10 +13768,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R121" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13835,10 +13830,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B122" t="n">
-        <v>91759</v>
+        <v>75156</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13846,16 +13841,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R122" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13930,7 +13930,7 @@
         <v>128092251</v>
       </c>
       <c r="B123" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092222</v>
+        <v>128092231</v>
       </c>
       <c r="B124" t="n">
-        <v>57672</v>
+        <v>91378</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,42 +14035,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733395</v>
+        <v>733194</v>
       </c>
       <c r="R124" t="n">
-        <v>7102558</v>
+        <v>7102684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14103,11 +14095,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14134,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092223</v>
+        <v>128092222</v>
       </c>
       <c r="B125" t="n">
-        <v>91352</v>
+        <v>57673</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14145,34 +14132,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733389</v>
+        <v>733395</v>
       </c>
       <c r="R125" t="n">
-        <v>7102564</v>
+        <v>7102558</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14205,6 +14200,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14231,10 +14231,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092231</v>
+        <v>128092239</v>
       </c>
       <c r="B126" t="n">
-        <v>91370</v>
+        <v>91767</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14242,21 +14242,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14266,10 +14261,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733194</v>
+        <v>733324</v>
       </c>
       <c r="R126" t="n">
-        <v>7102684</v>
+        <v>7102525</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14328,10 +14323,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092239</v>
+        <v>128092223</v>
       </c>
       <c r="B127" t="n">
-        <v>91759</v>
+        <v>91360</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14339,16 +14334,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733324</v>
+        <v>733389</v>
       </c>
       <c r="R127" t="n">
-        <v>7102525</v>
+        <v>7102564</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14423,7 +14423,7 @@
         <v>128092202</v>
       </c>
       <c r="B128" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>128092244</v>
       </c>
       <c r="B129" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14614,27 +14614,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092206</v>
+        <v>128092238</v>
       </c>
       <c r="B130" t="n">
-        <v>91759</v>
+        <v>105516</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6040186</v>
+        <v>221144</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14644,10 +14649,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733214</v>
+        <v>733339</v>
       </c>
       <c r="R130" t="n">
-        <v>7102100</v>
+        <v>7102561</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14706,10 +14711,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092235</v>
+        <v>128092206</v>
       </c>
       <c r="B131" t="n">
-        <v>57669</v>
+        <v>91767</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14717,39 +14722,29 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733171</v>
+        <v>733214</v>
       </c>
       <c r="R131" t="n">
-        <v>7102645</v>
+        <v>7102100</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14808,45 +14803,50 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B132" t="n">
-        <v>105508</v>
+        <v>57670</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R132" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14908,7 +14908,7 @@
         <v>128092240</v>
       </c>
       <c r="B133" t="n">
-        <v>91759</v>
+        <v>91767</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>128092224</v>
       </c>
       <c r="B134" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>128092247</v>
       </c>
       <c r="B135" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>128092249</v>
       </c>
       <c r="B136" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>128092203</v>
       </c>
       <c r="B137" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>128092219</v>
       </c>
       <c r="B138" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B139" t="n">
-        <v>91370</v>
+        <v>91767</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15512,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R139" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15582,7 +15577,7 @@
         <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15676,10 +15671,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092246</v>
+        <v>128092237</v>
       </c>
       <c r="B141" t="n">
-        <v>91759</v>
+        <v>91378</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15687,16 +15682,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>732940</v>
+        <v>733337</v>
       </c>
       <c r="R141" t="n">
-        <v>7102409</v>
+        <v>7102597</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15771,7 +15771,7 @@
         <v>128092208</v>
       </c>
       <c r="B142" t="n">
-        <v>91710</v>
+        <v>91718</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>128092211</v>
       </c>
       <c r="B143" t="n">
-        <v>91302</v>
+        <v>91310</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>128092214</v>
       </c>
       <c r="B144" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>128092213</v>
       </c>
       <c r="B145" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>128092229</v>
       </c>
       <c r="B146" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>128092212</v>
       </c>
       <c r="B147" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>128092227</v>
       </c>
       <c r="B148" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16452,32 +16452,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B149" t="n">
-        <v>91352</v>
+        <v>100633</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R149" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092218</v>
+        <v>128092205</v>
       </c>
       <c r="B150" t="n">
-        <v>100625</v>
+        <v>91360</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733367</v>
+        <v>733214</v>
       </c>
       <c r="R150" t="n">
-        <v>7102430</v>
+        <v>7102100</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,32 +16646,27 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092233</v>
+        <v>128092241</v>
       </c>
       <c r="B151" t="n">
-        <v>91317</v>
+        <v>91767</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16676,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733179</v>
+        <v>733206</v>
       </c>
       <c r="R151" t="n">
-        <v>7102677</v>
+        <v>7102446</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16743,27 +16738,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092241</v>
+        <v>128092233</v>
       </c>
       <c r="B152" t="n">
-        <v>91759</v>
+        <v>91325</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733206</v>
+        <v>733179</v>
       </c>
       <c r="R152" t="n">
-        <v>7102446</v>
+        <v>7102677</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B121" t="n">
-        <v>91767</v>
+        <v>75156</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,16 +13749,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13768,10 +13773,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R121" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13830,10 +13835,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B122" t="n">
-        <v>75156</v>
+        <v>91767</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13841,21 +13846,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R122" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092231</v>
+        <v>128092222</v>
       </c>
       <c r="B124" t="n">
-        <v>91378</v>
+        <v>57673</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,34 +14035,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733194</v>
+        <v>733395</v>
       </c>
       <c r="R124" t="n">
-        <v>7102684</v>
+        <v>7102558</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14095,6 +14103,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14121,10 +14134,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092222</v>
+        <v>128092239</v>
       </c>
       <c r="B125" t="n">
-        <v>57673</v>
+        <v>91767</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,42 +14145,29 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733395</v>
+        <v>733324</v>
       </c>
       <c r="R125" t="n">
-        <v>7102558</v>
+        <v>7102525</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,11 +14200,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14231,10 +14226,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092239</v>
+        <v>128092223</v>
       </c>
       <c r="B126" t="n">
-        <v>91767</v>
+        <v>91360</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14242,16 +14237,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733324</v>
+        <v>733389</v>
       </c>
       <c r="R126" t="n">
-        <v>7102525</v>
+        <v>7102564</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14323,10 +14323,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092223</v>
+        <v>128092231</v>
       </c>
       <c r="B127" t="n">
-        <v>91360</v>
+        <v>91378</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14334,21 +14334,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733389</v>
+        <v>733194</v>
       </c>
       <c r="R127" t="n">
-        <v>7102564</v>
+        <v>7102684</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092246</v>
+        <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>91767</v>
+        <v>91378</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,16 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15512,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>732940</v>
+        <v>733337</v>
       </c>
       <c r="R139" t="n">
-        <v>7102409</v>
+        <v>7102597</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>91378</v>
+        <v>91767</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15687,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R141" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092214</v>
+        <v>128092213</v>
       </c>
       <c r="B144" t="n">
-        <v>57670</v>
+        <v>88761</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,39 +15973,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733358</v>
+        <v>733347</v>
       </c>
       <c r="R144" t="n">
-        <v>7102265</v>
+        <v>7102250</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16064,10 +16059,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092213</v>
+        <v>128092229</v>
       </c>
       <c r="B145" t="n">
-        <v>88761</v>
+        <v>82873</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16075,21 +16070,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16099,10 +16094,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733347</v>
+        <v>733361</v>
       </c>
       <c r="R145" t="n">
-        <v>7102250</v>
+        <v>7102699</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16161,32 +16156,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092229</v>
+        <v>128092212</v>
       </c>
       <c r="B146" t="n">
-        <v>82873</v>
+        <v>91325</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16196,10 +16191,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733361</v>
+        <v>733283</v>
       </c>
       <c r="R146" t="n">
-        <v>7102699</v>
+        <v>7102190</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16258,45 +16253,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092212</v>
+        <v>128092214</v>
       </c>
       <c r="B147" t="n">
-        <v>91325</v>
+        <v>57670</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733283</v>
+        <v>733358</v>
       </c>
       <c r="R147" t="n">
-        <v>7102190</v>
+        <v>7102265</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16452,10 +16452,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092218</v>
+        <v>128092233</v>
       </c>
       <c r="B149" t="n">
-        <v>100633</v>
+        <v>91325</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16463,21 +16463,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733367</v>
+        <v>733179</v>
       </c>
       <c r="R149" t="n">
-        <v>7102430</v>
+        <v>7102677</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B150" t="n">
-        <v>91360</v>
+        <v>100633</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R150" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092241</v>
+        <v>128092205</v>
       </c>
       <c r="B151" t="n">
-        <v>91767</v>
+        <v>91360</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16657,16 +16657,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16676,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733206</v>
+        <v>733214</v>
       </c>
       <c r="R151" t="n">
-        <v>7102446</v>
+        <v>7102100</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16738,32 +16743,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092233</v>
+        <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>91325</v>
+        <v>91767</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733179</v>
+        <v>733206</v>
       </c>
       <c r="R152" t="n">
-        <v>7102677</v>
+        <v>7102446</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B121" t="n">
-        <v>75156</v>
+        <v>91859</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,21 +13749,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13773,10 +13768,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R121" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13835,10 +13830,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B122" t="n">
-        <v>91767</v>
+        <v>75171</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13846,16 +13841,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R122" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13930,7 +13930,7 @@
         <v>128092251</v>
       </c>
       <c r="B123" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092222</v>
+        <v>128092223</v>
       </c>
       <c r="B124" t="n">
-        <v>57673</v>
+        <v>91452</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,42 +14035,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733395</v>
+        <v>733389</v>
       </c>
       <c r="R124" t="n">
-        <v>7102558</v>
+        <v>7102564</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14103,11 +14095,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14134,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092239</v>
+        <v>128092231</v>
       </c>
       <c r="B125" t="n">
-        <v>91767</v>
+        <v>91470</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14145,16 +14132,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14164,10 +14156,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733324</v>
+        <v>733194</v>
       </c>
       <c r="R125" t="n">
-        <v>7102525</v>
+        <v>7102684</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14226,10 +14218,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092223</v>
+        <v>128092239</v>
       </c>
       <c r="B126" t="n">
-        <v>91360</v>
+        <v>91859</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14237,21 +14229,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14261,10 +14248,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733389</v>
+        <v>733324</v>
       </c>
       <c r="R126" t="n">
-        <v>7102564</v>
+        <v>7102525</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14323,10 +14310,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092231</v>
+        <v>128092222</v>
       </c>
       <c r="B127" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14334,34 +14321,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733194</v>
+        <v>733395</v>
       </c>
       <c r="R127" t="n">
-        <v>7102684</v>
+        <v>7102558</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14394,6 +14389,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14423,7 +14423,7 @@
         <v>128092202</v>
       </c>
       <c r="B128" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>128092244</v>
       </c>
       <c r="B129" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14614,45 +14614,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B130" t="n">
-        <v>105516</v>
+        <v>57682</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R130" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14711,27 +14716,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092206</v>
+        <v>128092238</v>
       </c>
       <c r="B131" t="n">
-        <v>91767</v>
+        <v>105609</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6040186</v>
+        <v>221144</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14741,10 +14751,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733214</v>
+        <v>733339</v>
       </c>
       <c r="R131" t="n">
-        <v>7102100</v>
+        <v>7102561</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14803,10 +14813,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092235</v>
+        <v>128092206</v>
       </c>
       <c r="B132" t="n">
-        <v>57670</v>
+        <v>91859</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14814,39 +14824,29 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733171</v>
+        <v>733214</v>
       </c>
       <c r="R132" t="n">
-        <v>7102645</v>
+        <v>7102100</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14908,7 +14908,7 @@
         <v>128092240</v>
       </c>
       <c r="B133" t="n">
-        <v>91767</v>
+        <v>91859</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>128092224</v>
       </c>
       <c r="B134" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>128092247</v>
       </c>
       <c r="B135" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>128092249</v>
       </c>
       <c r="B136" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>128092203</v>
       </c>
       <c r="B137" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>128092219</v>
       </c>
       <c r="B138" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B139" t="n">
-        <v>91378</v>
+        <v>91859</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15512,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R139" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15574,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B140" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,21 +15585,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15614,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R140" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15676,10 +15671,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B141" t="n">
-        <v>91767</v>
+        <v>79083</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15687,16 +15682,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R141" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15771,7 +15771,7 @@
         <v>128092208</v>
       </c>
       <c r="B142" t="n">
-        <v>91718</v>
+        <v>91810</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>128092211</v>
       </c>
       <c r="B143" t="n">
-        <v>91310</v>
+        <v>91402</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>128092213</v>
       </c>
       <c r="B144" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>128092229</v>
       </c>
       <c r="B145" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>128092212</v>
       </c>
       <c r="B146" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>128092214</v>
       </c>
       <c r="B147" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>128092227</v>
       </c>
       <c r="B148" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16452,32 +16452,27 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092233</v>
+        <v>128092241</v>
       </c>
       <c r="B149" t="n">
-        <v>91325</v>
+        <v>91859</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16482,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733179</v>
+        <v>733206</v>
       </c>
       <c r="R149" t="n">
-        <v>7102677</v>
+        <v>7102446</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16544,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092218</v>
+        <v>128092205</v>
       </c>
       <c r="B150" t="n">
-        <v>100633</v>
+        <v>91452</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16579,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733367</v>
+        <v>733214</v>
       </c>
       <c r="R150" t="n">
-        <v>7102430</v>
+        <v>7102100</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,32 +16641,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B151" t="n">
-        <v>91360</v>
+        <v>100726</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16676,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R151" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16743,27 +16738,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092241</v>
+        <v>128092233</v>
       </c>
       <c r="B152" t="n">
-        <v>91767</v>
+        <v>91417</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733206</v>
+        <v>733179</v>
       </c>
       <c r="R152" t="n">
-        <v>7102446</v>
+        <v>7102677</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B121" t="n">
-        <v>91859</v>
+        <v>75171</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,16 +13749,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13768,10 +13773,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R121" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13830,10 +13835,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B122" t="n">
-        <v>75171</v>
+        <v>91859</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13841,21 +13846,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R122" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092223</v>
+        <v>128092231</v>
       </c>
       <c r="B124" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,21 +14035,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733389</v>
+        <v>733194</v>
       </c>
       <c r="R124" t="n">
-        <v>7102564</v>
+        <v>7102684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092231</v>
+        <v>128092223</v>
       </c>
       <c r="B125" t="n">
-        <v>91470</v>
+        <v>91452</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,21 +14132,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14156,10 +14156,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733194</v>
+        <v>733389</v>
       </c>
       <c r="R125" t="n">
-        <v>7102684</v>
+        <v>7102564</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14218,10 +14218,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092239</v>
+        <v>128092222</v>
       </c>
       <c r="B126" t="n">
-        <v>91859</v>
+        <v>57685</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14229,29 +14229,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733324</v>
+        <v>733395</v>
       </c>
       <c r="R126" t="n">
-        <v>7102525</v>
+        <v>7102558</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14284,6 +14297,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14310,10 +14328,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092222</v>
+        <v>128092239</v>
       </c>
       <c r="B127" t="n">
-        <v>57685</v>
+        <v>91859</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14321,42 +14339,29 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733395</v>
+        <v>733324</v>
       </c>
       <c r="R127" t="n">
-        <v>7102558</v>
+        <v>7102525</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14389,11 +14394,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15094,32 +15094,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128092247</v>
+        <v>128092249</v>
       </c>
       <c r="B135" t="n">
-        <v>82942</v>
+        <v>92742</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>732914</v>
+        <v>732847</v>
       </c>
       <c r="R135" t="n">
-        <v>7102401</v>
+        <v>7102277</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15191,32 +15191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128092249</v>
+        <v>128092247</v>
       </c>
       <c r="B136" t="n">
-        <v>92742</v>
+        <v>82942</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15226,10 +15226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>732847</v>
+        <v>732914</v>
       </c>
       <c r="R136" t="n">
-        <v>7102277</v>
+        <v>7102401</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092213</v>
+        <v>128092214</v>
       </c>
       <c r="B144" t="n">
-        <v>88853</v>
+        <v>57682</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,34 +15973,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733347</v>
+        <v>733358</v>
       </c>
       <c r="R144" t="n">
-        <v>7102250</v>
+        <v>7102265</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16059,32 +16064,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092229</v>
+        <v>128092212</v>
       </c>
       <c r="B145" t="n">
-        <v>82942</v>
+        <v>91417</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16094,10 +16099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733361</v>
+        <v>733283</v>
       </c>
       <c r="R145" t="n">
-        <v>7102699</v>
+        <v>7102190</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16156,32 +16161,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092212</v>
+        <v>128092213</v>
       </c>
       <c r="B146" t="n">
-        <v>91417</v>
+        <v>88853</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16191,10 +16196,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733283</v>
+        <v>733347</v>
       </c>
       <c r="R146" t="n">
-        <v>7102190</v>
+        <v>7102250</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16253,10 +16258,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092214</v>
+        <v>128092229</v>
       </c>
       <c r="B147" t="n">
-        <v>57682</v>
+        <v>82942</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16264,39 +16269,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733358</v>
+        <v>733361</v>
       </c>
       <c r="R147" t="n">
-        <v>7102265</v>
+        <v>7102699</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16452,27 +16452,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092241</v>
+        <v>128092233</v>
       </c>
       <c r="B149" t="n">
-        <v>91859</v>
+        <v>91417</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16482,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733206</v>
+        <v>733179</v>
       </c>
       <c r="R149" t="n">
-        <v>7102446</v>
+        <v>7102677</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16738,32 +16743,27 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128092233</v>
+        <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>91417</v>
+        <v>91859</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16773,10 +16773,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>733179</v>
+        <v>733206</v>
       </c>
       <c r="R152" t="n">
-        <v>7102677</v>
+        <v>7102446</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B121" t="n">
-        <v>75171</v>
+        <v>91859</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,21 +13749,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13773,10 +13768,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R121" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13835,10 +13830,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B122" t="n">
-        <v>91859</v>
+        <v>75171</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13846,16 +13841,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R122" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092223</v>
+        <v>128092222</v>
       </c>
       <c r="B125" t="n">
-        <v>91452</v>
+        <v>57685</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,34 +14132,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733389</v>
+        <v>733395</v>
       </c>
       <c r="R125" t="n">
-        <v>7102564</v>
+        <v>7102558</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14192,6 +14200,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14218,10 +14231,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092222</v>
+        <v>128092239</v>
       </c>
       <c r="B126" t="n">
-        <v>57685</v>
+        <v>91859</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14229,42 +14242,29 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733395</v>
+        <v>733324</v>
       </c>
       <c r="R126" t="n">
-        <v>7102558</v>
+        <v>7102525</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14297,11 +14297,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14328,10 +14323,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092239</v>
+        <v>128092223</v>
       </c>
       <c r="B127" t="n">
-        <v>91859</v>
+        <v>91452</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14339,16 +14334,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733324</v>
+        <v>733389</v>
       </c>
       <c r="R127" t="n">
-        <v>7102525</v>
+        <v>7102564</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14614,50 +14614,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092235</v>
+        <v>128092238</v>
       </c>
       <c r="B130" t="n">
-        <v>57682</v>
+        <v>105609</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733171</v>
+        <v>733339</v>
       </c>
       <c r="R130" t="n">
-        <v>7102645</v>
+        <v>7102561</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14716,32 +14711,27 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092238</v>
+        <v>128092206</v>
       </c>
       <c r="B131" t="n">
-        <v>105609</v>
+        <v>91859</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14751,10 +14741,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733339</v>
+        <v>733214</v>
       </c>
       <c r="R131" t="n">
-        <v>7102561</v>
+        <v>7102100</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14813,10 +14803,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092206</v>
+        <v>128092235</v>
       </c>
       <c r="B132" t="n">
-        <v>91859</v>
+        <v>57682</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14824,29 +14814,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733214</v>
+        <v>733171</v>
       </c>
       <c r="R132" t="n">
-        <v>7102100</v>
+        <v>7102645</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15094,32 +15094,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128092249</v>
+        <v>128092247</v>
       </c>
       <c r="B135" t="n">
-        <v>92742</v>
+        <v>82942</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>732847</v>
+        <v>732914</v>
       </c>
       <c r="R135" t="n">
-        <v>7102277</v>
+        <v>7102401</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15191,32 +15191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128092247</v>
+        <v>128092249</v>
       </c>
       <c r="B136" t="n">
-        <v>82942</v>
+        <v>92742</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15226,10 +15226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>732914</v>
+        <v>732847</v>
       </c>
       <c r="R136" t="n">
-        <v>7102401</v>
+        <v>7102277</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B139" t="n">
-        <v>91859</v>
+        <v>79083</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,16 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15512,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R139" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15574,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B140" t="n">
-        <v>91470</v>
+        <v>91859</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15585,21 +15590,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15609,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R140" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15671,10 +15671,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B141" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15682,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R141" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092214</v>
+        <v>128092213</v>
       </c>
       <c r="B144" t="n">
-        <v>57682</v>
+        <v>88853</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,39 +15973,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733358</v>
+        <v>733347</v>
       </c>
       <c r="R144" t="n">
-        <v>7102265</v>
+        <v>7102250</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16064,32 +16059,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092212</v>
+        <v>128092229</v>
       </c>
       <c r="B145" t="n">
-        <v>91417</v>
+        <v>82942</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16099,10 +16094,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733283</v>
+        <v>733361</v>
       </c>
       <c r="R145" t="n">
-        <v>7102190</v>
+        <v>7102699</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16161,32 +16156,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092213</v>
+        <v>128092212</v>
       </c>
       <c r="B146" t="n">
-        <v>88853</v>
+        <v>91417</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16196,10 +16191,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733347</v>
+        <v>733283</v>
       </c>
       <c r="R146" t="n">
-        <v>7102250</v>
+        <v>7102190</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16258,10 +16253,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092229</v>
+        <v>128092214</v>
       </c>
       <c r="B147" t="n">
-        <v>82942</v>
+        <v>57682</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16269,34 +16264,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733361</v>
+        <v>733358</v>
       </c>
       <c r="R147" t="n">
-        <v>7102699</v>
+        <v>7102265</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16452,10 +16452,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092233</v>
+        <v>128092218</v>
       </c>
       <c r="B149" t="n">
-        <v>91417</v>
+        <v>100726</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16463,21 +16463,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733179</v>
+        <v>733367</v>
       </c>
       <c r="R149" t="n">
-        <v>7102677</v>
+        <v>7102430</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092205</v>
+        <v>128092233</v>
       </c>
       <c r="B150" t="n">
-        <v>91452</v>
+        <v>91417</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733214</v>
+        <v>733179</v>
       </c>
       <c r="R150" t="n">
-        <v>7102100</v>
+        <v>7102677</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,32 +16646,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092218</v>
+        <v>128092205</v>
       </c>
       <c r="B151" t="n">
-        <v>100726</v>
+        <v>91452</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733367</v>
+        <v>733214</v>
       </c>
       <c r="R151" t="n">
-        <v>7102430</v>
+        <v>7102100</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B121" t="n">
-        <v>91859</v>
+        <v>75171</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,16 +13749,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13768,10 +13773,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R121" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13830,10 +13835,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B122" t="n">
-        <v>75171</v>
+        <v>91859</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13841,21 +13846,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R122" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14614,45 +14614,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B130" t="n">
-        <v>105609</v>
+        <v>57682</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R130" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14711,27 +14716,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092206</v>
+        <v>128092238</v>
       </c>
       <c r="B131" t="n">
-        <v>91859</v>
+        <v>105609</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6040186</v>
+        <v>221144</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14741,10 +14751,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733214</v>
+        <v>733339</v>
       </c>
       <c r="R131" t="n">
-        <v>7102100</v>
+        <v>7102561</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14803,10 +14813,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092235</v>
+        <v>128092206</v>
       </c>
       <c r="B132" t="n">
-        <v>57682</v>
+        <v>91859</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14814,39 +14824,29 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733171</v>
+        <v>733214</v>
       </c>
       <c r="R132" t="n">
-        <v>7102645</v>
+        <v>7102100</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R139" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092246</v>
+        <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>91859</v>
+        <v>79083</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,16 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15609,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>732940</v>
+        <v>733376</v>
       </c>
       <c r="R140" t="n">
-        <v>7102409</v>
+        <v>7102482</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15671,10 +15676,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128092237</v>
+        <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>91470</v>
+        <v>91859</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15682,21 +15687,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15706,10 +15706,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>733337</v>
+        <v>732940</v>
       </c>
       <c r="R141" t="n">
-        <v>7102597</v>
+        <v>7102409</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16452,32 +16452,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092218</v>
+        <v>128092205</v>
       </c>
       <c r="B149" t="n">
-        <v>100726</v>
+        <v>91452</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733367</v>
+        <v>733214</v>
       </c>
       <c r="R149" t="n">
-        <v>7102430</v>
+        <v>7102100</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,10 +16549,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092233</v>
+        <v>128092218</v>
       </c>
       <c r="B150" t="n">
-        <v>91417</v>
+        <v>100726</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16560,21 +16560,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733179</v>
+        <v>733367</v>
       </c>
       <c r="R150" t="n">
-        <v>7102677</v>
+        <v>7102430</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,32 +16646,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092205</v>
+        <v>128092233</v>
       </c>
       <c r="B151" t="n">
-        <v>91452</v>
+        <v>91417</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733214</v>
+        <v>733179</v>
       </c>
       <c r="R151" t="n">
-        <v>7102100</v>
+        <v>7102677</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B121" t="n">
-        <v>75171</v>
+        <v>91871</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,21 +13749,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13773,10 +13768,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R121" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13835,10 +13830,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B122" t="n">
-        <v>91859</v>
+        <v>75175</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13846,16 +13841,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R122" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13930,7 +13930,7 @@
         <v>128092251</v>
       </c>
       <c r="B123" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092231</v>
+        <v>128092223</v>
       </c>
       <c r="B124" t="n">
-        <v>91470</v>
+        <v>91464</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,21 +14035,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733194</v>
+        <v>733389</v>
       </c>
       <c r="R124" t="n">
-        <v>7102684</v>
+        <v>7102564</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092222</v>
+        <v>128092231</v>
       </c>
       <c r="B125" t="n">
-        <v>57685</v>
+        <v>91482</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,42 +14132,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733395</v>
+        <v>733194</v>
       </c>
       <c r="R125" t="n">
-        <v>7102558</v>
+        <v>7102684</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,11 +14192,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14231,10 +14218,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092239</v>
+        <v>128092222</v>
       </c>
       <c r="B126" t="n">
-        <v>91859</v>
+        <v>57689</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14242,29 +14229,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733324</v>
+        <v>733395</v>
       </c>
       <c r="R126" t="n">
-        <v>7102525</v>
+        <v>7102558</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14297,6 +14297,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14323,10 +14328,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092223</v>
+        <v>128092239</v>
       </c>
       <c r="B127" t="n">
-        <v>91452</v>
+        <v>91871</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14334,21 +14339,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733389</v>
+        <v>733324</v>
       </c>
       <c r="R127" t="n">
-        <v>7102564</v>
+        <v>7102525</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14423,7 +14423,7 @@
         <v>128092202</v>
       </c>
       <c r="B128" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>128092244</v>
       </c>
       <c r="B129" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14614,50 +14614,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092235</v>
+        <v>128092238</v>
       </c>
       <c r="B130" t="n">
-        <v>57682</v>
+        <v>105630</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733171</v>
+        <v>733339</v>
       </c>
       <c r="R130" t="n">
-        <v>7102645</v>
+        <v>7102561</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14716,45 +14711,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B131" t="n">
-        <v>105609</v>
+        <v>57686</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R131" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14816,7 +14816,7 @@
         <v>128092206</v>
       </c>
       <c r="B132" t="n">
-        <v>91859</v>
+        <v>91871</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>128092240</v>
       </c>
       <c r="B133" t="n">
-        <v>91859</v>
+        <v>91871</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>128092224</v>
       </c>
       <c r="B134" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>128092247</v>
       </c>
       <c r="B135" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>128092249</v>
       </c>
       <c r="B136" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>128092203</v>
       </c>
       <c r="B137" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>128092219</v>
       </c>
       <c r="B138" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092237</v>
+        <v>128092221</v>
       </c>
       <c r="B139" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733337</v>
+        <v>733376</v>
       </c>
       <c r="R139" t="n">
-        <v>7102597</v>
+        <v>7102482</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B140" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,21 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15614,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R140" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15679,7 +15679,7 @@
         <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>91859</v>
+        <v>91871</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>128092208</v>
       </c>
       <c r="B142" t="n">
-        <v>91810</v>
+        <v>91822</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>128092211</v>
       </c>
       <c r="B143" t="n">
-        <v>91402</v>
+        <v>91414</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092213</v>
+        <v>128092214</v>
       </c>
       <c r="B144" t="n">
-        <v>88853</v>
+        <v>57686</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15973,34 +15973,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733347</v>
+        <v>733358</v>
       </c>
       <c r="R144" t="n">
-        <v>7102250</v>
+        <v>7102265</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16059,32 +16064,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092229</v>
+        <v>128092212</v>
       </c>
       <c r="B145" t="n">
-        <v>82942</v>
+        <v>91429</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16094,10 +16099,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733361</v>
+        <v>733283</v>
       </c>
       <c r="R145" t="n">
-        <v>7102699</v>
+        <v>7102190</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16156,32 +16161,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092212</v>
+        <v>128092213</v>
       </c>
       <c r="B146" t="n">
-        <v>91417</v>
+        <v>88865</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16191,10 +16196,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733283</v>
+        <v>733347</v>
       </c>
       <c r="R146" t="n">
-        <v>7102190</v>
+        <v>7102250</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16253,10 +16258,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092214</v>
+        <v>128092229</v>
       </c>
       <c r="B147" t="n">
-        <v>57682</v>
+        <v>82946</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16264,39 +16269,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733358</v>
+        <v>733361</v>
       </c>
       <c r="R147" t="n">
-        <v>7102265</v>
+        <v>7102699</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16358,7 +16358,7 @@
         <v>128092227</v>
       </c>
       <c r="B148" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16452,32 +16452,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092205</v>
+        <v>128092233</v>
       </c>
       <c r="B149" t="n">
-        <v>91452</v>
+        <v>91429</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733214</v>
+        <v>733179</v>
       </c>
       <c r="R149" t="n">
-        <v>7102100</v>
+        <v>7102677</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092218</v>
+        <v>128092205</v>
       </c>
       <c r="B150" t="n">
-        <v>100726</v>
+        <v>91464</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733367</v>
+        <v>733214</v>
       </c>
       <c r="R150" t="n">
-        <v>7102430</v>
+        <v>7102100</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092233</v>
+        <v>128092218</v>
       </c>
       <c r="B151" t="n">
-        <v>91417</v>
+        <v>100741</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16657,21 +16657,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733179</v>
+        <v>733367</v>
       </c>
       <c r="R151" t="n">
-        <v>7102677</v>
+        <v>7102430</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16746,7 +16746,7 @@
         <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>91859</v>
+        <v>91871</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -14121,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092231</v>
+        <v>128092222</v>
       </c>
       <c r="B125" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,34 +14132,42 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733194</v>
+        <v>733395</v>
       </c>
       <c r="R125" t="n">
-        <v>7102684</v>
+        <v>7102558</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14192,6 +14200,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14218,10 +14231,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092222</v>
+        <v>128092239</v>
       </c>
       <c r="B126" t="n">
-        <v>57689</v>
+        <v>91871</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14229,42 +14242,29 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733395</v>
+        <v>733324</v>
       </c>
       <c r="R126" t="n">
-        <v>7102558</v>
+        <v>7102525</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14297,11 +14297,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14328,10 +14323,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092239</v>
+        <v>128092231</v>
       </c>
       <c r="B127" t="n">
-        <v>91871</v>
+        <v>91482</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14339,16 +14334,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733324</v>
+        <v>733194</v>
       </c>
       <c r="R127" t="n">
-        <v>7102525</v>
+        <v>7102684</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14614,45 +14614,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B130" t="n">
-        <v>105630</v>
+        <v>57686</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R130" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14711,50 +14716,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092235</v>
+        <v>128092238</v>
       </c>
       <c r="B131" t="n">
-        <v>57686</v>
+        <v>105630</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733171</v>
+        <v>733339</v>
       </c>
       <c r="R131" t="n">
-        <v>7102645</v>
+        <v>7102561</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -14614,50 +14614,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128092235</v>
+        <v>128092238</v>
       </c>
       <c r="B130" t="n">
-        <v>57686</v>
+        <v>105630</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>733171</v>
+        <v>733339</v>
       </c>
       <c r="R130" t="n">
-        <v>7102645</v>
+        <v>7102561</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14716,45 +14711,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092238</v>
+        <v>128092235</v>
       </c>
       <c r="B131" t="n">
-        <v>105630</v>
+        <v>57686</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733339</v>
+        <v>733171</v>
       </c>
       <c r="R131" t="n">
-        <v>7102561</v>
+        <v>7102645</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15962,50 +15962,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128092214</v>
+        <v>128092212</v>
       </c>
       <c r="B144" t="n">
-        <v>57686</v>
+        <v>91429</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>733358</v>
+        <v>733283</v>
       </c>
       <c r="R144" t="n">
-        <v>7102265</v>
+        <v>7102190</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16064,32 +16059,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092212</v>
+        <v>128092213</v>
       </c>
       <c r="B145" t="n">
-        <v>91429</v>
+        <v>88865</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16099,10 +16094,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733283</v>
+        <v>733347</v>
       </c>
       <c r="R145" t="n">
-        <v>7102190</v>
+        <v>7102250</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16161,10 +16156,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092213</v>
+        <v>128092229</v>
       </c>
       <c r="B146" t="n">
-        <v>88865</v>
+        <v>82946</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16172,21 +16167,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16196,10 +16191,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733347</v>
+        <v>733361</v>
       </c>
       <c r="R146" t="n">
-        <v>7102250</v>
+        <v>7102699</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16258,10 +16253,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128092229</v>
+        <v>128092214</v>
       </c>
       <c r="B147" t="n">
-        <v>82946</v>
+        <v>57686</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16269,34 +16264,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>733361</v>
+        <v>733358</v>
       </c>
       <c r="R147" t="n">
-        <v>7102699</v>
+        <v>7102265</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -13738,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128092215</v>
+        <v>128092220</v>
       </c>
       <c r="B121" t="n">
-        <v>91871</v>
+        <v>75177</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13749,16 +13749,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6040186</v>
+        <v>6440</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13768,10 +13773,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>733389</v>
+        <v>733382</v>
       </c>
       <c r="R121" t="n">
-        <v>7102265</v>
+        <v>7102436</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13830,10 +13835,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128092220</v>
+        <v>128092215</v>
       </c>
       <c r="B122" t="n">
-        <v>75175</v>
+        <v>91873</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13841,21 +13846,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13865,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>733382</v>
+        <v>733389</v>
       </c>
       <c r="R122" t="n">
-        <v>7102436</v>
+        <v>7102265</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13930,7 +13930,7 @@
         <v>128092251</v>
       </c>
       <c r="B123" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092223</v>
+        <v>128092239</v>
       </c>
       <c r="B124" t="n">
-        <v>91464</v>
+        <v>91873</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,21 +14035,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14054,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733389</v>
+        <v>733324</v>
       </c>
       <c r="R124" t="n">
-        <v>7102564</v>
+        <v>7102525</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14121,10 +14116,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092222</v>
+        <v>128092231</v>
       </c>
       <c r="B125" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,42 +14127,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733395</v>
+        <v>733194</v>
       </c>
       <c r="R125" t="n">
-        <v>7102558</v>
+        <v>7102684</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,11 +14187,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14231,10 +14213,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128092239</v>
+        <v>128092223</v>
       </c>
       <c r="B126" t="n">
-        <v>91871</v>
+        <v>91466</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14242,16 +14224,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14261,10 +14248,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>733324</v>
+        <v>733389</v>
       </c>
       <c r="R126" t="n">
-        <v>7102525</v>
+        <v>7102564</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14323,10 +14310,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128092231</v>
+        <v>128092222</v>
       </c>
       <c r="B127" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14334,34 +14321,42 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>733194</v>
+        <v>733395</v>
       </c>
       <c r="R127" t="n">
-        <v>7102684</v>
+        <v>7102558</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14394,6 +14389,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14423,7 +14423,7 @@
         <v>128092202</v>
       </c>
       <c r="B128" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>128092244</v>
       </c>
       <c r="B129" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>128092238</v>
       </c>
       <c r="B130" t="n">
-        <v>105630</v>
+        <v>105651</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14711,10 +14711,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128092235</v>
+        <v>128092206</v>
       </c>
       <c r="B131" t="n">
-        <v>57686</v>
+        <v>91873</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14722,39 +14722,29 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>733171</v>
+        <v>733214</v>
       </c>
       <c r="R131" t="n">
-        <v>7102645</v>
+        <v>7102100</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14813,10 +14803,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128092206</v>
+        <v>128092235</v>
       </c>
       <c r="B132" t="n">
-        <v>91871</v>
+        <v>57686</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14824,29 +14814,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Stennäs, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>733214</v>
+        <v>733171</v>
       </c>
       <c r="R132" t="n">
-        <v>7102100</v>
+        <v>7102645</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14908,7 +14908,7 @@
         <v>128092240</v>
       </c>
       <c r="B133" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>128092224</v>
       </c>
       <c r="B134" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15094,32 +15094,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128092247</v>
+        <v>128092249</v>
       </c>
       <c r="B135" t="n">
-        <v>82946</v>
+        <v>92756</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15129,10 +15129,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>732914</v>
+        <v>732847</v>
       </c>
       <c r="R135" t="n">
-        <v>7102401</v>
+        <v>7102277</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15191,32 +15191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128092249</v>
+        <v>128092247</v>
       </c>
       <c r="B136" t="n">
-        <v>92754</v>
+        <v>82948</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15226,10 +15226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>732847</v>
+        <v>732914</v>
       </c>
       <c r="R136" t="n">
-        <v>7102277</v>
+        <v>7102401</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15291,7 +15291,7 @@
         <v>128092203</v>
       </c>
       <c r="B137" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>128092219</v>
       </c>
       <c r="B138" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15482,10 +15482,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128092221</v>
+        <v>128092237</v>
       </c>
       <c r="B139" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15493,21 +15493,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15517,10 +15517,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>733376</v>
+        <v>733337</v>
       </c>
       <c r="R139" t="n">
-        <v>7102482</v>
+        <v>7102597</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128092237</v>
+        <v>128092221</v>
       </c>
       <c r="B140" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15590,21 +15590,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15614,10 +15614,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>733337</v>
+        <v>733376</v>
       </c>
       <c r="R140" t="n">
-        <v>7102597</v>
+        <v>7102482</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15679,7 +15679,7 @@
         <v>128092246</v>
       </c>
       <c r="B141" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>128092208</v>
       </c>
       <c r="B142" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>128092211</v>
       </c>
       <c r="B143" t="n">
-        <v>91414</v>
+        <v>91416</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>128092212</v>
       </c>
       <c r="B144" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16059,10 +16059,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128092213</v>
+        <v>128092229</v>
       </c>
       <c r="B145" t="n">
-        <v>88865</v>
+        <v>82948</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16070,21 +16070,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16094,10 +16094,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>733347</v>
+        <v>733361</v>
       </c>
       <c r="R145" t="n">
-        <v>7102250</v>
+        <v>7102699</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16156,10 +16156,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128092229</v>
+        <v>128092213</v>
       </c>
       <c r="B146" t="n">
-        <v>82946</v>
+        <v>88867</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16167,21 +16167,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16191,10 +16191,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>733361</v>
+        <v>733347</v>
       </c>
       <c r="R146" t="n">
-        <v>7102699</v>
+        <v>7102250</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16358,7 +16358,7 @@
         <v>128092227</v>
       </c>
       <c r="B148" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>128092233</v>
       </c>
       <c r="B149" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>128092205</v>
       </c>
       <c r="B150" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>128092218</v>
       </c>
       <c r="B151" t="n">
-        <v>100741</v>
+        <v>100752</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>128092241</v>
       </c>
       <c r="B152" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128092239</v>
+        <v>128092231</v>
       </c>
       <c r="B124" t="n">
-        <v>91873</v>
+        <v>91484</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14035,16 +14035,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14054,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>733324</v>
+        <v>733194</v>
       </c>
       <c r="R124" t="n">
-        <v>7102525</v>
+        <v>7102684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14116,10 +14121,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128092231</v>
+        <v>128092239</v>
       </c>
       <c r="B125" t="n">
-        <v>91484</v>
+        <v>91873</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14127,21 +14132,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14151,10 +14151,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>733194</v>
+        <v>733324</v>
       </c>
       <c r="R125" t="n">
-        <v>7102684</v>
+        <v>7102525</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16452,32 +16452,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128092233</v>
+        <v>128092205</v>
       </c>
       <c r="B149" t="n">
-        <v>91431</v>
+        <v>91466</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>733179</v>
+        <v>733214</v>
       </c>
       <c r="R149" t="n">
-        <v>7102677</v>
+        <v>7102100</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16549,32 +16549,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128092205</v>
+        <v>128092218</v>
       </c>
       <c r="B150" t="n">
-        <v>91466</v>
+        <v>100752</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16584,10 +16584,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>733214</v>
+        <v>733367</v>
       </c>
       <c r="R150" t="n">
-        <v>7102100</v>
+        <v>7102430</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16646,10 +16646,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128092218</v>
+        <v>128092233</v>
       </c>
       <c r="B151" t="n">
-        <v>100752</v>
+        <v>91431</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16657,21 +16657,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16681,10 +16681,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>733367</v>
+        <v>733179</v>
       </c>
       <c r="R151" t="n">
-        <v>7102430</v>
+        <v>7102677</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -16835,32 +16835,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128997716</v>
+        <v>128997268</v>
       </c>
       <c r="B153" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16870,10 +16870,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>733013</v>
+        <v>733182</v>
       </c>
       <c r="R153" t="n">
-        <v>7102506</v>
+        <v>7102205</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16920,22 +16920,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128997665</v>
+        <v>128997347</v>
       </c>
       <c r="B154" t="n">
-        <v>95862</v>
+        <v>91478</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16943,21 +16943,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16967,10 +16967,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>732913</v>
+        <v>733204</v>
       </c>
       <c r="R154" t="n">
-        <v>7102121</v>
+        <v>7102701</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16997,12 +16997,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17017,12 +17017,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
@@ -17032,7 +17032,7 @@
         <v>128997403</v>
       </c>
       <c r="B155" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17112,36 +17112,46 @@
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128997268</v>
+        <v>128997716</v>
       </c>
       <c r="B156" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17151,10 +17161,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>733182</v>
+        <v>733013</v>
       </c>
       <c r="R156" t="n">
-        <v>7102205</v>
+        <v>7102506</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17199,14 +17209,24 @@
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128997347</v>
+        <v>128997665</v>
       </c>
       <c r="B157" t="n">
-        <v>91473</v>
+        <v>95869</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17214,21 +17234,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17238,10 +17258,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>733204</v>
+        <v>732913</v>
       </c>
       <c r="R157" t="n">
-        <v>7102701</v>
+        <v>7102121</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17268,12 +17288,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17286,14 +17306,24 @@
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+        </is>
+      </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128997402</v>
+        <v>128997364</v>
       </c>
       <c r="B158" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17301,21 +17331,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17325,10 +17355,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>733365</v>
+        <v>733061</v>
       </c>
       <c r="R158" t="n">
-        <v>7102292</v>
+        <v>7102497</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17373,6 +17403,16 @@
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -17380,7 +17420,7 @@
         <v>128997609</v>
       </c>
       <c r="B159" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17467,39 +17507,39 @@
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128997388</v>
+        <v>128997346</v>
       </c>
       <c r="B160" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17509,10 +17549,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>733309</v>
+        <v>733218</v>
       </c>
       <c r="R160" t="n">
-        <v>7102762</v>
+        <v>7102691</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17557,6 +17597,16 @@
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
@@ -17564,7 +17614,7 @@
         <v>128997399</v>
       </c>
       <c r="B161" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17644,6 +17694,16 @@
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
@@ -17651,7 +17711,7 @@
         <v>128997695</v>
       </c>
       <c r="B162" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17738,17 +17798,17 @@
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128997235</v>
+        <v>128997388</v>
       </c>
       <c r="B163" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17780,10 +17840,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>733200</v>
+        <v>733309</v>
       </c>
       <c r="R163" t="n">
-        <v>7102599</v>
+        <v>7102762</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17828,14 +17888,24 @@
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128997364</v>
+        <v>128997402</v>
       </c>
       <c r="B164" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17843,21 +17913,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17867,10 +17937,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>733061</v>
+        <v>733365</v>
       </c>
       <c r="R164" t="n">
-        <v>7102497</v>
+        <v>7102292</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17915,36 +17985,46 @@
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128997346</v>
+        <v>128997235</v>
       </c>
       <c r="B165" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17954,10 +18034,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>733218</v>
+        <v>733200</v>
       </c>
       <c r="R165" t="n">
-        <v>7102691</v>
+        <v>7102599</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18002,14 +18082,24 @@
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128997634</v>
+        <v>128997396</v>
       </c>
       <c r="B166" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18017,21 +18107,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18041,10 +18131,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>733444</v>
+        <v>733112</v>
       </c>
       <c r="R166" t="n">
-        <v>7102591</v>
+        <v>7102527</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18091,44 +18181,44 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128997608</v>
+        <v>128997394</v>
       </c>
       <c r="B167" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18138,10 +18228,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>733270</v>
+        <v>733155</v>
       </c>
       <c r="R167" t="n">
-        <v>7102532</v>
+        <v>7102609</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18188,22 +18278,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128997394</v>
+        <v>128997634</v>
       </c>
       <c r="B168" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18211,21 +18301,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18235,10 +18325,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>733155</v>
+        <v>733444</v>
       </c>
       <c r="R168" t="n">
-        <v>7102609</v>
+        <v>7102591</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18283,6 +18373,16 @@
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
@@ -18290,7 +18390,7 @@
         <v>128997642</v>
       </c>
       <c r="B169" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18377,17 +18477,17 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128997396</v>
+        <v>128997223</v>
       </c>
       <c r="B170" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18395,21 +18495,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18419,10 +18519,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>733112</v>
+        <v>733195</v>
       </c>
       <c r="R170" t="n">
-        <v>7102527</v>
+        <v>7102141</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18467,36 +18567,46 @@
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128996679</v>
+        <v>128997608</v>
       </c>
       <c r="B171" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18506,10 +18616,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>733232</v>
+        <v>733270</v>
       </c>
       <c r="R171" t="n">
-        <v>7102624</v>
+        <v>7102532</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18556,22 +18666,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128997223</v>
+        <v>128996679</v>
       </c>
       <c r="B172" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18579,21 +18689,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18603,10 +18713,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>733195</v>
+        <v>733232</v>
       </c>
       <c r="R172" t="n">
-        <v>7102141</v>
+        <v>7102624</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18651,6 +18761,16 @@
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Emma Lundh</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Emma Lundh</t>
+        </is>
+      </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
@@ -18658,7 +18778,7 @@
         <v>128997222</v>
       </c>
       <c r="B173" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18738,6 +18858,16 @@
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
@@ -18745,7 +18875,7 @@
         <v>128997274</v>
       </c>
       <c r="B174" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18825,6 +18955,16 @@
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Amelie Anderson</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Amelie Anderson</t>
+        </is>
+      </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
@@ -18832,7 +18972,7 @@
         <v>128997351</v>
       </c>
       <c r="B175" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18912,36 +19052,46 @@
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128997623</v>
+        <v>128997408</v>
       </c>
       <c r="B176" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18951,10 +19101,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>733444</v>
+        <v>733071</v>
       </c>
       <c r="R176" t="n">
-        <v>7102610</v>
+        <v>7102035</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19001,12 +19151,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
@@ -19016,7 +19166,7 @@
         <v>128997701</v>
       </c>
       <c r="B177" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19103,17 +19253,17 @@
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128997408</v>
+        <v>128997636</v>
       </c>
       <c r="B178" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19121,21 +19271,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19145,10 +19295,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>733071</v>
+        <v>733246</v>
       </c>
       <c r="R178" t="n">
-        <v>7102035</v>
+        <v>7102410</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19193,36 +19343,46 @@
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128997636</v>
+        <v>128997623</v>
       </c>
       <c r="B179" t="n">
-        <v>91508</v>
+        <v>91478</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19232,10 +19392,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>733246</v>
+        <v>733444</v>
       </c>
       <c r="R179" t="n">
-        <v>7102410</v>
+        <v>7102610</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19287,7 +19447,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -19297,7 +19457,7 @@
         <v>128997350</v>
       </c>
       <c r="B180" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19377,36 +19537,46 @@
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128997393</v>
+        <v>128997629</v>
       </c>
       <c r="B181" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19416,10 +19586,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>733147</v>
+        <v>733008</v>
       </c>
       <c r="R181" t="n">
-        <v>7102651</v>
+        <v>7102087</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19446,12 +19616,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19464,36 +19634,46 @@
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128997673</v>
+        <v>128997393</v>
       </c>
       <c r="B182" t="n">
-        <v>58090</v>
+        <v>79029</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19503,10 +19683,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>732975</v>
+        <v>733147</v>
       </c>
       <c r="R182" t="n">
-        <v>7102093</v>
+        <v>7102651</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19533,12 +19713,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19553,44 +19733,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128997629</v>
+        <v>128997242</v>
       </c>
       <c r="B183" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19600,10 +19780,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>733008</v>
+        <v>733176</v>
       </c>
       <c r="R183" t="n">
-        <v>7102087</v>
+        <v>7102141</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19630,12 +19810,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19650,44 +19830,44 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128997242</v>
+        <v>128997673</v>
       </c>
       <c r="B184" t="n">
-        <v>79124</v>
+        <v>58093</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19697,10 +19877,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>733176</v>
+        <v>732975</v>
       </c>
       <c r="R184" t="n">
-        <v>7102141</v>
+        <v>7102093</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19727,12 +19907,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19745,36 +19925,46 @@
         <v>0</v>
       </c>
       <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+        </is>
+      </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128997708</v>
+        <v>128997349</v>
       </c>
       <c r="B185" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19784,10 +19974,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>732937</v>
+        <v>733124</v>
       </c>
       <c r="R185" t="n">
-        <v>7102152</v>
+        <v>7102590</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19814,12 +20004,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19834,12 +20024,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -19849,7 +20039,7 @@
         <v>128997407</v>
       </c>
       <c r="B186" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19929,14 +20119,24 @@
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128997703</v>
+        <v>128997708</v>
       </c>
       <c r="B187" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19968,10 +20168,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>733040</v>
+        <v>732937</v>
       </c>
       <c r="R187" t="n">
-        <v>7102258</v>
+        <v>7102152</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19998,12 +20198,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20023,17 +20223,17 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128997700</v>
+        <v>128997703</v>
       </c>
       <c r="B188" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20065,10 +20265,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>733292</v>
+        <v>733040</v>
       </c>
       <c r="R188" t="n">
-        <v>7102469</v>
+        <v>7102258</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20120,39 +20320,39 @@
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128997349</v>
+        <v>128997700</v>
       </c>
       <c r="B189" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20162,10 +20362,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>733124</v>
+        <v>733292</v>
       </c>
       <c r="R189" t="n">
-        <v>7102590</v>
+        <v>7102469</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20210,6 +20410,16 @@
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
@@ -20217,7 +20427,7 @@
         <v>128996681</v>
       </c>
       <c r="B190" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20311,10 +20521,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128997717</v>
+        <v>128997405</v>
       </c>
       <c r="B191" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20346,10 +20556,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>732994</v>
+        <v>733208</v>
       </c>
       <c r="R191" t="n">
-        <v>7102352</v>
+        <v>7102136</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20396,22 +20606,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128997405</v>
+        <v>128997717</v>
       </c>
       <c r="B192" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20443,10 +20653,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>733208</v>
+        <v>732994</v>
       </c>
       <c r="R192" t="n">
-        <v>7102136</v>
+        <v>7102352</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20491,36 +20701,46 @@
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128997683</v>
+        <v>128996668</v>
       </c>
       <c r="B193" t="n">
-        <v>91526</v>
+        <v>97514</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20530,10 +20750,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>733315</v>
+        <v>733253</v>
       </c>
       <c r="R193" t="n">
-        <v>7102574</v>
+        <v>7102418</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20580,44 +20800,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128996668</v>
+        <v>128997683</v>
       </c>
       <c r="B194" t="n">
-        <v>97507</v>
+        <v>91531</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20627,10 +20847,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>733253</v>
+        <v>733315</v>
       </c>
       <c r="R194" t="n">
-        <v>7102418</v>
+        <v>7102574</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20677,44 +20897,44 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128997710</v>
+        <v>128997352</v>
       </c>
       <c r="B195" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20724,10 +20944,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>732994</v>
+        <v>733230</v>
       </c>
       <c r="R195" t="n">
-        <v>7102126</v>
+        <v>7102166</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20754,12 +20974,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20774,44 +20994,44 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128997404</v>
+        <v>128997610</v>
       </c>
       <c r="B196" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20821,10 +21041,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>733288</v>
+        <v>733235</v>
       </c>
       <c r="R196" t="n">
-        <v>7102184</v>
+        <v>7102384</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20869,14 +21089,24 @@
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128997391</v>
+        <v>128997241</v>
       </c>
       <c r="B197" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -20908,10 +21138,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>733208</v>
+        <v>733293</v>
       </c>
       <c r="R197" t="n">
-        <v>7102668</v>
+        <v>7102250</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20956,36 +21186,46 @@
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128997610</v>
+        <v>128997391</v>
       </c>
       <c r="B198" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20995,10 +21235,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>733235</v>
+        <v>733208</v>
       </c>
       <c r="R198" t="n">
-        <v>7102384</v>
+        <v>7102668</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21045,22 +21285,22 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128997720</v>
+        <v>128997404</v>
       </c>
       <c r="B199" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21092,10 +21332,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>732905</v>
+        <v>733288</v>
       </c>
       <c r="R199" t="n">
-        <v>7102199</v>
+        <v>7102184</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21122,12 +21362,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21142,44 +21382,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128997352</v>
+        <v>128997710</v>
       </c>
       <c r="B200" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21189,10 +21429,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>733230</v>
+        <v>732994</v>
       </c>
       <c r="R200" t="n">
-        <v>7102166</v>
+        <v>7102126</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21219,12 +21459,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21237,14 +21477,24 @@
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128997241</v>
+        <v>128997720</v>
       </c>
       <c r="B201" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21276,10 +21526,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>733293</v>
+        <v>732905</v>
       </c>
       <c r="R201" t="n">
-        <v>7102250</v>
+        <v>7102199</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21306,12 +21556,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21324,36 +21574,46 @@
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128997672</v>
+        <v>128997687</v>
       </c>
       <c r="B202" t="n">
-        <v>95486</v>
+        <v>91531</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2387</v>
+        <v>5432</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21363,10 +21623,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>732982</v>
+        <v>732923</v>
       </c>
       <c r="R202" t="n">
-        <v>7102108</v>
+        <v>7102344</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21393,12 +21653,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21418,39 +21678,39 @@
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128997687</v>
+        <v>128997358</v>
       </c>
       <c r="B203" t="n">
-        <v>91526</v>
+        <v>91478</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21460,10 +21720,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>732923</v>
+        <v>733089</v>
       </c>
       <c r="R203" t="n">
-        <v>7102344</v>
+        <v>7102035</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21510,44 +21770,44 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128997719</v>
+        <v>128997672</v>
       </c>
       <c r="B204" t="n">
-        <v>79124</v>
+        <v>95493</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21557,10 +21817,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>732845</v>
+        <v>732982</v>
       </c>
       <c r="R204" t="n">
-        <v>7102214</v>
+        <v>7102108</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21612,39 +21872,39 @@
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128997358</v>
+        <v>128997719</v>
       </c>
       <c r="B205" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21654,10 +21914,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>733089</v>
+        <v>732845</v>
       </c>
       <c r="R205" t="n">
-        <v>7102035</v>
+        <v>7102214</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21684,12 +21944,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -21702,6 +21962,16 @@
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
@@ -21709,7 +21979,7 @@
         <v>128996680</v>
       </c>
       <c r="B206" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21803,32 +22073,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128997715</v>
+        <v>128997267</v>
       </c>
       <c r="B207" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21838,10 +22108,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>733353</v>
+        <v>733216</v>
       </c>
       <c r="R207" t="n">
-        <v>7102649</v>
+        <v>7102335</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21888,12 +22158,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
@@ -21903,7 +22173,7 @@
         <v>128997618</v>
       </c>
       <c r="B208" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -21990,17 +22260,17 @@
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128997308</v>
+        <v>128997715</v>
       </c>
       <c r="B209" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22032,10 +22302,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>733331</v>
+        <v>733353</v>
       </c>
       <c r="R209" t="n">
-        <v>7102372</v>
+        <v>7102649</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22080,36 +22350,46 @@
         <v>0</v>
       </c>
       <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128997267</v>
+        <v>128997308</v>
       </c>
       <c r="B210" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22119,10 +22399,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>733216</v>
+        <v>733331</v>
       </c>
       <c r="R210" t="n">
-        <v>7102335</v>
+        <v>7102372</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22167,6 +22447,16 @@
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Amelie Anderson</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Amelie Anderson</t>
+        </is>
+      </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
@@ -22174,7 +22464,7 @@
         <v>128997366</v>
       </c>
       <c r="B211" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22254,14 +22544,24 @@
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128997390</v>
+        <v>128997238</v>
       </c>
       <c r="B212" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22293,10 +22593,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>733234</v>
+        <v>733122</v>
       </c>
       <c r="R212" t="n">
-        <v>7102737</v>
+        <v>7102436</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22341,6 +22641,16 @@
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
@@ -22348,7 +22658,7 @@
         <v>128997661</v>
       </c>
       <c r="B213" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22435,39 +22745,39 @@
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128997664</v>
+        <v>128997361</v>
       </c>
       <c r="B214" t="n">
-        <v>80257</v>
+        <v>91513</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22477,10 +22787,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>733456</v>
+        <v>733368</v>
       </c>
       <c r="R214" t="n">
-        <v>7102608</v>
+        <v>7102873</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22527,22 +22837,22 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128997238</v>
+        <v>128997390</v>
       </c>
       <c r="B215" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -22574,10 +22884,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>733122</v>
+        <v>733234</v>
       </c>
       <c r="R215" t="n">
-        <v>7102436</v>
+        <v>7102737</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22622,36 +22932,46 @@
         <v>0</v>
       </c>
       <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128997361</v>
+        <v>128997664</v>
       </c>
       <c r="B216" t="n">
-        <v>91508</v>
+        <v>80162</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22661,10 +22981,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>733368</v>
+        <v>733456</v>
       </c>
       <c r="R216" t="n">
-        <v>7102873</v>
+        <v>7102608</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22709,14 +23029,24 @@
         <v>0</v>
       </c>
       <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+        </is>
+      </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128997306</v>
+        <v>128997639</v>
       </c>
       <c r="B217" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22724,21 +23054,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22748,10 +23078,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>733122</v>
+        <v>733169</v>
       </c>
       <c r="R217" t="n">
-        <v>7102126</v>
+        <v>7102382</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22796,14 +23126,24 @@
         <v>0</v>
       </c>
       <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128997240</v>
+        <v>128997641</v>
       </c>
       <c r="B218" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22811,21 +23151,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22835,10 +23175,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>733309</v>
+        <v>732869</v>
       </c>
       <c r="R218" t="n">
-        <v>7102326</v>
+        <v>7102347</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22865,12 +23205,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -22883,14 +23223,24 @@
         <v>0</v>
       </c>
       <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128997639</v>
+        <v>128997240</v>
       </c>
       <c r="B219" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22898,21 +23248,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22922,10 +23272,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>733169</v>
+        <v>733309</v>
       </c>
       <c r="R219" t="n">
-        <v>7102382</v>
+        <v>7102326</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22972,12 +23322,12 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
@@ -22987,7 +23337,7 @@
         <v>128997628</v>
       </c>
       <c r="B220" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23074,17 +23424,17 @@
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128997667</v>
+        <v>128997685</v>
       </c>
       <c r="B221" t="n">
-        <v>80229</v>
+        <v>91531</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23092,21 +23442,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23116,10 +23466,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>732976</v>
+        <v>733407</v>
       </c>
       <c r="R221" t="n">
-        <v>7102116</v>
+        <v>7102536</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23146,12 +23496,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23171,17 +23521,17 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128997685</v>
+        <v>128997306</v>
       </c>
       <c r="B222" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23189,21 +23539,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23213,10 +23563,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>733407</v>
+        <v>733122</v>
       </c>
       <c r="R222" t="n">
-        <v>7102536</v>
+        <v>7102126</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23263,22 +23613,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128997637</v>
+        <v>128997667</v>
       </c>
       <c r="B223" t="n">
-        <v>91508</v>
+        <v>80134</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23286,21 +23636,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23310,10 +23660,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>733228</v>
+        <v>732976</v>
       </c>
       <c r="R223" t="n">
-        <v>7102399</v>
+        <v>7102116</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23340,12 +23690,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23365,17 +23715,17 @@
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128997641</v>
+        <v>128997694</v>
       </c>
       <c r="B224" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -23383,21 +23733,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23407,10 +23757,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>732869</v>
+        <v>733419</v>
       </c>
       <c r="R224" t="n">
-        <v>7102347</v>
+        <v>7102646</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23437,12 +23787,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23462,17 +23812,17 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128997694</v>
+        <v>128997637</v>
       </c>
       <c r="B225" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -23480,21 +23830,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23504,10 +23854,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>733419</v>
+        <v>733228</v>
       </c>
       <c r="R225" t="n">
-        <v>7102646</v>
+        <v>7102399</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23559,39 +23909,39 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128997718</v>
+        <v>128997348</v>
       </c>
       <c r="B226" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23601,10 +23951,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>732810</v>
+        <v>733192</v>
       </c>
       <c r="R226" t="n">
-        <v>7102198</v>
+        <v>7102672</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23631,12 +23981,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23651,44 +24001,44 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128997218</v>
+        <v>128997718</v>
       </c>
       <c r="B227" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23698,10 +24048,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>733152</v>
+        <v>732810</v>
       </c>
       <c r="R227" t="n">
-        <v>7102090</v>
+        <v>7102198</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23728,12 +24078,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -23746,36 +24096,46 @@
         <v>0</v>
       </c>
       <c r="AT227" t="inlineStr"/>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128997348</v>
+        <v>128997705</v>
       </c>
       <c r="B228" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23785,10 +24145,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>733192</v>
+        <v>733002</v>
       </c>
       <c r="R228" t="n">
-        <v>7102672</v>
+        <v>7102410</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23833,6 +24193,16 @@
         <v>0</v>
       </c>
       <c r="AT228" t="inlineStr"/>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -23840,7 +24210,7 @@
         <v>128996674</v>
       </c>
       <c r="B229" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23934,32 +24304,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128997705</v>
+        <v>128997218</v>
       </c>
       <c r="B230" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23969,10 +24339,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>733002</v>
+        <v>733152</v>
       </c>
       <c r="R230" t="n">
-        <v>7102410</v>
+        <v>7102090</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24019,22 +24389,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128997626</v>
+        <v>128997295</v>
       </c>
       <c r="B231" t="n">
-        <v>91473</v>
+        <v>82990</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24042,21 +24412,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>5447</v>
+        <v>306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24066,10 +24436,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>732917</v>
+        <v>733239</v>
       </c>
       <c r="R231" t="n">
-        <v>7102230</v>
+        <v>7102219</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24096,12 +24466,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24116,22 +24486,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128997406</v>
+        <v>128997724</v>
       </c>
       <c r="B232" t="n">
-        <v>79124</v>
+        <v>88913</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24139,21 +24509,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -24163,10 +24533,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>733178</v>
+        <v>732905</v>
       </c>
       <c r="R232" t="n">
-        <v>7102089</v>
+        <v>7102156</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24193,12 +24563,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -24211,36 +24581,46 @@
         <v>0</v>
       </c>
       <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128997724</v>
+        <v>128997626</v>
       </c>
       <c r="B233" t="n">
-        <v>88908</v>
+        <v>91478</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24250,10 +24630,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>732905</v>
+        <v>732917</v>
       </c>
       <c r="R233" t="n">
-        <v>7102156</v>
+        <v>7102230</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24305,17 +24685,17 @@
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128997397</v>
+        <v>128997398</v>
       </c>
       <c r="B234" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -24347,10 +24727,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>733074</v>
+        <v>733069</v>
       </c>
       <c r="R234" t="n">
-        <v>7102532</v>
+        <v>7102479</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24395,14 +24775,24 @@
         <v>0</v>
       </c>
       <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128997398</v>
+        <v>128997397</v>
       </c>
       <c r="B235" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -24434,10 +24824,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>733069</v>
+        <v>733074</v>
       </c>
       <c r="R235" t="n">
-        <v>7102479</v>
+        <v>7102532</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24482,14 +24872,24 @@
         <v>0</v>
       </c>
       <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128997707</v>
+        <v>128997406</v>
       </c>
       <c r="B236" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -24521,10 +24921,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>732913</v>
+        <v>733178</v>
       </c>
       <c r="R236" t="n">
-        <v>7102166</v>
+        <v>7102089</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24551,12 +24951,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -24571,44 +24971,44 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128997295</v>
+        <v>128996683</v>
       </c>
       <c r="B237" t="n">
-        <v>75194</v>
+        <v>79029</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24618,10 +25018,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>733239</v>
+        <v>733186</v>
       </c>
       <c r="R237" t="n">
-        <v>7102219</v>
+        <v>7102300</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24666,14 +25066,24 @@
         <v>0</v>
       </c>
       <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Emma Lundh</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Emma Lundh</t>
+        </is>
+      </c>
       <c r="AY237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128996683</v>
+        <v>128997243</v>
       </c>
       <c r="B238" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -24705,10 +25115,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>733186</v>
+        <v>733099</v>
       </c>
       <c r="R238" t="n">
-        <v>7102300</v>
+        <v>7102127</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24755,22 +25165,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128997243</v>
+        <v>128997707</v>
       </c>
       <c r="B239" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -24802,10 +25212,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>733099</v>
+        <v>732913</v>
       </c>
       <c r="R239" t="n">
-        <v>7102127</v>
+        <v>7102166</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24832,12 +25242,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -24850,14 +25260,24 @@
         <v>0</v>
       </c>
       <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128997392</v>
+        <v>128997363</v>
       </c>
       <c r="B240" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -24865,21 +25285,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -24889,10 +25309,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>733178</v>
+        <v>733135</v>
       </c>
       <c r="R240" t="n">
-        <v>7102646</v>
+        <v>7102631</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -24937,14 +25357,24 @@
         <v>0</v>
       </c>
       <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128997693</v>
+        <v>128997362</v>
       </c>
       <c r="B241" t="n">
-        <v>91526</v>
+        <v>91513</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -24952,21 +25382,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -24976,10 +25406,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>733141</v>
+        <v>733147</v>
       </c>
       <c r="R241" t="n">
-        <v>7102438</v>
+        <v>7102613</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25026,22 +25456,22 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128997704</v>
+        <v>128997392</v>
       </c>
       <c r="B242" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -25073,10 +25503,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>732937</v>
+        <v>733178</v>
       </c>
       <c r="R242" t="n">
-        <v>7102349</v>
+        <v>7102646</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25123,22 +25553,22 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128997697</v>
+        <v>128997704</v>
       </c>
       <c r="B243" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -25170,10 +25600,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>733373</v>
+        <v>732937</v>
       </c>
       <c r="R243" t="n">
-        <v>7102580</v>
+        <v>7102349</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25225,17 +25655,17 @@
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128997702</v>
+        <v>128997693</v>
       </c>
       <c r="B244" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -25243,21 +25673,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25267,10 +25697,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>733169</v>
+        <v>733141</v>
       </c>
       <c r="R244" t="n">
-        <v>7102372</v>
+        <v>7102438</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25322,7 +25752,7 @@
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
@@ -25332,7 +25762,7 @@
         <v>128997614</v>
       </c>
       <c r="B245" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -25419,17 +25849,17 @@
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128997363</v>
+        <v>128997697</v>
       </c>
       <c r="B246" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -25437,21 +25867,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25461,10 +25891,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>733135</v>
+        <v>733373</v>
       </c>
       <c r="R246" t="n">
-        <v>7102631</v>
+        <v>7102580</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25509,14 +25939,24 @@
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128997362</v>
+        <v>128997702</v>
       </c>
       <c r="B247" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -25524,21 +25964,21 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25548,10 +25988,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>733147</v>
+        <v>733169</v>
       </c>
       <c r="R247" t="n">
-        <v>7102613</v>
+        <v>7102372</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25596,36 +26036,46 @@
         <v>0</v>
       </c>
       <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128997239</v>
+        <v>128997617</v>
       </c>
       <c r="B248" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25635,10 +26085,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>733446</v>
+        <v>732926</v>
       </c>
       <c r="R248" t="n">
-        <v>7102454</v>
+        <v>7102342</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25683,36 +26133,46 @@
         <v>0</v>
       </c>
       <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>128996693</v>
+        <v>128997611</v>
       </c>
       <c r="B249" t="n">
-        <v>78527</v>
+        <v>91478</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25722,10 +26182,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>733080</v>
+        <v>733103</v>
       </c>
       <c r="R249" t="n">
-        <v>7102183</v>
+        <v>7102358</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25772,22 +26232,22 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128997617</v>
+        <v>128997615</v>
       </c>
       <c r="B250" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -25819,10 +26279,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>732926</v>
+        <v>733046</v>
       </c>
       <c r="R250" t="n">
-        <v>7102342</v>
+        <v>7102212</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -25874,39 +26334,39 @@
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128997712</v>
+        <v>128997675</v>
       </c>
       <c r="B251" t="n">
-        <v>79124</v>
+        <v>58093</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -25916,10 +26376,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>733015</v>
+        <v>733060</v>
       </c>
       <c r="R251" t="n">
-        <v>7102088</v>
+        <v>7102276</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -25946,12 +26406,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -25971,17 +26431,17 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>128997706</v>
+        <v>128997239</v>
       </c>
       <c r="B252" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -26013,10 +26473,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>732885</v>
+        <v>733446</v>
       </c>
       <c r="R252" t="n">
-        <v>7102267</v>
+        <v>7102454</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26043,12 +26503,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -26063,44 +26523,44 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128997675</v>
+        <v>128996693</v>
       </c>
       <c r="B253" t="n">
-        <v>58090</v>
+        <v>78432</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>103015</v>
+        <v>6437</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26110,10 +26570,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>733060</v>
+        <v>733080</v>
       </c>
       <c r="R253" t="n">
-        <v>7102276</v>
+        <v>7102183</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26160,22 +26620,22 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128997698</v>
+        <v>128997712</v>
       </c>
       <c r="B254" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -26207,10 +26667,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>733350</v>
+        <v>733015</v>
       </c>
       <c r="R254" t="n">
-        <v>7102542</v>
+        <v>7102088</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26237,12 +26697,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -26262,39 +26722,39 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>128997611</v>
+        <v>128997706</v>
       </c>
       <c r="B255" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26304,10 +26764,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>733103</v>
+        <v>732885</v>
       </c>
       <c r="R255" t="n">
-        <v>7102358</v>
+        <v>7102267</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26334,12 +26794,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -26359,39 +26819,39 @@
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>128997615</v>
+        <v>128997698</v>
       </c>
       <c r="B256" t="n">
-        <v>91473</v>
+        <v>79029</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26401,10 +26861,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>733046</v>
+        <v>733350</v>
       </c>
       <c r="R256" t="n">
-        <v>7102212</v>
+        <v>7102542</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26456,17 +26916,17 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128997652</v>
+        <v>128997237</v>
       </c>
       <c r="B257" t="n">
-        <v>57880</v>
+        <v>79029</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -26474,21 +26934,21 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26498,10 +26958,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>733386</v>
+        <v>733215</v>
       </c>
       <c r="R257" t="n">
-        <v>7102695</v>
+        <v>7102543</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26548,44 +27008,44 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128997640</v>
+        <v>128997217</v>
       </c>
       <c r="B258" t="n">
-        <v>91508</v>
+        <v>91478</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26595,10 +27055,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>733058</v>
+        <v>733205</v>
       </c>
       <c r="R258" t="n">
-        <v>7102269</v>
+        <v>7102146</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26645,44 +27105,44 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128997217</v>
+        <v>128997640</v>
       </c>
       <c r="B259" t="n">
-        <v>91473</v>
+        <v>91513</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26692,10 +27152,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>733205</v>
+        <v>733058</v>
       </c>
       <c r="R259" t="n">
-        <v>7102146</v>
+        <v>7102269</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -26740,14 +27200,24 @@
         <v>0</v>
       </c>
       <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128997237</v>
+        <v>128997652</v>
       </c>
       <c r="B260" t="n">
-        <v>79124</v>
+        <v>57883</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -26755,21 +27225,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -26779,10 +27249,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>733215</v>
+        <v>733386</v>
       </c>
       <c r="R260" t="n">
-        <v>7102543</v>
+        <v>7102695</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -26827,6 +27297,16 @@
         <v>0</v>
       </c>
       <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+        </is>
+      </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
@@ -26834,7 +27314,7 @@
         <v>128997624</v>
       </c>
       <c r="B261" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -26921,39 +27401,39 @@
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128997709</v>
+        <v>128997631</v>
       </c>
       <c r="B262" t="n">
-        <v>79124</v>
+        <v>91478</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -26963,10 +27443,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>732984</v>
+        <v>733026</v>
       </c>
       <c r="R262" t="n">
-        <v>7102142</v>
+        <v>7102084</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27018,7 +27498,7 @@
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
@@ -27028,7 +27508,7 @@
         <v>128997389</v>
       </c>
       <c r="B263" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -27108,6 +27588,16 @@
         <v>0</v>
       </c>
       <c r="AT263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
@@ -27115,7 +27605,7 @@
         <v>128997401</v>
       </c>
       <c r="B264" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -27195,14 +27685,24 @@
         <v>0</v>
       </c>
       <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Ida Persson</t>
+        </is>
+      </c>
       <c r="AY264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128997729</v>
+        <v>128997309</v>
       </c>
       <c r="B265" t="n">
-        <v>78527</v>
+        <v>79029</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27210,21 +27710,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27234,10 +27734,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>733142</v>
+        <v>733141</v>
       </c>
       <c r="R265" t="n">
-        <v>7102356</v>
+        <v>7102172</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27284,44 +27784,44 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128997631</v>
+        <v>128996691</v>
       </c>
       <c r="B266" t="n">
-        <v>91473</v>
+        <v>78432</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27331,10 +27831,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>733026</v>
+        <v>733156</v>
       </c>
       <c r="R266" t="n">
-        <v>7102084</v>
+        <v>7102275</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27361,12 +27861,12 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -27381,22 +27881,22 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128996691</v>
+        <v>128997709</v>
       </c>
       <c r="B267" t="n">
-        <v>78527</v>
+        <v>79029</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27404,21 +27904,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27428,10 +27928,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>733156</v>
+        <v>732984</v>
       </c>
       <c r="R267" t="n">
-        <v>7102275</v>
+        <v>7102142</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27458,12 +27958,12 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -27478,22 +27978,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128996682</v>
+        <v>128997729</v>
       </c>
       <c r="B268" t="n">
-        <v>79124</v>
+        <v>78432</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -27501,21 +28001,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27525,10 +28025,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>733268</v>
+        <v>733142</v>
       </c>
       <c r="R268" t="n">
-        <v>7102530</v>
+        <v>7102356</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27575,22 +28075,22 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128997309</v>
+        <v>128996682</v>
       </c>
       <c r="B269" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -27622,10 +28122,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>733141</v>
+        <v>733268</v>
       </c>
       <c r="R269" t="n">
-        <v>7102172</v>
+        <v>7102530</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -27670,14 +28170,24 @@
         <v>0</v>
       </c>
       <c r="AT269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Emma Lundh</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>Emma Lundh</t>
+        </is>
+      </c>
       <c r="AY269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>128997711</v>
+        <v>128997686</v>
       </c>
       <c r="B270" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -27685,21 +28195,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -27709,10 +28219,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>732962</v>
+        <v>733241</v>
       </c>
       <c r="R270" t="n">
-        <v>7102097</v>
+        <v>7102403</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -27739,12 +28249,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -27764,17 +28274,17 @@
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>128997696</v>
+        <v>128997234</v>
       </c>
       <c r="B271" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -27806,10 +28316,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>733155</v>
+        <v>733343</v>
       </c>
       <c r="R271" t="n">
-        <v>7102412</v>
+        <v>7102660</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -27856,22 +28366,22 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>128997686</v>
+        <v>128997395</v>
       </c>
       <c r="B272" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -27879,21 +28389,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -27903,10 +28413,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>733241</v>
+        <v>733124</v>
       </c>
       <c r="R272" t="n">
-        <v>7102403</v>
+        <v>7102572</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -27953,22 +28463,22 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>128997651</v>
+        <v>128997387</v>
       </c>
       <c r="B273" t="n">
-        <v>57880</v>
+        <v>79029</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -27976,21 +28486,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28000,10 +28510,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>733016</v>
+        <v>733390</v>
       </c>
       <c r="R273" t="n">
-        <v>7102357</v>
+        <v>7102845</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28050,22 +28560,22 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>128997395</v>
+        <v>128997711</v>
       </c>
       <c r="B274" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -28097,10 +28607,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>733124</v>
+        <v>732962</v>
       </c>
       <c r="R274" t="n">
-        <v>7102572</v>
+        <v>7102097</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28127,12 +28637,12 @@
       </c>
       <c r="Y274" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -28145,14 +28655,24 @@
         <v>0</v>
       </c>
       <c r="AT274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>128997387</v>
+        <v>128997696</v>
       </c>
       <c r="B275" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -28184,10 +28704,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>733390</v>
+        <v>733155</v>
       </c>
       <c r="R275" t="n">
-        <v>7102845</v>
+        <v>7102412</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28232,14 +28752,24 @@
         <v>0</v>
       </c>
       <c r="AT275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+        </is>
+      </c>
       <c r="AY275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>128997234</v>
+        <v>128997651</v>
       </c>
       <c r="B276" t="n">
-        <v>79124</v>
+        <v>57883</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -28247,21 +28777,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28271,10 +28801,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>733343</v>
+        <v>733016</v>
       </c>
       <c r="R276" t="n">
-        <v>7102660</v>
+        <v>7102357</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28319,6 +28849,16 @@
         <v>0</v>
       </c>
       <c r="AT276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+        </is>
+      </c>
       <c r="AY276" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -16835,32 +16835,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128997347</v>
+        <v>128997716</v>
       </c>
       <c r="B153" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16870,10 +16870,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>733204</v>
+        <v>733013</v>
       </c>
       <c r="R153" t="n">
-        <v>7102701</v>
+        <v>7102506</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16920,19 +16920,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128997268</v>
+        <v>128997347</v>
       </c>
       <c r="B154" t="n">
         <v>91485</v>
@@ -16967,10 +16967,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>733182</v>
+        <v>733204</v>
       </c>
       <c r="R154" t="n">
-        <v>7102205</v>
+        <v>7102701</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17017,22 +17017,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128997665</v>
+        <v>128997268</v>
       </c>
       <c r="B155" t="n">
-        <v>95877</v>
+        <v>91485</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17040,21 +17040,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>732913</v>
+        <v>733182</v>
       </c>
       <c r="R155" t="n">
-        <v>7102121</v>
+        <v>7102205</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17094,12 +17094,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17114,44 +17114,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128997403</v>
+        <v>128997665</v>
       </c>
       <c r="B156" t="n">
-        <v>79034</v>
+        <v>95877</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17161,10 +17161,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>733336</v>
+        <v>732913</v>
       </c>
       <c r="R156" t="n">
-        <v>7102236</v>
+        <v>7102121</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17191,12 +17191,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17211,19 +17211,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128997716</v>
+        <v>128997403</v>
       </c>
       <c r="B157" t="n">
         <v>79034</v>
@@ -17258,10 +17258,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>733013</v>
+        <v>733336</v>
       </c>
       <c r="R157" t="n">
-        <v>7102506</v>
+        <v>7102236</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17308,12 +17308,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -18775,32 +18775,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128997351</v>
+        <v>128997222</v>
       </c>
       <c r="B173" t="n">
-        <v>91485</v>
+        <v>91520</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>733343</v>
+        <v>733438</v>
       </c>
       <c r="R173" t="n">
-        <v>7102250</v>
+        <v>7102459</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18860,19 +18860,19 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128997222</v>
+        <v>128997274</v>
       </c>
       <c r="B174" t="n">
         <v>91520</v>
@@ -18907,10 +18907,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>733438</v>
+        <v>733160</v>
       </c>
       <c r="R174" t="n">
-        <v>7102459</v>
+        <v>7102187</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18957,44 +18957,44 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128997274</v>
+        <v>128997351</v>
       </c>
       <c r="B175" t="n">
-        <v>91520</v>
+        <v>91485</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19004,10 +19004,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>733160</v>
+        <v>733343</v>
       </c>
       <c r="R175" t="n">
-        <v>7102187</v>
+        <v>7102250</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19054,12 +19054,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -19551,32 +19551,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128997629</v>
+        <v>128997242</v>
       </c>
       <c r="B181" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19586,10 +19586,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>733008</v>
+        <v>733176</v>
       </c>
       <c r="R181" t="n">
-        <v>7102087</v>
+        <v>7102141</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19616,12 +19616,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19636,44 +19636,44 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128997393</v>
+        <v>128997629</v>
       </c>
       <c r="B182" t="n">
-        <v>79034</v>
+        <v>91485</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19683,10 +19683,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>733147</v>
+        <v>733008</v>
       </c>
       <c r="R182" t="n">
-        <v>7102651</v>
+        <v>7102087</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19713,12 +19713,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19733,19 +19733,19 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128997242</v>
+        <v>128997393</v>
       </c>
       <c r="B183" t="n">
         <v>79034</v>
@@ -19780,10 +19780,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>733176</v>
+        <v>733147</v>
       </c>
       <c r="R183" t="n">
-        <v>7102141</v>
+        <v>7102651</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19830,12 +19830,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -20715,32 +20715,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128997405</v>
+        <v>128996668</v>
       </c>
       <c r="B193" t="n">
-        <v>79034</v>
+        <v>97522</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20750,10 +20750,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>733208</v>
+        <v>733253</v>
       </c>
       <c r="R193" t="n">
-        <v>7102136</v>
+        <v>7102418</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20800,44 +20800,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128996668</v>
+        <v>128997405</v>
       </c>
       <c r="B194" t="n">
-        <v>97522</v>
+        <v>79034</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>733253</v>
+        <v>733208</v>
       </c>
       <c r="R194" t="n">
-        <v>7102418</v>
+        <v>7102136</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20897,12 +20897,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -22073,32 +22073,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128997267</v>
+        <v>128997715</v>
       </c>
       <c r="B207" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>733216</v>
+        <v>733353</v>
       </c>
       <c r="R207" t="n">
-        <v>7102335</v>
+        <v>7102649</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22158,44 +22158,44 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128997618</v>
+        <v>128997308</v>
       </c>
       <c r="B208" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22205,10 +22205,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>732884</v>
+        <v>733331</v>
       </c>
       <c r="R208" t="n">
-        <v>7102341</v>
+        <v>7102372</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22235,12 +22235,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22255,12 +22255,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
@@ -22364,32 +22364,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128997715</v>
+        <v>128997267</v>
       </c>
       <c r="B210" t="n">
-        <v>79034</v>
+        <v>91485</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22399,10 +22399,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>733353</v>
+        <v>733216</v>
       </c>
       <c r="R210" t="n">
-        <v>7102649</v>
+        <v>7102335</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22449,44 +22449,44 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128997308</v>
+        <v>128997618</v>
       </c>
       <c r="B211" t="n">
-        <v>79034</v>
+        <v>91485</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22496,10 +22496,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>733331</v>
+        <v>732884</v>
       </c>
       <c r="R211" t="n">
-        <v>7102372</v>
+        <v>7102341</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22526,12 +22526,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22546,22 +22546,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128997664</v>
+        <v>128997661</v>
       </c>
       <c r="B212" t="n">
-        <v>80167</v>
+        <v>97522</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22569,21 +22569,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22593,10 +22593,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>733456</v>
+        <v>733345</v>
       </c>
       <c r="R212" t="n">
-        <v>7102608</v>
+        <v>7102514</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22655,10 +22655,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128997238</v>
+        <v>128997361</v>
       </c>
       <c r="B213" t="n">
-        <v>79034</v>
+        <v>91520</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22666,21 +22666,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22690,10 +22690,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>733122</v>
+        <v>733368</v>
       </c>
       <c r="R213" t="n">
-        <v>7102436</v>
+        <v>7102873</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22740,22 +22740,22 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128997361</v>
+        <v>128997390</v>
       </c>
       <c r="B214" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -22763,21 +22763,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22787,10 +22787,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>733368</v>
+        <v>733234</v>
       </c>
       <c r="R214" t="n">
-        <v>7102873</v>
+        <v>7102737</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22849,7 +22849,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128997390</v>
+        <v>128997238</v>
       </c>
       <c r="B215" t="n">
         <v>79034</v>
@@ -22884,10 +22884,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>733234</v>
+        <v>733122</v>
       </c>
       <c r="R215" t="n">
-        <v>7102737</v>
+        <v>7102436</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22934,22 +22934,22 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128997661</v>
+        <v>128997664</v>
       </c>
       <c r="B216" t="n">
-        <v>97522</v>
+        <v>80167</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -22957,21 +22957,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22981,10 +22981,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>733345</v>
+        <v>733456</v>
       </c>
       <c r="R216" t="n">
-        <v>7102514</v>
+        <v>7102608</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23043,10 +23043,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128997639</v>
+        <v>128997667</v>
       </c>
       <c r="B217" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23054,21 +23054,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23078,10 +23078,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>733169</v>
+        <v>732976</v>
       </c>
       <c r="R217" t="n">
-        <v>7102382</v>
+        <v>7102116</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23108,12 +23108,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23133,17 +23133,17 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128997637</v>
+        <v>128997694</v>
       </c>
       <c r="B218" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23151,21 +23151,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -23175,10 +23175,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>733228</v>
+        <v>733419</v>
       </c>
       <c r="R218" t="n">
-        <v>7102399</v>
+        <v>7102646</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23230,17 +23230,17 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128997641</v>
+        <v>128997306</v>
       </c>
       <c r="B219" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23248,21 +23248,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>732869</v>
+        <v>733122</v>
       </c>
       <c r="R219" t="n">
-        <v>7102347</v>
+        <v>7102126</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23302,12 +23302,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23322,19 +23322,19 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128997306</v>
+        <v>128997240</v>
       </c>
       <c r="B220" t="n">
         <v>79034</v>
@@ -23369,10 +23369,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>733122</v>
+        <v>733309</v>
       </c>
       <c r="R220" t="n">
-        <v>7102126</v>
+        <v>7102326</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23419,22 +23419,22 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128997667</v>
+        <v>128997639</v>
       </c>
       <c r="B221" t="n">
-        <v>80139</v>
+        <v>91520</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23442,21 +23442,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23466,10 +23466,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>732976</v>
+        <v>733169</v>
       </c>
       <c r="R221" t="n">
-        <v>7102116</v>
+        <v>7102382</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23496,12 +23496,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23521,17 +23521,17 @@
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128997240</v>
+        <v>128997637</v>
       </c>
       <c r="B222" t="n">
-        <v>79034</v>
+        <v>91520</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23539,21 +23539,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23563,10 +23563,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>733309</v>
+        <v>733228</v>
       </c>
       <c r="R222" t="n">
-        <v>7102326</v>
+        <v>7102399</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23613,22 +23613,22 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128997685</v>
+        <v>128997641</v>
       </c>
       <c r="B223" t="n">
-        <v>91538</v>
+        <v>91520</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23636,21 +23636,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23660,10 +23660,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>733407</v>
+        <v>732869</v>
       </c>
       <c r="R223" t="n">
-        <v>7102536</v>
+        <v>7102347</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23690,12 +23690,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23715,39 +23715,39 @@
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128997628</v>
+        <v>128997685</v>
       </c>
       <c r="B224" t="n">
-        <v>91485</v>
+        <v>91538</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23757,10 +23757,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>732875</v>
+        <v>733407</v>
       </c>
       <c r="R224" t="n">
-        <v>7102148</v>
+        <v>7102536</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23787,12 +23787,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23812,39 +23812,39 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128997694</v>
+        <v>128997628</v>
       </c>
       <c r="B225" t="n">
-        <v>79034</v>
+        <v>91485</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23854,10 +23854,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>733419</v>
+        <v>732875</v>
       </c>
       <c r="R225" t="n">
-        <v>7102646</v>
+        <v>7102148</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23884,12 +23884,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23909,17 +23909,17 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128996674</v>
+        <v>128997218</v>
       </c>
       <c r="B226" t="n">
-        <v>58093</v>
+        <v>91485</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23927,21 +23927,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23951,10 +23951,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>733336</v>
+        <v>733152</v>
       </c>
       <c r="R226" t="n">
-        <v>7102620</v>
+        <v>7102090</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24001,19 +24001,19 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128997218</v>
+        <v>128997348</v>
       </c>
       <c r="B227" t="n">
         <v>91485</v>
@@ -24048,10 +24048,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>733152</v>
+        <v>733192</v>
       </c>
       <c r="R227" t="n">
-        <v>7102090</v>
+        <v>7102672</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24098,44 +24098,44 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128997348</v>
+        <v>128997718</v>
       </c>
       <c r="B228" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24145,10 +24145,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>733192</v>
+        <v>732810</v>
       </c>
       <c r="R228" t="n">
-        <v>7102672</v>
+        <v>7102198</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24175,12 +24175,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24195,19 +24195,19 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128997718</v>
+        <v>128997705</v>
       </c>
       <c r="B229" t="n">
         <v>79034</v>
@@ -24242,10 +24242,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>732810</v>
+        <v>733002</v>
       </c>
       <c r="R229" t="n">
-        <v>7102198</v>
+        <v>7102410</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24272,12 +24272,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -24304,32 +24304,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128997705</v>
+        <v>128996674</v>
       </c>
       <c r="B230" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24339,10 +24339,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>733002</v>
+        <v>733336</v>
       </c>
       <c r="R230" t="n">
-        <v>7102410</v>
+        <v>7102620</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24389,12 +24389,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
@@ -26923,32 +26923,32 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>128997652</v>
+        <v>128997217</v>
       </c>
       <c r="B257" t="n">
-        <v>57883</v>
+        <v>91485</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26958,10 +26958,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>733386</v>
+        <v>733205</v>
       </c>
       <c r="R257" t="n">
-        <v>7102695</v>
+        <v>7102146</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -27008,22 +27008,22 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>128997640</v>
+        <v>128997237</v>
       </c>
       <c r="B258" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -27031,21 +27031,21 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -27055,10 +27055,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>733058</v>
+        <v>733215</v>
       </c>
       <c r="R258" t="n">
-        <v>7102269</v>
+        <v>7102543</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -27105,44 +27105,44 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128997217</v>
+        <v>128997640</v>
       </c>
       <c r="B259" t="n">
-        <v>91485</v>
+        <v>91520</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -27152,10 +27152,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>733205</v>
+        <v>733058</v>
       </c>
       <c r="R259" t="n">
-        <v>7102146</v>
+        <v>7102269</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27202,22 +27202,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128997237</v>
+        <v>128997652</v>
       </c>
       <c r="B260" t="n">
-        <v>79034</v>
+        <v>57883</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -27225,21 +27225,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27249,10 +27249,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>733215</v>
+        <v>733386</v>
       </c>
       <c r="R260" t="n">
-        <v>7102543</v>
+        <v>7102695</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27299,12 +27299,12 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
@@ -27505,7 +27505,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>128997709</v>
+        <v>128997389</v>
       </c>
       <c r="B263" t="n">
         <v>79034</v>
@@ -27540,10 +27540,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>732984</v>
+        <v>733292</v>
       </c>
       <c r="R263" t="n">
-        <v>7102142</v>
+        <v>7102798</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27570,12 +27570,12 @@
       </c>
       <c r="Y263" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -27590,19 +27590,19 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>128997389</v>
+        <v>128997401</v>
       </c>
       <c r="B264" t="n">
         <v>79034</v>
@@ -27637,10 +27637,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>733292</v>
+        <v>733429</v>
       </c>
       <c r="R264" t="n">
-        <v>7102798</v>
+        <v>7102359</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27699,10 +27699,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>128997401</v>
+        <v>128996691</v>
       </c>
       <c r="B265" t="n">
-        <v>79034</v>
+        <v>78437</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -27710,21 +27710,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27734,10 +27734,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>733429</v>
+        <v>733156</v>
       </c>
       <c r="R265" t="n">
-        <v>7102359</v>
+        <v>7102275</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27784,22 +27784,22 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>128996682</v>
+        <v>128997729</v>
       </c>
       <c r="B266" t="n">
-        <v>79034</v>
+        <v>78437</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -27807,21 +27807,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27831,10 +27831,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>733268</v>
+        <v>733142</v>
       </c>
       <c r="R266" t="n">
-        <v>7102530</v>
+        <v>7102356</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27881,22 +27881,22 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>128996691</v>
+        <v>128997309</v>
       </c>
       <c r="B267" t="n">
-        <v>78437</v>
+        <v>79034</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -27904,21 +27904,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27928,10 +27928,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>733156</v>
+        <v>733141</v>
       </c>
       <c r="R267" t="n">
-        <v>7102275</v>
+        <v>7102172</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27978,22 +27978,22 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>128997729</v>
+        <v>128997709</v>
       </c>
       <c r="B268" t="n">
-        <v>78437</v>
+        <v>79034</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -28001,21 +28001,21 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -28025,10 +28025,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>733142</v>
+        <v>732984</v>
       </c>
       <c r="R268" t="n">
-        <v>7102356</v>
+        <v>7102142</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -28055,12 +28055,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -28087,7 +28087,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>128997309</v>
+        <v>128996682</v>
       </c>
       <c r="B269" t="n">
         <v>79034</v>
@@ -28122,10 +28122,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>733141</v>
+        <v>733268</v>
       </c>
       <c r="R269" t="n">
-        <v>7102172</v>
+        <v>7102530</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28172,12 +28172,12 @@
       <c r="AT269" t="inlineStr"/>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>

--- a/artfynd/A 36333-2025 artfynd.xlsx
+++ b/artfynd/A 36333-2025 artfynd.xlsx
@@ -16835,32 +16835,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128997716</v>
+        <v>128997665</v>
       </c>
       <c r="B153" t="n">
-        <v>79034</v>
+        <v>95882</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16870,10 +16870,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>733013</v>
+        <v>732913</v>
       </c>
       <c r="R153" t="n">
-        <v>7102506</v>
+        <v>7102121</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16900,12 +16900,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16925,17 +16925,17 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128997347</v>
+        <v>128997268</v>
       </c>
       <c r="B154" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16967,10 +16967,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>733204</v>
+        <v>733182</v>
       </c>
       <c r="R154" t="n">
-        <v>7102701</v>
+        <v>7102205</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17017,22 +17017,22 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128997268</v>
+        <v>128997347</v>
       </c>
       <c r="B155" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17064,10 +17064,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>733182</v>
+        <v>733204</v>
       </c>
       <c r="R155" t="n">
-        <v>7102205</v>
+        <v>7102701</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17114,44 +17114,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128997665</v>
+        <v>128997403</v>
       </c>
       <c r="B156" t="n">
-        <v>95877</v>
+        <v>79034</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17161,10 +17161,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>732913</v>
+        <v>733336</v>
       </c>
       <c r="R156" t="n">
-        <v>7102121</v>
+        <v>7102236</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17191,12 +17191,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17211,19 +17211,19 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128997403</v>
+        <v>128997716</v>
       </c>
       <c r="B157" t="n">
         <v>79034</v>
@@ -17258,10 +17258,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>733336</v>
+        <v>733013</v>
       </c>
       <c r="R157" t="n">
-        <v>7102236</v>
+        <v>7102506</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17308,22 +17308,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128997364</v>
+        <v>128997235</v>
       </c>
       <c r="B158" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17331,21 +17331,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17355,10 +17355,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>733061</v>
+        <v>733200</v>
       </c>
       <c r="R158" t="n">
-        <v>7102497</v>
+        <v>7102599</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17405,44 +17405,44 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128997609</v>
+        <v>128997399</v>
       </c>
       <c r="B159" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17452,10 +17452,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>733367</v>
+        <v>733467</v>
       </c>
       <c r="R159" t="n">
-        <v>7102587</v>
+        <v>7102362</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17502,44 +17502,44 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128997346</v>
+        <v>128997695</v>
       </c>
       <c r="B160" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17549,10 +17549,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>733218</v>
+        <v>733171</v>
       </c>
       <c r="R160" t="n">
-        <v>7102691</v>
+        <v>7102512</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17599,19 +17599,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128997402</v>
+        <v>128997388</v>
       </c>
       <c r="B161" t="n">
         <v>79034</v>
@@ -17646,10 +17646,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>733365</v>
+        <v>733309</v>
       </c>
       <c r="R161" t="n">
-        <v>7102292</v>
+        <v>7102762</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17708,7 +17708,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128997388</v>
+        <v>128997402</v>
       </c>
       <c r="B162" t="n">
         <v>79034</v>
@@ -17743,10 +17743,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>733309</v>
+        <v>733365</v>
       </c>
       <c r="R162" t="n">
-        <v>7102762</v>
+        <v>7102292</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17805,10 +17805,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128997399</v>
+        <v>128997364</v>
       </c>
       <c r="B163" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17816,21 +17816,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17840,10 +17840,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>733467</v>
+        <v>733061</v>
       </c>
       <c r="R163" t="n">
-        <v>7102362</v>
+        <v>7102497</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17902,32 +17902,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128997235</v>
+        <v>128997609</v>
       </c>
       <c r="B164" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17937,10 +17937,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>733200</v>
+        <v>733367</v>
       </c>
       <c r="R164" t="n">
-        <v>7102599</v>
+        <v>7102587</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17987,44 +17987,44 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128997695</v>
+        <v>128997346</v>
       </c>
       <c r="B165" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18034,10 +18034,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>733171</v>
+        <v>733218</v>
       </c>
       <c r="R165" t="n">
-        <v>7102512</v>
+        <v>7102691</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18084,22 +18084,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128997394</v>
+        <v>128997642</v>
       </c>
       <c r="B166" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18107,21 +18107,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18131,10 +18131,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>733155</v>
+        <v>732978</v>
       </c>
       <c r="R166" t="n">
-        <v>7102609</v>
+        <v>7102118</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18161,12 +18161,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18181,22 +18181,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128996679</v>
+        <v>128997223</v>
       </c>
       <c r="B167" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18204,21 +18204,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>733232</v>
+        <v>733195</v>
       </c>
       <c r="R167" t="n">
-        <v>7102624</v>
+        <v>7102141</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18278,22 +18278,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128997396</v>
+        <v>128997634</v>
       </c>
       <c r="B168" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18301,21 +18301,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18325,10 +18325,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>733112</v>
+        <v>733444</v>
       </c>
       <c r="R168" t="n">
-        <v>7102527</v>
+        <v>7102591</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18375,22 +18375,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128997634</v>
+        <v>128996679</v>
       </c>
       <c r="B169" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18398,21 +18398,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18422,10 +18422,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>733444</v>
+        <v>733232</v>
       </c>
       <c r="R169" t="n">
-        <v>7102591</v>
+        <v>7102624</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18472,22 +18472,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128997642</v>
+        <v>128997396</v>
       </c>
       <c r="B170" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18495,21 +18495,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18519,10 +18519,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>732978</v>
+        <v>733112</v>
       </c>
       <c r="R170" t="n">
-        <v>7102118</v>
+        <v>7102527</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18549,12 +18549,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18569,22 +18569,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128997223</v>
+        <v>128997394</v>
       </c>
       <c r="B171" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18592,21 +18592,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18616,10 +18616,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>733195</v>
+        <v>733155</v>
       </c>
       <c r="R171" t="n">
-        <v>7102141</v>
+        <v>7102609</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18666,12 +18666,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18681,7 +18681,7 @@
         <v>128997608</v>
       </c>
       <c r="B172" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>128997222</v>
       </c>
       <c r="B173" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>128997274</v>
       </c>
       <c r="B174" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>128997351</v>
       </c>
       <c r="B175" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19066,10 +19066,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128997350</v>
+        <v>128997623</v>
       </c>
       <c r="B176" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19101,10 +19101,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>733389</v>
+        <v>733444</v>
       </c>
       <c r="R176" t="n">
-        <v>7102341</v>
+        <v>7102610</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19151,22 +19151,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128997623</v>
+        <v>128997350</v>
       </c>
       <c r="B177" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19198,10 +19198,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>733444</v>
+        <v>733389</v>
       </c>
       <c r="R177" t="n">
-        <v>7102610</v>
+        <v>7102341</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19248,22 +19248,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128997408</v>
+        <v>128997636</v>
       </c>
       <c r="B178" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19271,21 +19271,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19295,10 +19295,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>733071</v>
+        <v>733246</v>
       </c>
       <c r="R178" t="n">
-        <v>7102035</v>
+        <v>7102410</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19345,12 +19345,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
@@ -19454,10 +19454,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128997636</v>
+        <v>128997408</v>
       </c>
       <c r="B180" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19465,21 +19465,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19489,10 +19489,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>733246</v>
+        <v>733071</v>
       </c>
       <c r="R180" t="n">
-        <v>7102410</v>
+        <v>7102035</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19539,12 +19539,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -19648,32 +19648,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128997629</v>
+        <v>128997393</v>
       </c>
       <c r="B182" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19683,10 +19683,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>733008</v>
+        <v>733147</v>
       </c>
       <c r="R182" t="n">
-        <v>7102087</v>
+        <v>7102651</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19713,12 +19713,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19733,44 +19733,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128997393</v>
+        <v>128997629</v>
       </c>
       <c r="B183" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19780,10 +19780,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>733147</v>
+        <v>733008</v>
       </c>
       <c r="R183" t="n">
-        <v>7102651</v>
+        <v>7102087</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19810,12 +19810,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19830,12 +19830,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -19939,32 +19939,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128997349</v>
+        <v>128997407</v>
       </c>
       <c r="B185" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19974,10 +19974,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>733124</v>
+        <v>733145</v>
       </c>
       <c r="R185" t="n">
-        <v>7102590</v>
+        <v>7102048</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20036,7 +20036,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128996681</v>
+        <v>128997708</v>
       </c>
       <c r="B186" t="n">
         <v>79034</v>
@@ -20071,10 +20071,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>733336</v>
+        <v>732937</v>
       </c>
       <c r="R186" t="n">
-        <v>7102601</v>
+        <v>7102152</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20101,12 +20101,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20121,19 +20121,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128997703</v>
+        <v>128997700</v>
       </c>
       <c r="B187" t="n">
         <v>79034</v>
@@ -20168,10 +20168,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>733040</v>
+        <v>733292</v>
       </c>
       <c r="R187" t="n">
-        <v>7102258</v>
+        <v>7102469</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20230,7 +20230,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128997407</v>
+        <v>128997703</v>
       </c>
       <c r="B188" t="n">
         <v>79034</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>733145</v>
+        <v>733040</v>
       </c>
       <c r="R188" t="n">
-        <v>7102048</v>
+        <v>7102258</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20315,19 +20315,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128997700</v>
+        <v>128996681</v>
       </c>
       <c r="B189" t="n">
         <v>79034</v>
@@ -20362,10 +20362,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>733292</v>
+        <v>733336</v>
       </c>
       <c r="R189" t="n">
-        <v>7102469</v>
+        <v>7102601</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20412,44 +20412,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128997708</v>
+        <v>128997349</v>
       </c>
       <c r="B190" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20459,10 +20459,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>732937</v>
+        <v>733124</v>
       </c>
       <c r="R190" t="n">
-        <v>7102152</v>
+        <v>7102590</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20509,44 +20509,44 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128997683</v>
+        <v>128996668</v>
       </c>
       <c r="B191" t="n">
-        <v>91538</v>
+        <v>97527</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20556,10 +20556,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>733315</v>
+        <v>733253</v>
       </c>
       <c r="R191" t="n">
-        <v>7102574</v>
+        <v>7102418</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20606,19 +20606,19 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128997717</v>
+        <v>128997405</v>
       </c>
       <c r="B192" t="n">
         <v>79034</v>
@@ -20653,10 +20653,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>732994</v>
+        <v>733208</v>
       </c>
       <c r="R192" t="n">
-        <v>7102352</v>
+        <v>7102136</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20703,44 +20703,44 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128996668</v>
+        <v>128997717</v>
       </c>
       <c r="B193" t="n">
-        <v>97522</v>
+        <v>79034</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20750,10 +20750,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>733253</v>
+        <v>732994</v>
       </c>
       <c r="R193" t="n">
-        <v>7102418</v>
+        <v>7102352</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20800,22 +20800,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128997405</v>
+        <v>128997683</v>
       </c>
       <c r="B194" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20823,21 +20823,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20847,10 +20847,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>733208</v>
+        <v>733315</v>
       </c>
       <c r="R194" t="n">
-        <v>7102136</v>
+        <v>7102574</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20897,44 +20897,44 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128997610</v>
+        <v>128997241</v>
       </c>
       <c r="B195" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20944,10 +20944,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>733235</v>
+        <v>733293</v>
       </c>
       <c r="R195" t="n">
-        <v>7102384</v>
+        <v>7102250</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20994,44 +20994,44 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128997352</v>
+        <v>128997391</v>
       </c>
       <c r="B196" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21041,10 +21041,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>733230</v>
+        <v>733208</v>
       </c>
       <c r="R196" t="n">
-        <v>7102166</v>
+        <v>7102668</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21200,7 +21200,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128997391</v>
+        <v>128997710</v>
       </c>
       <c r="B198" t="n">
         <v>79034</v>
@@ -21235,10 +21235,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>733208</v>
+        <v>732994</v>
       </c>
       <c r="R198" t="n">
-        <v>7102668</v>
+        <v>7102126</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21265,12 +21265,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21285,19 +21285,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128997241</v>
+        <v>128997720</v>
       </c>
       <c r="B199" t="n">
         <v>79034</v>
@@ -21332,10 +21332,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>733293</v>
+        <v>732905</v>
       </c>
       <c r="R199" t="n">
-        <v>7102250</v>
+        <v>7102199</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21362,12 +21362,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21382,44 +21382,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128997710</v>
+        <v>128997352</v>
       </c>
       <c r="B200" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21429,10 +21429,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>732994</v>
+        <v>733230</v>
       </c>
       <c r="R200" t="n">
-        <v>7102126</v>
+        <v>7102166</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21459,12 +21459,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21479,44 +21479,44 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128997720</v>
+        <v>128997610</v>
       </c>
       <c r="B201" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21526,10 +21526,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>732905</v>
+        <v>733235</v>
       </c>
       <c r="R201" t="n">
-        <v>7102199</v>
+        <v>7102384</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21556,12 +21556,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21581,17 +21581,17 @@
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Felix Gustafsson, Tuva Niska, Emma Lundh, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128997358</v>
+        <v>128997672</v>
       </c>
       <c r="B202" t="n">
-        <v>91485</v>
+        <v>95506</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21599,21 +21599,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5447</v>
+        <v>2387</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21623,10 +21623,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>733089</v>
+        <v>732982</v>
       </c>
       <c r="R202" t="n">
-        <v>7102035</v>
+        <v>7102108</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21653,12 +21653,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21673,22 +21673,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128997687</v>
+        <v>128997719</v>
       </c>
       <c r="B203" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21696,21 +21696,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21720,10 +21720,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>732923</v>
+        <v>732845</v>
       </c>
       <c r="R203" t="n">
-        <v>7102344</v>
+        <v>7102214</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21750,12 +21750,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -21782,32 +21782,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128997672</v>
+        <v>128996680</v>
       </c>
       <c r="B204" t="n">
-        <v>95501</v>
+        <v>79034</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21817,10 +21817,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>732982</v>
+        <v>733089</v>
       </c>
       <c r="R204" t="n">
-        <v>7102108</v>
+        <v>7102430</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21847,12 +21847,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21867,22 +21867,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128996680</v>
+        <v>128997687</v>
       </c>
       <c r="B205" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -21890,21 +21890,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21914,10 +21914,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>733089</v>
+        <v>732923</v>
       </c>
       <c r="R205" t="n">
-        <v>7102430</v>
+        <v>7102344</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21964,44 +21964,44 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128997719</v>
+        <v>128997358</v>
       </c>
       <c r="B206" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22011,10 +22011,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>732845</v>
+        <v>733089</v>
       </c>
       <c r="R206" t="n">
-        <v>7102214</v>
+        <v>7102035</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22041,12 +22041,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22061,22 +22061,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128997715</v>
+        <v>128997366</v>
       </c>
       <c r="B207" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22084,21 +22084,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22108,10 +22108,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>733353</v>
+        <v>733203</v>
       </c>
       <c r="R207" t="n">
-        <v>7102649</v>
+        <v>7102097</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22158,19 +22158,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128997308</v>
+        <v>128997715</v>
       </c>
       <c r="B208" t="n">
         <v>79034</v>
@@ -22205,10 +22205,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>733331</v>
+        <v>733353</v>
       </c>
       <c r="R208" t="n">
-        <v>7102372</v>
+        <v>7102649</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22255,22 +22255,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128997366</v>
+        <v>128997308</v>
       </c>
       <c r="B209" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22278,21 +22278,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>733203</v>
+        <v>733331</v>
       </c>
       <c r="R209" t="n">
-        <v>7102097</v>
+        <v>7102372</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22352,12 +22352,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
@@ -22367,7 +22367,7 @@
         <v>128997267</v>
       </c>
       <c r="B210" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>128997618</v>
       </c>
       <c r="B211" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -22558,32 +22558,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128997661</v>
+        <v>128997361</v>
       </c>
       <c r="B212" t="n">
-        <v>97522</v>
+        <v>91523</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22593,10 +22593,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>733345</v>
+        <v>733368</v>
       </c>
       <c r="R212" t="n">
-        <v>7102514</v>
+        <v>7102873</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22643,44 +22643,44 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128997361</v>
+        <v>128997664</v>
       </c>
       <c r="B213" t="n">
-        <v>91520</v>
+        <v>80167</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22690,10 +22690,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>733368</v>
+        <v>733456</v>
       </c>
       <c r="R213" t="n">
-        <v>7102873</v>
+        <v>7102608</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22740,44 +22740,44 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128997390</v>
+        <v>128997661</v>
       </c>
       <c r="B214" t="n">
-        <v>79034</v>
+        <v>97527</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22787,10 +22787,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>733234</v>
+        <v>733345</v>
       </c>
       <c r="R214" t="n">
-        <v>7102737</v>
+        <v>7102514</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22837,12 +22837,12 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
@@ -22946,32 +22946,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128997664</v>
+        <v>128997390</v>
       </c>
       <c r="B216" t="n">
-        <v>80167</v>
+        <v>79034</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22981,10 +22981,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>733456</v>
+        <v>733234</v>
       </c>
       <c r="R216" t="n">
-        <v>7102608</v>
+        <v>7102737</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23031,22 +23031,22 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128997667</v>
+        <v>128997240</v>
       </c>
       <c r="B217" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23054,21 +23054,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23078,10 +23078,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>732976</v>
+        <v>733309</v>
       </c>
       <c r="R217" t="n">
-        <v>7102116</v>
+        <v>7102326</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23108,12 +23108,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23128,19 +23128,19 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128997694</v>
+        <v>128997306</v>
       </c>
       <c r="B218" t="n">
         <v>79034</v>
@@ -23175,10 +23175,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>733419</v>
+        <v>733122</v>
       </c>
       <c r="R218" t="n">
-        <v>7102646</v>
+        <v>7102126</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23225,19 +23225,19 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Amelie Anderson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128997306</v>
+        <v>128997694</v>
       </c>
       <c r="B219" t="n">
         <v>79034</v>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>733122</v>
+        <v>733419</v>
       </c>
       <c r="R219" t="n">
-        <v>7102126</v>
+        <v>7102646</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23322,22 +23322,22 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Amelie Anderson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128997240</v>
+        <v>128997641</v>
       </c>
       <c r="B220" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23345,21 +23345,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23369,10 +23369,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>733309</v>
+        <v>732869</v>
       </c>
       <c r="R220" t="n">
-        <v>7102326</v>
+        <v>7102347</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23399,12 +23399,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23419,12 +23419,12 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
@@ -23434,7 +23434,7 @@
         <v>128997639</v>
       </c>
       <c r="B221" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>128997637</v>
       </c>
       <c r="B222" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -23625,10 +23625,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128997641</v>
+        <v>128997667</v>
       </c>
       <c r="B223" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -23636,21 +23636,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23660,10 +23660,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>732869</v>
+        <v>732976</v>
       </c>
       <c r="R223" t="n">
-        <v>7102347</v>
+        <v>7102116</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23715,39 +23715,39 @@
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Ida Persson, Amelie Anderson</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128997685</v>
+        <v>128997628</v>
       </c>
       <c r="B224" t="n">
-        <v>91538</v>
+        <v>91488</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23757,10 +23757,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>733407</v>
+        <v>732875</v>
       </c>
       <c r="R224" t="n">
-        <v>7102536</v>
+        <v>7102148</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23787,12 +23787,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -23812,39 +23812,39 @@
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128997628</v>
+        <v>128997685</v>
       </c>
       <c r="B225" t="n">
-        <v>91485</v>
+        <v>91541</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23854,10 +23854,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>732875</v>
+        <v>733407</v>
       </c>
       <c r="R225" t="n">
-        <v>7102148</v>
+        <v>7102536</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23884,12 +23884,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -23909,17 +23909,17 @@
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Amelie Anderson, Ida Persson, Tuva Niska</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128997218</v>
+        <v>128996674</v>
       </c>
       <c r="B226" t="n">
-        <v>91485</v>
+        <v>58093</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23927,21 +23927,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23951,10 +23951,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>733152</v>
+        <v>733336</v>
       </c>
       <c r="R226" t="n">
-        <v>7102090</v>
+        <v>7102620</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24001,44 +24001,44 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Tuva Niska</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128997348</v>
+        <v>128997705</v>
       </c>
       <c r="B227" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24048,10 +24048,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>733192</v>
+        <v>733002</v>
       </c>
       <c r="R227" t="n">
-        <v>7102672</v>
+        <v>7102410</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24098,12 +24098,12 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
@@ -24207,32 +24207,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128997705</v>
+        <v>128997218</v>
       </c>
       <c r="B229" t="n">
-        <v>79034</v>
+        <v>91488</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24242,10 +24242,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>733002</v>
+        <v>733152</v>
       </c>
       <c r="R229" t="n">
-        <v>7102410</v>
+        <v>7102090</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24292,22 +24292,22 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
+          <t>Tuva Niska</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128996674</v>
+        <v>128997348</v>
       </c>
       <c r="B230" t="n">
-        <v>58093</v>
+        <v>91488</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -24315,21 +24315,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -24339,10 +24339,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>733336</v>
+        <v>733192</v>
       </c>
       <c r="R230" t="n">
-        <v>7102620</v>
+        <v>7102672</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24389,22 +24389,22 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Emma Lundh</t>
+          <t>Ida Persson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128997406</v>
+        <v>128997724</v>
       </c>
       <c r="B231" t="n">
-        <v>79034</v>
+        <v>88923</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24412,21 +24412,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24436,10 +24436,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>733178</v>
+        <v>732905</v>
       </c>
       <c r="R231" t="n">
-        <v>7102089</v>
+        <v>7102156</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24466,12 +24466,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -24486,19 +24486,19 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Felix Gustafsson, Emma Lundh, Tuva Niska, Amelie Anderson, Ida Persson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128997397</v>
+        <v>128996683</v>
       </c>
       <c r="B232" t="n">
         <v>79034</v>
@@ -24533,10 +24533,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>733074</v>
+        <v>733186</v>
       </c>
       <c r="R232" t="n">
-        <v>7102532</v>
+        <v>7102300</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24583,44 +24583,44 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Ida Persson</t>
+          <t>Emma Lundh</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128997626</v>
+        <v>128997398</v>
       </c>
       <c r="B233" t="n">
-        <v>91485</v>
+        <v>79034</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24630,10 +24630,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>732917</v>
+        <v>733069</v>
       </c>
       <c r="R233" t="n">
-        <v>7102230</v>
+        <v>7102479</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24660,12 +24660,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -24680,19 +24680,19 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>I